--- a/data/italy/p4_modeling/2024-10-15/df_iteration_test.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_iteration_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X354"/>
+  <dimension ref="A1:X404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26360,6 +26360,3742 @@
       <c r="W354" t="inlineStr"/>
       <c r="X354" t="inlineStr"/>
     </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>390</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>17.70925110132159</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>42.89693593314763</v>
+      </c>
+      <c r="F355" t="n">
+        <v>42.72686317151786</v>
+      </c>
+      <c r="G355" t="n">
+        <v>36.47253727539186</v>
+      </c>
+      <c r="H355" t="n">
+        <v>51.25348189415042</v>
+      </c>
+      <c r="I355" t="n">
+        <v>-8.356545961002787</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0.1144178126137504</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0.06080098936951714</v>
+      </c>
+      <c r="L355" t="n">
+        <v>0.07031932407017176</v>
+      </c>
+      <c r="M355" t="n">
+        <v>27.89151669269441</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0.07769224705485907</v>
+      </c>
+      <c r="O355" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>5</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0</v>
+      </c>
+      <c r="S355" t="b">
+        <v>0</v>
+      </c>
+      <c r="T355" t="n">
+        <v>0.1687138432095337</v>
+      </c>
+      <c r="U355" t="n">
+        <v>0.3220926814791364</v>
+      </c>
+      <c r="V355" t="n">
+        <v>0.1836722123868553</v>
+      </c>
+      <c r="W355" t="inlineStr"/>
+      <c r="X355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>391</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>17.53846153846154</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F356" t="n">
+        <v>40.73099415204678</v>
+      </c>
+      <c r="G356" t="n">
+        <v>35.04260035258208</v>
+      </c>
+      <c r="H356" t="n">
+        <v>54.93421052631579</v>
+      </c>
+      <c r="I356" t="n">
+        <v>-17.43421052631579</v>
+      </c>
+      <c r="J356" t="n">
+        <v>-0.120982447111063</v>
+      </c>
+      <c r="K356" t="n">
+        <v>-0.02986523702524835</v>
+      </c>
+      <c r="L356" t="n">
+        <v>-0.04737147852798661</v>
+      </c>
+      <c r="M356" t="n">
+        <v>-25.77745380288205</v>
+      </c>
+      <c r="N356" t="n">
+        <v>-0.08507410496000677</v>
+      </c>
+      <c r="O356" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="b">
+        <v>1</v>
+      </c>
+      <c r="T356" t="n">
+        <v>-0.05751643696257489</v>
+      </c>
+      <c r="U356" t="n">
+        <v>-0.07205438728700068</v>
+      </c>
+      <c r="V356" t="n">
+        <v>-0.08456604558662036</v>
+      </c>
+      <c r="W356" t="inlineStr"/>
+      <c r="X356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>392</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>13.61277445109781</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>45.24421593830334</v>
+      </c>
+      <c r="F357" t="n">
+        <v>44.49059644636246</v>
+      </c>
+      <c r="G357" t="n">
+        <v>40.05226480836237</v>
+      </c>
+      <c r="H357" t="n">
+        <v>52.69922879177378</v>
+      </c>
+      <c r="I357" t="n">
+        <v>-7.455012853470436</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0.6755597431208048</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0.6857331214936829</v>
+      </c>
+      <c r="L357" t="n">
+        <v>0.2653505534974075</v>
+      </c>
+      <c r="M357" t="n">
+        <v>13.40941197424179</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0.03456034013979843</v>
+      </c>
+      <c r="O357" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>5</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0</v>
+      </c>
+      <c r="S357" t="b">
+        <v>0</v>
+      </c>
+      <c r="T357" t="n">
+        <v>0.2374517005036802</v>
+      </c>
+      <c r="U357" t="n">
+        <v>0.1008561247545068</v>
+      </c>
+      <c r="V357" t="n">
+        <v>0.02817405336156336</v>
+      </c>
+      <c r="W357" t="inlineStr"/>
+      <c r="X357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>394</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>18.31632653061225</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>44.61538461538462</v>
+      </c>
+      <c r="F358" t="n">
+        <v>43.19383203114928</v>
+      </c>
+      <c r="G358" t="n">
+        <v>38.77970097825968</v>
+      </c>
+      <c r="H358" t="n">
+        <v>49.84615384615385</v>
+      </c>
+      <c r="I358" t="n">
+        <v>-5.230769230769226</v>
+      </c>
+      <c r="J358" t="n">
+        <v>0.09515267226345202</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0.8232999776881457</v>
+      </c>
+      <c r="L358" t="n">
+        <v>0.9448055772076509</v>
+      </c>
+      <c r="M358" t="n">
+        <v>83.31497256100528</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0.2563537617261701</v>
+      </c>
+      <c r="O358" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>10</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="b">
+        <v>0</v>
+      </c>
+      <c r="T358" t="n">
+        <v>0.6625901983549505</v>
+      </c>
+      <c r="U358" t="n">
+        <v>1.342171542758704</v>
+      </c>
+      <c r="V358" t="n">
+        <v>0.3991854473715128</v>
+      </c>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>395</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>19.84496124031008</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>40.625</v>
+      </c>
+      <c r="F359" t="n">
+        <v>37.00389020019232</v>
+      </c>
+      <c r="G359" t="n">
+        <v>33.42334856668052</v>
+      </c>
+      <c r="H359" t="n">
+        <v>50</v>
+      </c>
+      <c r="I359" t="n">
+        <v>-9.375</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0.252155123802433</v>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="n">
+        <v>5.571901571649704</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0.05804064137135109</v>
+      </c>
+      <c r="O359" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>10</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="b">
+        <v>1</v>
+      </c>
+      <c r="T359" t="inlineStr"/>
+      <c r="U359" t="inlineStr"/>
+      <c r="V359" t="inlineStr"/>
+      <c r="W359" t="inlineStr"/>
+      <c r="X359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>396</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>17.33333333333333</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>41.53846153846154</v>
+      </c>
+      <c r="F360" t="n">
+        <v>43.31939466348069</v>
+      </c>
+      <c r="G360" t="n">
+        <v>37.13701278348918</v>
+      </c>
+      <c r="H360" t="n">
+        <v>46.76923076923077</v>
+      </c>
+      <c r="I360" t="n">
+        <v>-5.230769230769226</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0.2232684864645802</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0.1843327230825916</v>
+      </c>
+      <c r="L360" t="n">
+        <v>0.06009375671273214</v>
+      </c>
+      <c r="M360" t="n">
+        <v>55.35816973288053</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0.1708585485582732</v>
+      </c>
+      <c r="O360" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>10</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="b">
+        <v>0</v>
+      </c>
+      <c r="T360" t="n">
+        <v>0.1550365919097473</v>
+      </c>
+      <c r="U360" t="n">
+        <v>0.3051343593056596</v>
+      </c>
+      <c r="V360" t="n">
+        <v>-0.04121087208912063</v>
+      </c>
+      <c r="W360" t="inlineStr"/>
+      <c r="X360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>397</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>16.94267515923567</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>42.01680672268908</v>
+      </c>
+      <c r="F361" t="n">
+        <v>42.19090413943356</v>
+      </c>
+      <c r="G361" t="n">
+        <v>39.00575917491988</v>
+      </c>
+      <c r="H361" t="n">
+        <v>46.21848739495798</v>
+      </c>
+      <c r="I361" t="n">
+        <v>-4.201680672268907</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0.2102642245473231</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0.212848727151397</v>
+      </c>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="n">
+        <v>-0.9535458646156342</v>
+      </c>
+      <c r="N361" t="n">
+        <v>-0.00801299045895491</v>
+      </c>
+      <c r="O361" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>5</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" t="b">
+        <v>0</v>
+      </c>
+      <c r="T361" t="inlineStr"/>
+      <c r="U361" t="inlineStr"/>
+      <c r="V361" t="inlineStr"/>
+      <c r="W361" t="inlineStr"/>
+      <c r="X361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>398</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>18.84057971014493</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>43.36283185840708</v>
+      </c>
+      <c r="F362" t="n">
+        <v>42.94353392018029</v>
+      </c>
+      <c r="G362" t="n">
+        <v>39.16314523979347</v>
+      </c>
+      <c r="H362" t="n">
+        <v>51.91740412979351</v>
+      </c>
+      <c r="I362" t="n">
+        <v>-8.554572271386434</v>
+      </c>
+      <c r="J362" t="n">
+        <v>-0.0827714308277885</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0.02433186118376668</v>
+      </c>
+      <c r="L362" t="n">
+        <v>0.04522100936370899</v>
+      </c>
+      <c r="M362" t="n">
+        <v>2.02497593278224</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0.005991053055568758</v>
+      </c>
+      <c r="O362" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="b">
+        <v>1</v>
+      </c>
+      <c r="T362" t="n">
+        <v>0.02679221853853001</v>
+      </c>
+      <c r="U362" t="n">
+        <v>-0.01055468861598246</v>
+      </c>
+      <c r="V362" t="n">
+        <v>0.0113626797859601</v>
+      </c>
+      <c r="W362" t="inlineStr"/>
+      <c r="X362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>399</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>17.78625954198473</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>46.60194174757282</v>
+      </c>
+      <c r="F363" t="n">
+        <v>42.07634744719144</v>
+      </c>
+      <c r="G363" t="n">
+        <v>39.62538862980235</v>
+      </c>
+      <c r="H363" t="n">
+        <v>49.02912621359224</v>
+      </c>
+      <c r="I363" t="n">
+        <v>-2.427184466019419</v>
+      </c>
+      <c r="J363" t="n">
+        <v>-0.7270598886737948</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0.5465392831610387</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0.1189079915722855</v>
+      </c>
+      <c r="M363" t="n">
+        <v>97.62179762054387</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0.4762038908319213</v>
+      </c>
+      <c r="O363" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>15</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="b">
+        <v>0</v>
+      </c>
+      <c r="T363" t="n">
+        <v>0.5766884447562597</v>
+      </c>
+      <c r="U363" t="inlineStr"/>
+      <c r="V363" t="inlineStr"/>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>400</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>18.7308533916849</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>41.5041782729805</v>
+      </c>
+      <c r="F364" t="n">
+        <v>43.66559291018255</v>
+      </c>
+      <c r="G364" t="n">
+        <v>37.34480043057035</v>
+      </c>
+      <c r="H364" t="n">
+        <v>46.51810584958218</v>
+      </c>
+      <c r="I364" t="n">
+        <v>-5.013927576601674</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0.6509840678388451</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0.4301866242041456</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0.2283729628568422</v>
+      </c>
+      <c r="M364" t="n">
+        <v>27.64700481943867</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0.07722627044535943</v>
+      </c>
+      <c r="O364" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q364" t="n">
+        <v>5</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="b">
+        <v>0</v>
+      </c>
+      <c r="T364" t="n">
+        <v>0.01840698267522605</v>
+      </c>
+      <c r="U364" t="n">
+        <v>0.07225183698261799</v>
+      </c>
+      <c r="V364" t="n">
+        <v>0.1706620571439088</v>
+      </c>
+      <c r="W364" t="inlineStr"/>
+      <c r="X364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>402</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>17.8125</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>40.06410256410257</v>
+      </c>
+      <c r="F365" t="n">
+        <v>40.0033274582898</v>
+      </c>
+      <c r="G365" t="n">
+        <v>33.74947313815128</v>
+      </c>
+      <c r="H365" t="n">
+        <v>55.44871794871795</v>
+      </c>
+      <c r="I365" t="n">
+        <v>-15.38461538461538</v>
+      </c>
+      <c r="J365" t="n">
+        <v>-0.1142768676884558</v>
+      </c>
+      <c r="K365" t="n">
+        <v>-0.05949813548757447</v>
+      </c>
+      <c r="L365" t="n">
+        <v>-0.04364479689249341</v>
+      </c>
+      <c r="M365" t="n">
+        <v>-7.928282111008414</v>
+      </c>
+      <c r="N365" t="n">
+        <v>-0.02549286852414281</v>
+      </c>
+      <c r="O365" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q365" t="n">
+        <v>0</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0</v>
+      </c>
+      <c r="S365" t="b">
+        <v>1</v>
+      </c>
+      <c r="T365" t="n">
+        <v>-0.01178289252785561</v>
+      </c>
+      <c r="U365" t="n">
+        <v>-0.04329258299534149</v>
+      </c>
+      <c r="V365" t="n">
+        <v>-0.01895979255604814</v>
+      </c>
+      <c r="W365" t="inlineStr"/>
+      <c r="X365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>404</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>19.42257217847769</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>44.23076923076923</v>
+      </c>
+      <c r="F366" t="n">
+        <v>43.23498929303553</v>
+      </c>
+      <c r="G366" t="n">
+        <v>38.58232489915658</v>
+      </c>
+      <c r="H366" t="n">
+        <v>50.64102564102564</v>
+      </c>
+      <c r="I366" t="n">
+        <v>-6.410256410256409</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0.4428178345010252</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0.01069759201997073</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0.2955284642090032</v>
+      </c>
+      <c r="M366" t="n">
+        <v>194.6682355353564</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0.6259428795349081</v>
+      </c>
+      <c r="O366" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>20</v>
+      </c>
+      <c r="R366" t="n">
+        <v>0</v>
+      </c>
+      <c r="S366" t="b">
+        <v>0</v>
+      </c>
+      <c r="T366" t="n">
+        <v>0.9303001086371606</v>
+      </c>
+      <c r="U366" t="n">
+        <v>0.8263029810458541</v>
+      </c>
+      <c r="V366" t="n">
+        <v>0.3697843249379527</v>
+      </c>
+      <c r="W366" t="inlineStr"/>
+      <c r="X366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>405</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>16.54135338345865</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F367" t="n">
+        <v>37.71025044662419</v>
+      </c>
+      <c r="G367" t="n">
+        <v>33.16882093668007</v>
+      </c>
+      <c r="H367" t="n">
+        <v>39.42307692307692</v>
+      </c>
+      <c r="I367" t="n">
+        <v>-1.92307692307692</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0.1403136285744822</v>
+      </c>
+      <c r="K367" t="n">
+        <v>-0.01881619535461226</v>
+      </c>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="n">
+        <v>-3.075130519592378</v>
+      </c>
+      <c r="N367" t="n">
+        <v>-0.02956856268838825</v>
+      </c>
+      <c r="O367" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>0</v>
+      </c>
+      <c r="R367" t="n">
+        <v>0</v>
+      </c>
+      <c r="S367" t="b">
+        <v>1</v>
+      </c>
+      <c r="T367" t="inlineStr"/>
+      <c r="U367" t="inlineStr"/>
+      <c r="V367" t="inlineStr"/>
+      <c r="W367" t="inlineStr"/>
+      <c r="X367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>406</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>18.57506361323155</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>44.92307692307692</v>
+      </c>
+      <c r="F368" t="n">
+        <v>43.25362733867888</v>
+      </c>
+      <c r="G368" t="n">
+        <v>38.58212774917429</v>
+      </c>
+      <c r="H368" t="n">
+        <v>50.46153846153846</v>
+      </c>
+      <c r="I368" t="n">
+        <v>-5.53846153846154</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0.5530880021036378</v>
+      </c>
+      <c r="K368" t="n">
+        <v>-0.3976282200622465</v>
+      </c>
+      <c r="L368" t="n">
+        <v>0.1830606666842542</v>
+      </c>
+      <c r="M368" t="n">
+        <v>381.0474190804452</v>
+      </c>
+      <c r="N368" t="n">
+        <v>1.176072281112485</v>
+      </c>
+      <c r="O368" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>20</v>
+      </c>
+      <c r="R368" t="n">
+        <v>0</v>
+      </c>
+      <c r="S368" t="b">
+        <v>0</v>
+      </c>
+      <c r="T368" t="n">
+        <v>2.364352908338713</v>
+      </c>
+      <c r="U368" t="n">
+        <v>4.5156443477862</v>
+      </c>
+      <c r="V368" t="n">
+        <v>1.097431838726106</v>
+      </c>
+      <c r="W368" t="inlineStr"/>
+      <c r="X368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>407</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>12.20973782771536</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>44.97607655502392</v>
+      </c>
+      <c r="F369" t="n">
+        <v>45.41447908853888</v>
+      </c>
+      <c r="G369" t="n">
+        <v>43.28416651946063</v>
+      </c>
+      <c r="H369" t="n">
+        <v>48.32535885167464</v>
+      </c>
+      <c r="I369" t="n">
+        <v>-3.349282296650721</v>
+      </c>
+      <c r="J369" t="n">
+        <v>4.088532142618704</v>
+      </c>
+      <c r="K369" t="n">
+        <v>1.373340302993962</v>
+      </c>
+      <c r="L369" t="n">
+        <v>0.5306191022660414</v>
+      </c>
+      <c r="M369" t="n">
+        <v>56.09754073500346</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0.269699715072132</v>
+      </c>
+      <c r="O369" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>10</v>
+      </c>
+      <c r="R369" t="n">
+        <v>0</v>
+      </c>
+      <c r="S369" t="b">
+        <v>1</v>
+      </c>
+      <c r="T369" t="n">
+        <v>0.1491861128141848</v>
+      </c>
+      <c r="U369" t="inlineStr"/>
+      <c r="V369" t="inlineStr"/>
+      <c r="W369" t="inlineStr"/>
+      <c r="X369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>408</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>17.12962962962963</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>39.30635838150289</v>
+      </c>
+      <c r="F370" t="n">
+        <v>40.88614766552497</v>
+      </c>
+      <c r="G370" t="n">
+        <v>35.93753610987307</v>
+      </c>
+      <c r="H370" t="n">
+        <v>50.86705202312138</v>
+      </c>
+      <c r="I370" t="n">
+        <v>-11.56069364161849</v>
+      </c>
+      <c r="J370" t="n">
+        <v>-0.07619246068753086</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-0.01847867344787559</v>
+      </c>
+      <c r="L370" t="n">
+        <v>-0.02752022626235278</v>
+      </c>
+      <c r="M370" t="n">
+        <v>-11.81592516243579</v>
+      </c>
+      <c r="N370" t="n">
+        <v>-0.03415007272380286</v>
+      </c>
+      <c r="O370" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>0</v>
+      </c>
+      <c r="R370" t="n">
+        <v>0</v>
+      </c>
+      <c r="S370" t="b">
+        <v>1</v>
+      </c>
+      <c r="T370" t="n">
+        <v>0.004663648512651548</v>
+      </c>
+      <c r="U370" t="n">
+        <v>-0.01535883547457689</v>
+      </c>
+      <c r="V370" t="n">
+        <v>-0.02838612424173178</v>
+      </c>
+      <c r="W370" t="inlineStr"/>
+      <c r="X370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>409</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>20.56338028169014</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>51.80180180180181</v>
+      </c>
+      <c r="F371" t="n">
+        <v>48.81659594530881</v>
+      </c>
+      <c r="G371" t="n">
+        <v>46.7141560164816</v>
+      </c>
+      <c r="H371" t="n">
+        <v>58.55855855855856</v>
+      </c>
+      <c r="I371" t="n">
+        <v>-6.756756756756751</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0.4460170123765198</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-0.8256118727963778</v>
+      </c>
+      <c r="L371" t="n">
+        <v>-0.2142854835000401</v>
+      </c>
+      <c r="M371" t="n">
+        <v>484.6935067063819</v>
+      </c>
+      <c r="N371" t="n">
+        <v>2.193183288264172</v>
+      </c>
+      <c r="O371" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>20</v>
+      </c>
+      <c r="R371" t="n">
+        <v>0</v>
+      </c>
+      <c r="S371" t="b">
+        <v>0</v>
+      </c>
+      <c r="T371" t="n">
+        <v>1.152602281575109</v>
+      </c>
+      <c r="U371" t="inlineStr"/>
+      <c r="V371" t="inlineStr"/>
+      <c r="W371" t="inlineStr"/>
+      <c r="X371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>410</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>15.36529680365297</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>44.51038575667656</v>
+      </c>
+      <c r="F372" t="n">
+        <v>44.13014199970721</v>
+      </c>
+      <c r="G372" t="n">
+        <v>40.86829321494581</v>
+      </c>
+      <c r="H372" t="n">
+        <v>49.25816023738873</v>
+      </c>
+      <c r="I372" t="n">
+        <v>-4.747774480712174</v>
+      </c>
+      <c r="J372" t="n">
+        <v>3.269131862105474</v>
+      </c>
+      <c r="K372" t="n">
+        <v>1.670552655192973</v>
+      </c>
+      <c r="L372" t="n">
+        <v>1.820158165412755</v>
+      </c>
+      <c r="M372" t="n">
+        <v>75.00742768444715</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0.1112869846950254</v>
+      </c>
+      <c r="O372" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>10</v>
+      </c>
+      <c r="R372" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" t="b">
+        <v>0</v>
+      </c>
+      <c r="T372" t="n">
+        <v>0.7224108246913472</v>
+      </c>
+      <c r="U372" t="n">
+        <v>1.257148340850603</v>
+      </c>
+      <c r="V372" t="n">
+        <v>1.740123336158142</v>
+      </c>
+      <c r="W372" t="n">
+        <v>1.480643463070489</v>
+      </c>
+      <c r="X372" t="n">
+        <v>0.4762895895038529</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>411</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>21.18421052631579</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>40.7563025210084</v>
+      </c>
+      <c r="F373" t="n">
+        <v>41.43617021276596</v>
+      </c>
+      <c r="G373" t="n">
+        <v>39.59273656221023</v>
+      </c>
+      <c r="H373" t="n">
+        <v>49.15966386554621</v>
+      </c>
+      <c r="I373" t="n">
+        <v>-8.403361344537814</v>
+      </c>
+      <c r="J373" t="n">
+        <v>-0.1326062455335176</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-0.04887256647226323</v>
+      </c>
+      <c r="L373" t="n">
+        <v>-0.07074973896841433</v>
+      </c>
+      <c r="M373" t="n">
+        <v>-2.754153350095834</v>
+      </c>
+      <c r="N373" t="n">
+        <v>-0.01157207289956233</v>
+      </c>
+      <c r="O373" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0</v>
+      </c>
+      <c r="S373" t="b">
+        <v>1</v>
+      </c>
+      <c r="T373" t="n">
+        <v>-0.04352295325721663</v>
+      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr"/>
+      <c r="W373" t="inlineStr"/>
+      <c r="X373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>412</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>12.05479452054795</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>45.67567567567568</v>
+      </c>
+      <c r="F374" t="n">
+        <v>46.56902356902356</v>
+      </c>
+      <c r="G374" t="n">
+        <v>43.3910533910534</v>
+      </c>
+      <c r="H374" t="n">
+        <v>51.89189189189189</v>
+      </c>
+      <c r="I374" t="n">
+        <v>-6.216216216216218</v>
+      </c>
+      <c r="J374" t="n">
+        <v>-1.161727882714566</v>
+      </c>
+      <c r="K374" t="n">
+        <v>-0.7421057897221038</v>
+      </c>
+      <c r="L374" t="n">
+        <v>-0.4042827554863069</v>
+      </c>
+      <c r="M374" t="n">
+        <v>70.44794895827241</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0.09532875366477998</v>
+      </c>
+      <c r="O374" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>10</v>
+      </c>
+      <c r="R374" t="n">
+        <v>0</v>
+      </c>
+      <c r="S374" t="b">
+        <v>0</v>
+      </c>
+      <c r="T374" t="n">
+        <v>-0.2961490948561177</v>
+      </c>
+      <c r="U374" t="n">
+        <v>-0.2731620419536068</v>
+      </c>
+      <c r="V374" t="n">
+        <v>-0.1725983478019001</v>
+      </c>
+      <c r="W374" t="n">
+        <v>-0.03600049946108055</v>
+      </c>
+      <c r="X374" t="n">
+        <v>0.1002456400987266</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>413</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>14.98084291187739</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>45.21531100478469</v>
+      </c>
+      <c r="F375" t="n">
+        <v>43.75126195855968</v>
+      </c>
+      <c r="G375" t="n">
+        <v>37.30933078359549</v>
+      </c>
+      <c r="H375" t="n">
+        <v>53.11004784688996</v>
+      </c>
+      <c r="I375" t="n">
+        <v>-7.894736842105267</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0.04636227895628565</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-0.05798695428362351</v>
+      </c>
+      <c r="L375" t="n">
+        <v>0.1056970936152119</v>
+      </c>
+      <c r="M375" t="n">
+        <v>20.06511993671188</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0.04800267927443034</v>
+      </c>
+      <c r="O375" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>5</v>
+      </c>
+      <c r="R375" t="n">
+        <v>0</v>
+      </c>
+      <c r="S375" t="b">
+        <v>0</v>
+      </c>
+      <c r="T375" t="n">
+        <v>-0.02247727010572333</v>
+      </c>
+      <c r="U375" t="n">
+        <v>0.01537096660001021</v>
+      </c>
+      <c r="V375" t="n">
+        <v>-0.01271070051090026</v>
+      </c>
+      <c r="W375" t="n">
+        <v>0.03023288479902849</v>
+      </c>
+      <c r="X375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>414</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>12.65388496468214</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>45.12353706111833</v>
+      </c>
+      <c r="F376" t="n">
+        <v>45.11147108644897</v>
+      </c>
+      <c r="G376" t="n">
+        <v>41.27405973664561</v>
+      </c>
+      <c r="H376" t="n">
+        <v>54.22626788036411</v>
+      </c>
+      <c r="I376" t="n">
+        <v>-9.102730819245778</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0.01127942515423598</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-0.0523707311339885</v>
+      </c>
+      <c r="L376" t="n">
+        <v>-0.04759953936444541</v>
+      </c>
+      <c r="M376" t="n">
+        <v>-6.353286514590067</v>
+      </c>
+      <c r="N376" t="n">
+        <v>-0.008261750994265366</v>
+      </c>
+      <c r="O376" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>0</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0</v>
+      </c>
+      <c r="S376" t="b">
+        <v>1</v>
+      </c>
+      <c r="T376" t="n">
+        <v>-0.05515582256202123</v>
+      </c>
+      <c r="U376" t="n">
+        <v>-0.05845722511212927</v>
+      </c>
+      <c r="V376" t="n">
+        <v>-0.04413691847234096</v>
+      </c>
+      <c r="W376" t="n">
+        <v>-0.03303486518514639</v>
+      </c>
+      <c r="X376" t="n">
+        <v>-0.02081862371733692</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>415</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>17.0635838150289</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>45.6973293768546</v>
+      </c>
+      <c r="F377" t="n">
+        <v>44.88741553497685</v>
+      </c>
+      <c r="G377" t="n">
+        <v>41.95556490281247</v>
+      </c>
+      <c r="H377" t="n">
+        <v>46.43916913946587</v>
+      </c>
+      <c r="I377" t="n">
+        <v>-0.7418397626112778</v>
+      </c>
+      <c r="J377" t="n">
+        <v>-0.5945794504204309</v>
+      </c>
+      <c r="K377" t="n">
+        <v>-0.5501141172487966</v>
+      </c>
+      <c r="L377" t="n">
+        <v>-0.4851739804692174</v>
+      </c>
+      <c r="M377" t="n">
+        <v>252.9942401544902</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0.3753623741164543</v>
+      </c>
+      <c r="O377" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>10</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0</v>
+      </c>
+      <c r="S377" t="b">
+        <v>1</v>
+      </c>
+      <c r="T377" t="n">
+        <v>-0.3011918955836708</v>
+      </c>
+      <c r="U377" t="n">
+        <v>-0.1877193974838343</v>
+      </c>
+      <c r="V377" t="n">
+        <v>0.00111883421564689</v>
+      </c>
+      <c r="W377" t="n">
+        <v>0.01650309341424062</v>
+      </c>
+      <c r="X377" t="n">
+        <v>0.1860208460453191</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>416</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>14.45506692160612</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>43.26683291770573</v>
+      </c>
+      <c r="F378" t="n">
+        <v>42.03854102989551</v>
+      </c>
+      <c r="G378" t="n">
+        <v>38.10478736949325</v>
+      </c>
+      <c r="H378" t="n">
+        <v>50.99750623441397</v>
+      </c>
+      <c r="I378" t="n">
+        <v>-7.730673316708234</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0.01086881175109966</v>
+      </c>
+      <c r="K378" t="n">
+        <v>-0.05470570011453233</v>
+      </c>
+      <c r="L378" t="n">
+        <v>-0.01448712291430278</v>
+      </c>
+      <c r="M378" t="n">
+        <v>5.76268628067406</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0.007194364894724171</v>
+      </c>
+      <c r="O378" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q378" t="n">
+        <v>0</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" t="b">
+        <v>1</v>
+      </c>
+      <c r="T378" t="n">
+        <v>-0.01356172618851211</v>
+      </c>
+      <c r="U378" t="n">
+        <v>-0.00510357199582171</v>
+      </c>
+      <c r="V378" t="n">
+        <v>0.01144816063667865</v>
+      </c>
+      <c r="W378" t="n">
+        <v>0.01265279509214995</v>
+      </c>
+      <c r="X378" t="n">
+        <v>0.02050293915972634</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>417</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>21.3986013986014</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>45</v>
+      </c>
+      <c r="F379" t="n">
+        <v>45.03209617180205</v>
+      </c>
+      <c r="G379" t="n">
+        <v>42.90313417290029</v>
+      </c>
+      <c r="H379" t="n">
+        <v>58.63636363636363</v>
+      </c>
+      <c r="I379" t="n">
+        <v>-13.63636363636363</v>
+      </c>
+      <c r="J379" t="n">
+        <v>-0.07222580273059891</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-0.04681707154073479</v>
+      </c>
+      <c r="L379" t="n">
+        <v>-0.03109130057148424</v>
+      </c>
+      <c r="M379" t="n">
+        <v>-3.465968273793891</v>
+      </c>
+      <c r="N379" t="n">
+        <v>-0.01575440124451769</v>
+      </c>
+      <c r="O379" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="b">
+        <v>1</v>
+      </c>
+      <c r="T379" t="n">
+        <v>-0.03239760424536058</v>
+      </c>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr"/>
+      <c r="W379" t="inlineStr"/>
+      <c r="X379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>418</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>14.2242355605889</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>40.65281899109792</v>
+      </c>
+      <c r="F380" t="n">
+        <v>41.40953669824403</v>
+      </c>
+      <c r="G380" t="n">
+        <v>36.23010818195245</v>
+      </c>
+      <c r="H380" t="n">
+        <v>50</v>
+      </c>
+      <c r="I380" t="n">
+        <v>-9.347181008902076</v>
+      </c>
+      <c r="J380" t="n">
+        <v>-0.08325642149163912</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-0.04382778184850366</v>
+      </c>
+      <c r="L380" t="n">
+        <v>-0.002188654728950136</v>
+      </c>
+      <c r="M380" t="n">
+        <v>-4.89007102095789</v>
+      </c>
+      <c r="N380" t="n">
+        <v>-0.007266078782998352</v>
+      </c>
+      <c r="O380" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q380" t="n">
+        <v>0</v>
+      </c>
+      <c r="R380" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" t="b">
+        <v>1</v>
+      </c>
+      <c r="T380" t="n">
+        <v>-0.00680501656019274</v>
+      </c>
+      <c r="U380" t="n">
+        <v>0.03435665949407047</v>
+      </c>
+      <c r="V380" t="n">
+        <v>0.02273436533942122</v>
+      </c>
+      <c r="W380" t="n">
+        <v>0.03592207034693143</v>
+      </c>
+      <c r="X380" t="n">
+        <v>0.03187322782407939</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>419</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>16.66026871401152</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>47.33009708737864</v>
+      </c>
+      <c r="F381" t="n">
+        <v>44.38177606401906</v>
+      </c>
+      <c r="G381" t="n">
+        <v>40.30847847121432</v>
+      </c>
+      <c r="H381" t="n">
+        <v>52.42718446601942</v>
+      </c>
+      <c r="I381" t="n">
+        <v>-5.097087378640779</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0.1213782566290143</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-0.3450108911666885</v>
+      </c>
+      <c r="L381" t="n">
+        <v>-0.2650573530064507</v>
+      </c>
+      <c r="M381" t="n">
+        <v>33.47179548858676</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0.08143989169972449</v>
+      </c>
+      <c r="O381" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q381" t="n">
+        <v>10</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0</v>
+      </c>
+      <c r="S381" t="b">
+        <v>0</v>
+      </c>
+      <c r="T381" t="n">
+        <v>-0.1618771372224165</v>
+      </c>
+      <c r="U381" t="n">
+        <v>-0.1375309666776361</v>
+      </c>
+      <c r="V381" t="n">
+        <v>-0.0006506744694605023</v>
+      </c>
+      <c r="W381" t="n">
+        <v>0.08941134160948672</v>
+      </c>
+      <c r="X381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>420</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>12.01725997842503</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="F382" t="n">
+        <v>45.61825407560522</v>
+      </c>
+      <c r="G382" t="n">
+        <v>43.75879422262981</v>
+      </c>
+      <c r="H382" t="n">
+        <v>52.77777777777778</v>
+      </c>
+      <c r="I382" t="n">
+        <v>-6.527777777777779</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0.148350414107295</v>
+      </c>
+      <c r="K382" t="n">
+        <v>-0.0562881519314476</v>
+      </c>
+      <c r="L382" t="n">
+        <v>-0.08475291578632606</v>
+      </c>
+      <c r="M382" t="n">
+        <v>7.245901785090838</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0.01006375247929283</v>
+      </c>
+      <c r="O382" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q382" t="n">
+        <v>5</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0</v>
+      </c>
+      <c r="S382" t="b">
+        <v>0</v>
+      </c>
+      <c r="T382" t="n">
+        <v>-0.05368681053098136</v>
+      </c>
+      <c r="U382" t="n">
+        <v>-0.03729541306531996</v>
+      </c>
+      <c r="V382" t="n">
+        <v>-0.03150866812802609</v>
+      </c>
+      <c r="W382" t="n">
+        <v>-0.02141024120947101</v>
+      </c>
+      <c r="X382" t="n">
+        <v>0.001040565640018485</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>421</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>18.65384615384615</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>48.35680751173709</v>
+      </c>
+      <c r="F383" t="n">
+        <v>46.60838185558383</v>
+      </c>
+      <c r="G383" t="n">
+        <v>45.48270483215946</v>
+      </c>
+      <c r="H383" t="n">
+        <v>50.46948356807511</v>
+      </c>
+      <c r="I383" t="n">
+        <v>-2.112676056338024</v>
+      </c>
+      <c r="J383" t="n">
+        <v>-0.8264937345468923</v>
+      </c>
+      <c r="K383" t="n">
+        <v>-0.6420954387070907</v>
+      </c>
+      <c r="L383" t="n">
+        <v>-0.460797233175322</v>
+      </c>
+      <c r="M383" t="n">
+        <v>694.2740333151893</v>
+      </c>
+      <c r="N383" t="n">
+        <v>1.637438757818843</v>
+      </c>
+      <c r="O383" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>25</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" t="b">
+        <v>0</v>
+      </c>
+      <c r="T383" t="n">
+        <v>-0.2550736372433666</v>
+      </c>
+      <c r="U383" t="n">
+        <v>0.06037637155617512</v>
+      </c>
+      <c r="V383" t="n">
+        <v>0.2401259345774527</v>
+      </c>
+      <c r="W383" t="n">
+        <v>0.4023763450473089</v>
+      </c>
+      <c r="X383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>422</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>13.68191721132898</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>46.1756373937677</v>
+      </c>
+      <c r="F384" t="n">
+        <v>45.98312262413427</v>
+      </c>
+      <c r="G384" t="n">
+        <v>43.67309683581047</v>
+      </c>
+      <c r="H384" t="n">
+        <v>50.70821529745042</v>
+      </c>
+      <c r="I384" t="n">
+        <v>-4.532577903682721</v>
+      </c>
+      <c r="J384" t="n">
+        <v>1.336017647013571</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1.893638512723897</v>
+      </c>
+      <c r="L384" t="n">
+        <v>0.7191246889491697</v>
+      </c>
+      <c r="M384" t="n">
+        <v>197.7133419273811</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0.2804444566345831</v>
+      </c>
+      <c r="O384" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>10</v>
+      </c>
+      <c r="R384" t="n">
+        <v>0</v>
+      </c>
+      <c r="S384" t="b">
+        <v>1</v>
+      </c>
+      <c r="T384" t="n">
+        <v>0.211869514004763</v>
+      </c>
+      <c r="U384" t="n">
+        <v>0.03761043073291216</v>
+      </c>
+      <c r="V384" t="n">
+        <v>0.04846650525092799</v>
+      </c>
+      <c r="W384" t="n">
+        <v>0.2431147176840827</v>
+      </c>
+      <c r="X384" t="n">
+        <v>0.05852198076188295</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>423</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>17.42808798646362</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>45.35637149028078</v>
+      </c>
+      <c r="F385" t="n">
+        <v>47.18537414965986</v>
+      </c>
+      <c r="G385" t="n">
+        <v>43.35203289736702</v>
+      </c>
+      <c r="H385" t="n">
+        <v>52.48380129589633</v>
+      </c>
+      <c r="I385" t="n">
+        <v>-7.127429805615549</v>
+      </c>
+      <c r="J385" t="n">
+        <v>-0.1210719383229011</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-0.05213004295922218</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0.001978350961504418</v>
+      </c>
+      <c r="M385" t="n">
+        <v>1.74453216482091</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0.003767888044969568</v>
+      </c>
+      <c r="O385" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" t="b">
+        <v>1</v>
+      </c>
+      <c r="T385" t="n">
+        <v>-0.01886097682642827</v>
+      </c>
+      <c r="U385" t="n">
+        <v>-0.03111518127286735</v>
+      </c>
+      <c r="V385" t="n">
+        <v>-0.01071444161926493</v>
+      </c>
+      <c r="W385" t="n">
+        <v>-0.005372540558605081</v>
+      </c>
+      <c r="X385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>424</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>13.29205366357069</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>44.99332443257677</v>
+      </c>
+      <c r="F386" t="n">
+        <v>44.99571577951282</v>
+      </c>
+      <c r="G386" t="n">
+        <v>42.71123015524527</v>
+      </c>
+      <c r="H386" t="n">
+        <v>52.60347129506007</v>
+      </c>
+      <c r="I386" t="n">
+        <v>-7.610146862483305</v>
+      </c>
+      <c r="J386" t="n">
+        <v>-0.5169766481586455</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-0.1265639457777507</v>
+      </c>
+      <c r="L386" t="n">
+        <v>0.03333773584596827</v>
+      </c>
+      <c r="M386" t="n">
+        <v>28.41381915049876</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0.03793567309812919</v>
+      </c>
+      <c r="O386" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>5</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="b">
+        <v>0</v>
+      </c>
+      <c r="T386" t="n">
+        <v>0.1038063350512689</v>
+      </c>
+      <c r="U386" t="n">
+        <v>0.08385672852202754</v>
+      </c>
+      <c r="V386" t="n">
+        <v>0.08863958078841899</v>
+      </c>
+      <c r="W386" t="n">
+        <v>0.02262300426416299</v>
+      </c>
+      <c r="X386" t="n">
+        <v>0.04838475527220402</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>425</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>22.89308176100629</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>47.5177304964539</v>
+      </c>
+      <c r="F387" t="n">
+        <v>47.27642276422764</v>
+      </c>
+      <c r="G387" t="n">
+        <v>45.87960948036387</v>
+      </c>
+      <c r="H387" t="n">
+        <v>55.31914893617022</v>
+      </c>
+      <c r="I387" t="n">
+        <v>-7.801418439716315</v>
+      </c>
+      <c r="J387" t="n">
+        <v>4.083824458900815</v>
+      </c>
+      <c r="K387" t="n">
+        <v>1.676151502298048</v>
+      </c>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="n">
+        <v>86.3221118261045</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0.6122135590503865</v>
+      </c>
+      <c r="O387" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>20</v>
+      </c>
+      <c r="R387" t="n">
+        <v>0</v>
+      </c>
+      <c r="S387" t="b">
+        <v>0</v>
+      </c>
+      <c r="T387" t="inlineStr"/>
+      <c r="U387" t="inlineStr"/>
+      <c r="V387" t="inlineStr"/>
+      <c r="W387" t="inlineStr"/>
+      <c r="X387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>426</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>14.52436194895592</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="F388" t="n">
+        <v>44.77948763838826</v>
+      </c>
+      <c r="G388" t="n">
+        <v>41.63722613922538</v>
+      </c>
+      <c r="H388" t="n">
+        <v>58.24345146379045</v>
+      </c>
+      <c r="I388" t="n">
+        <v>-12.788906009245</v>
+      </c>
+      <c r="J388" t="n">
+        <v>-0.09553181340421844</v>
+      </c>
+      <c r="K388" t="n">
+        <v>-0.08746382610446418</v>
+      </c>
+      <c r="L388" t="n">
+        <v>-0.08196903843095925</v>
+      </c>
+      <c r="M388" t="n">
+        <v>-26.10314108660535</v>
+      </c>
+      <c r="N388" t="n">
+        <v>-0.0402205563738141</v>
+      </c>
+      <c r="O388" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>0</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0</v>
+      </c>
+      <c r="S388" t="b">
+        <v>1</v>
+      </c>
+      <c r="T388" t="n">
+        <v>-0.06564622329092196</v>
+      </c>
+      <c r="U388" t="n">
+        <v>-0.07020909599458708</v>
+      </c>
+      <c r="V388" t="n">
+        <v>-0.06150428061274155</v>
+      </c>
+      <c r="W388" t="n">
+        <v>-0.06081385861633844</v>
+      </c>
+      <c r="X388" t="n">
+        <v>-0.04957777896489165</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>427</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>24.26229508196721</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>45.85987261146497</v>
+      </c>
+      <c r="F389" t="n">
+        <v>43.29861111111111</v>
+      </c>
+      <c r="G389" t="n">
+        <v>42.5287652689593</v>
+      </c>
+      <c r="H389" t="n">
+        <v>54.14012738853503</v>
+      </c>
+      <c r="I389" t="n">
+        <v>-8.280254777070056</v>
+      </c>
+      <c r="J389" t="n">
+        <v>-0.012454997027709</v>
+      </c>
+      <c r="K389" t="n">
+        <v>0.04622422965384445</v>
+      </c>
+      <c r="L389" t="n">
+        <v>0.009713089298930508</v>
+      </c>
+      <c r="M389" t="n">
+        <v>4.919866127786094</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.03133672692857385</v>
+      </c>
+      <c r="O389" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>0</v>
+      </c>
+      <c r="R389" t="n">
+        <v>0</v>
+      </c>
+      <c r="S389" t="b">
+        <v>1</v>
+      </c>
+      <c r="T389" t="inlineStr"/>
+      <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr"/>
+      <c r="W389" t="inlineStr"/>
+      <c r="X389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>428</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>15.78947368421053</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>50.52631578947368</v>
+      </c>
+      <c r="F390" t="n">
+        <v>50.3527318228664</v>
+      </c>
+      <c r="G390" t="n">
+        <v>49.73925372996257</v>
+      </c>
+      <c r="H390" t="n">
+        <v>56.09022556390978</v>
+      </c>
+      <c r="I390" t="n">
+        <v>-5.563909774436091</v>
+      </c>
+      <c r="J390" t="n">
+        <v>-0.4601883273554469</v>
+      </c>
+      <c r="K390" t="n">
+        <v>-0.2869911216372111</v>
+      </c>
+      <c r="L390" t="n">
+        <v>-0.01802272595907112</v>
+      </c>
+      <c r="M390" t="n">
+        <v>286.9476553901872</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.4315002336694544</v>
+      </c>
+      <c r="O390" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>15</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0</v>
+      </c>
+      <c r="S390" t="b">
+        <v>0</v>
+      </c>
+      <c r="T390" t="n">
+        <v>0.08615673288559407</v>
+      </c>
+      <c r="U390" t="n">
+        <v>-0.02724576940473247</v>
+      </c>
+      <c r="V390" t="n">
+        <v>-0.1695037936955789</v>
+      </c>
+      <c r="W390" t="n">
+        <v>-0.1058346506493202</v>
+      </c>
+      <c r="X390" t="n">
+        <v>-0.03325037485291986</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>429</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>22.54742547425474</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>50</v>
+      </c>
+      <c r="F391" t="n">
+        <v>46.94288035673797</v>
+      </c>
+      <c r="G391" t="n">
+        <v>45.12345679012346</v>
+      </c>
+      <c r="H391" t="n">
+        <v>49.67948717948718</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0.3205128205128176</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1.608364247683801</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-0.0570522789456902</v>
+      </c>
+      <c r="L391" t="n">
+        <v>-0.4708438599509694</v>
+      </c>
+      <c r="M391" t="n">
+        <v>4085.527160168788</v>
+      </c>
+      <c r="N391" t="n">
+        <v>13.09463833387432</v>
+      </c>
+      <c r="O391" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q391" t="n">
+        <v>20</v>
+      </c>
+      <c r="R391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S391" t="b">
+        <v>1</v>
+      </c>
+      <c r="T391" t="n">
+        <v>0.3144507240988781</v>
+      </c>
+      <c r="U391" t="n">
+        <v>0.6397100580547863</v>
+      </c>
+      <c r="V391" t="n">
+        <v>8.296551774786776</v>
+      </c>
+      <c r="W391" t="inlineStr"/>
+      <c r="X391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>430</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>13.03252885624344</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>50.33738191632929</v>
+      </c>
+      <c r="F392" t="n">
+        <v>50.302381148554</v>
+      </c>
+      <c r="G392" t="n">
+        <v>48.92010644822031</v>
+      </c>
+      <c r="H392" t="n">
+        <v>51.82186234817814</v>
+      </c>
+      <c r="I392" t="n">
+        <v>-1.484480431848851</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1.574551877629087</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0.5903813680181194</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1.134054047671601</v>
+      </c>
+      <c r="M392" t="n">
+        <v>8259.525462158526</v>
+      </c>
+      <c r="N392" t="n">
+        <v>11.14645811357426</v>
+      </c>
+      <c r="O392" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q392" t="n">
+        <v>25</v>
+      </c>
+      <c r="R392" t="n">
+        <v>0</v>
+      </c>
+      <c r="S392" t="b">
+        <v>0</v>
+      </c>
+      <c r="T392" t="n">
+        <v>0.3826995291504603</v>
+      </c>
+      <c r="U392" t="n">
+        <v>0.5801704440068703</v>
+      </c>
+      <c r="V392" t="n">
+        <v>0.06837572275937494</v>
+      </c>
+      <c r="W392" t="n">
+        <v>4.604073451028288</v>
+      </c>
+      <c r="X392" t="n">
+        <v>5.74345958456394</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>431</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>17.33333333333333</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>45.54655870445345</v>
+      </c>
+      <c r="F393" t="n">
+        <v>44.39728276761814</v>
+      </c>
+      <c r="G393" t="n">
+        <v>41.99640598264629</v>
+      </c>
+      <c r="H393" t="n">
+        <v>48.98785425101214</v>
+      </c>
+      <c r="I393" t="n">
+        <v>-3.441295546558699</v>
+      </c>
+      <c r="J393" t="n">
+        <v>-0.4456688170111249</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0.1955179255609124</v>
+      </c>
+      <c r="L393" t="n">
+        <v>0.1845238290209814</v>
+      </c>
+      <c r="M393" t="n">
+        <v>58.33090486238387</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.1180787547821536</v>
+      </c>
+      <c r="O393" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q393" t="n">
+        <v>10</v>
+      </c>
+      <c r="R393" t="n">
+        <v>0</v>
+      </c>
+      <c r="S393" t="b">
+        <v>0</v>
+      </c>
+      <c r="T393" t="n">
+        <v>0.3454039734020211</v>
+      </c>
+      <c r="U393" t="n">
+        <v>0.4624946680559252</v>
+      </c>
+      <c r="V393" t="n">
+        <v>0.230394729936468</v>
+      </c>
+      <c r="W393" t="n">
+        <v>0.1465647245059996</v>
+      </c>
+      <c r="X393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>432</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>15.37806176783813</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>46.96132596685083</v>
+      </c>
+      <c r="F394" t="n">
+        <v>45.47456238161129</v>
+      </c>
+      <c r="G394" t="n">
+        <v>43.89913111001435</v>
+      </c>
+      <c r="H394" t="n">
+        <v>49.4475138121547</v>
+      </c>
+      <c r="I394" t="n">
+        <v>-2.486187845303867</v>
+      </c>
+      <c r="J394" t="n">
+        <v>4.877853882456223</v>
+      </c>
+      <c r="K394" t="n">
+        <v>1.482207703584288</v>
+      </c>
+      <c r="L394" t="n">
+        <v>3.01424191228433</v>
+      </c>
+      <c r="M394" t="n">
+        <v>475.5044609722058</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0.6567741173649252</v>
+      </c>
+      <c r="O394" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q394" t="n">
+        <v>15</v>
+      </c>
+      <c r="R394" t="n">
+        <v>0</v>
+      </c>
+      <c r="S394" t="b">
+        <v>0</v>
+      </c>
+      <c r="T394" t="n">
+        <v>1.268210205298238</v>
+      </c>
+      <c r="U394" t="n">
+        <v>1.02790712603302</v>
+      </c>
+      <c r="V394" t="n">
+        <v>0.4279256334058635</v>
+      </c>
+      <c r="W394" t="n">
+        <v>0.3650118241241128</v>
+      </c>
+      <c r="X394" t="n">
+        <v>0.4197588758493696</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>433</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>21.06382978723404</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>52.77777777777778</v>
+      </c>
+      <c r="F395" t="n">
+        <v>45.60551163812034</v>
+      </c>
+      <c r="G395" t="n">
+        <v>42.30019493177388</v>
+      </c>
+      <c r="H395" t="n">
+        <v>51.38888888888889</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1.388888888888893</v>
+      </c>
+      <c r="J395" t="n">
+        <v>3.240727351186882</v>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="n">
+        <v>206.5651539856946</v>
+      </c>
+      <c r="N395" t="n">
+        <v>2.868960472023536</v>
+      </c>
+      <c r="O395" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q395" t="n">
+        <v>40</v>
+      </c>
+      <c r="R395" t="n">
+        <v>0</v>
+      </c>
+      <c r="S395" t="b">
+        <v>0</v>
+      </c>
+      <c r="T395" t="inlineStr"/>
+      <c r="U395" t="inlineStr"/>
+      <c r="V395" t="inlineStr"/>
+      <c r="W395" t="inlineStr"/>
+      <c r="X395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>434</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>17.33333333333333</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>40.51282051282051</v>
+      </c>
+      <c r="F396" t="n">
+        <v>39.38140536071664</v>
+      </c>
+      <c r="G396" t="n">
+        <v>35.55575777798</v>
+      </c>
+      <c r="H396" t="n">
+        <v>51.28205128205128</v>
+      </c>
+      <c r="I396" t="n">
+        <v>-10.76923076923077</v>
+      </c>
+      <c r="J396" t="n">
+        <v>-0.05075899113765758</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-0.050208130750989</v>
+      </c>
+      <c r="L396" t="n">
+        <v>-0.06801408643150533</v>
+      </c>
+      <c r="M396" t="n">
+        <v>-8.029832875402178</v>
+      </c>
+      <c r="N396" t="n">
+        <v>-0.04117863013026758</v>
+      </c>
+      <c r="O396" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q396" t="n">
+        <v>0</v>
+      </c>
+      <c r="R396" t="n">
+        <v>0</v>
+      </c>
+      <c r="S396" t="b">
+        <v>1</v>
+      </c>
+      <c r="T396" t="inlineStr"/>
+      <c r="U396" t="inlineStr"/>
+      <c r="V396" t="inlineStr"/>
+      <c r="W396" t="inlineStr"/>
+      <c r="X396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>435</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>14.77707006369427</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>44.62809917355372</v>
+      </c>
+      <c r="F397" t="n">
+        <v>44.06920992286847</v>
+      </c>
+      <c r="G397" t="n">
+        <v>39.82106198486381</v>
+      </c>
+      <c r="H397" t="n">
+        <v>44.62809917355372</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0.5169605755523184</v>
+      </c>
+      <c r="K397" t="n">
+        <v>-0.05978748593355874</v>
+      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="n">
+        <v>203.9027470479169</v>
+      </c>
+      <c r="N397" t="n">
+        <v>1.685146669817495</v>
+      </c>
+      <c r="O397" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q397" t="n">
+        <v>20</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0</v>
+      </c>
+      <c r="S397" t="b">
+        <v>1</v>
+      </c>
+      <c r="T397" t="inlineStr"/>
+      <c r="U397" t="inlineStr"/>
+      <c r="V397" t="inlineStr"/>
+      <c r="W397" t="inlineStr"/>
+      <c r="X397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>436</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>17.98387096774193</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>45.64102564102564</v>
+      </c>
+      <c r="F398" t="n">
+        <v>42.33149148403385</v>
+      </c>
+      <c r="G398" t="n">
+        <v>39.960407239819</v>
+      </c>
+      <c r="H398" t="n">
+        <v>48.71794871794872</v>
+      </c>
+      <c r="I398" t="n">
+        <v>-3.076923076923073</v>
+      </c>
+      <c r="J398" t="n">
+        <v>1.048296324569929</v>
+      </c>
+      <c r="K398" t="n">
+        <v>-0.04249969245883605</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0.09246485978423286</v>
+      </c>
+      <c r="M398" t="n">
+        <v>17.12505932532471</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0.08782081705294725</v>
+      </c>
+      <c r="O398" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q398" t="n">
+        <v>10</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0</v>
+      </c>
+      <c r="S398" t="b">
+        <v>1</v>
+      </c>
+      <c r="T398" t="inlineStr"/>
+      <c r="U398" t="inlineStr"/>
+      <c r="V398" t="inlineStr"/>
+      <c r="W398" t="inlineStr"/>
+      <c r="X398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>437</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>19.64285714285715</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>47.56756756756757</v>
+      </c>
+      <c r="F399" t="n">
+        <v>46.28284744983038</v>
+      </c>
+      <c r="G399" t="n">
+        <v>45.2992018831145</v>
+      </c>
+      <c r="H399" t="n">
+        <v>46.48648648648649</v>
+      </c>
+      <c r="I399" t="n">
+        <v>1.081081081081081</v>
+      </c>
+      <c r="J399" t="n">
+        <v>1.11927667592024</v>
+      </c>
+      <c r="K399" t="n">
+        <v>5.176242106930672</v>
+      </c>
+      <c r="L399" t="n">
+        <v>5.627107488495967</v>
+      </c>
+      <c r="M399" t="n">
+        <v>476.9739346798401</v>
+      </c>
+      <c r="N399" t="n">
+        <v>2.578237484755892</v>
+      </c>
+      <c r="O399" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q399" t="n">
+        <v>30</v>
+      </c>
+      <c r="R399" t="n">
+        <v>0</v>
+      </c>
+      <c r="S399" t="b">
+        <v>0</v>
+      </c>
+      <c r="T399" t="inlineStr"/>
+      <c r="U399" t="inlineStr"/>
+      <c r="V399" t="inlineStr"/>
+      <c r="W399" t="inlineStr"/>
+      <c r="X399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>438</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>13.40136054421769</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>50.88495575221239</v>
+      </c>
+      <c r="F400" t="n">
+        <v>50.16463575840604</v>
+      </c>
+      <c r="G400" t="n">
+        <v>48.98697576544097</v>
+      </c>
+      <c r="H400" t="n">
+        <v>51.32743362831859</v>
+      </c>
+      <c r="I400" t="n">
+        <v>-0.4424778761061958</v>
+      </c>
+      <c r="J400" t="n">
+        <v>14.72682271388523</v>
+      </c>
+      <c r="K400" t="n">
+        <v>23.25265562295684</v>
+      </c>
+      <c r="L400" t="n">
+        <v>3.211409042492065</v>
+      </c>
+      <c r="M400" t="n">
+        <v>1429.902479103064</v>
+      </c>
+      <c r="N400" t="n">
+        <v>6.327002119925064</v>
+      </c>
+      <c r="O400" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q400" t="n">
+        <v>40</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0</v>
+      </c>
+      <c r="S400" t="b">
+        <v>0</v>
+      </c>
+      <c r="T400" t="n">
+        <v>4.385772307422949</v>
+      </c>
+      <c r="U400" t="inlineStr"/>
+      <c r="V400" t="inlineStr"/>
+      <c r="W400" t="inlineStr"/>
+      <c r="X400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>439</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>20.32921810699589</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>45.78947368421053</v>
+      </c>
+      <c r="F401" t="n">
+        <v>43.04397815464214</v>
+      </c>
+      <c r="G401" t="n">
+        <v>42.08084701120519</v>
+      </c>
+      <c r="H401" t="n">
+        <v>43.68421052631579</v>
+      </c>
+      <c r="I401" t="n">
+        <v>2.105263157894733</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0.5338626863696981</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-0.5200940701757066</v>
+      </c>
+      <c r="L401" t="n">
+        <v>1.889260714194906</v>
+      </c>
+      <c r="M401" t="n">
+        <v>488.3332981371727</v>
+      </c>
+      <c r="N401" t="n">
+        <v>2.570175253353541</v>
+      </c>
+      <c r="O401" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q401" t="n">
+        <v>20</v>
+      </c>
+      <c r="R401" t="n">
+        <v>0</v>
+      </c>
+      <c r="S401" t="b">
+        <v>1</v>
+      </c>
+      <c r="T401" t="inlineStr"/>
+      <c r="U401" t="inlineStr"/>
+      <c r="V401" t="inlineStr"/>
+      <c r="W401" t="inlineStr"/>
+      <c r="X401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>440</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>18.00687285223368</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>46.46017699115044</v>
+      </c>
+      <c r="F402" t="n">
+        <v>42.86833881769709</v>
+      </c>
+      <c r="G402" t="n">
+        <v>39.96296296296296</v>
+      </c>
+      <c r="H402" t="n">
+        <v>49.11504424778761</v>
+      </c>
+      <c r="I402" t="n">
+        <v>-2.654867256637168</v>
+      </c>
+      <c r="J402" t="n">
+        <v>-0.3356375840597196</v>
+      </c>
+      <c r="K402" t="n">
+        <v>-0.2158179699657249</v>
+      </c>
+      <c r="L402" t="n">
+        <v>-0.04036075824587935</v>
+      </c>
+      <c r="M402" t="n">
+        <v>24.96362107145241</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0.1104585003161611</v>
+      </c>
+      <c r="O402" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q402" t="n">
+        <v>5</v>
+      </c>
+      <c r="R402" t="n">
+        <v>0</v>
+      </c>
+      <c r="S402" t="b">
+        <v>0</v>
+      </c>
+      <c r="T402" t="n">
+        <v>0.04606612237358597</v>
+      </c>
+      <c r="U402" t="inlineStr"/>
+      <c r="V402" t="inlineStr"/>
+      <c r="W402" t="inlineStr"/>
+      <c r="X402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>441</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>17.01149425287356</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>32.3943661971831</v>
+      </c>
+      <c r="F403" t="n">
+        <v>34.09645909645909</v>
+      </c>
+      <c r="G403" t="n">
+        <v>30.57098229781326</v>
+      </c>
+      <c r="H403" t="n">
+        <v>43.66197183098591</v>
+      </c>
+      <c r="I403" t="n">
+        <v>-11.26760563380281</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0.03946700354447216</v>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="n">
+        <v>-4.679006249885319</v>
+      </c>
+      <c r="N403" t="n">
+        <v>-0.06590149647725801</v>
+      </c>
+      <c r="O403" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>0</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0</v>
+      </c>
+      <c r="S403" t="b">
+        <v>1</v>
+      </c>
+      <c r="T403" t="inlineStr"/>
+      <c r="U403" t="inlineStr"/>
+      <c r="V403" t="inlineStr"/>
+      <c r="W403" t="inlineStr"/>
+      <c r="X403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>442</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>21.14503816793893</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>42.05128205128205</v>
+      </c>
+      <c r="F404" t="n">
+        <v>42.35836855577089</v>
+      </c>
+      <c r="G404" t="n">
+        <v>39.33193027899196</v>
+      </c>
+      <c r="H404" t="n">
+        <v>52.30769230769231</v>
+      </c>
+      <c r="I404" t="n">
+        <v>-10.25641025641026</v>
+      </c>
+      <c r="J404" t="n">
+        <v>-0.08988756292801242</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0.01288936771392883</v>
+      </c>
+      <c r="L404" t="n">
+        <v>0.006825304146737589</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0.006157503674174336</v>
+      </c>
+      <c r="N404" t="n">
+        <v>3.157694191884275e-05</v>
+      </c>
+      <c r="O404" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0</v>
+      </c>
+      <c r="S404" t="b">
+        <v>1</v>
+      </c>
+      <c r="T404" t="inlineStr"/>
+      <c r="U404" t="inlineStr"/>
+      <c r="V404" t="inlineStr"/>
+      <c r="W404" t="inlineStr"/>
+      <c r="X404" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p4_modeling/2024-10-15/df_iteration_test.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_iteration_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X404"/>
+  <dimension ref="A1:X528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30096,6 +30096,9198 @@
       <c r="W404" t="inlineStr"/>
       <c r="X404" t="inlineStr"/>
     </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>443</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>21.91489361702127</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>39.43661971830986</v>
+      </c>
+      <c r="F405" t="n">
+        <v>37.49712445364619</v>
+      </c>
+      <c r="G405" t="n">
+        <v>34.03459119496855</v>
+      </c>
+      <c r="H405" t="n">
+        <v>38.0281690140845</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1.408450704225352</v>
+      </c>
+      <c r="J405" t="n">
+        <v>-0.1191490900070636</v>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="n">
+        <v>16.61169680806501</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0.2339675606769719</v>
+      </c>
+      <c r="O405" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>15</v>
+      </c>
+      <c r="R405" t="n">
+        <v>0</v>
+      </c>
+      <c r="S405" t="b">
+        <v>0</v>
+      </c>
+      <c r="T405" t="inlineStr"/>
+      <c r="U405" t="inlineStr"/>
+      <c r="V405" t="inlineStr"/>
+      <c r="W405" t="inlineStr"/>
+      <c r="X405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>444</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>19.16030534351145</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>43.07692307692308</v>
+      </c>
+      <c r="F406" t="n">
+        <v>44.39067430579369</v>
+      </c>
+      <c r="G406" t="n">
+        <v>37.62221741603184</v>
+      </c>
+      <c r="H406" t="n">
+        <v>52.30769230769231</v>
+      </c>
+      <c r="I406" t="n">
+        <v>-9.230769230769234</v>
+      </c>
+      <c r="J406" t="n">
+        <v>-0.5110317319783511</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0.5156061743532723</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0.4824615004594218</v>
+      </c>
+      <c r="M406" t="n">
+        <v>24.95867444201927</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0.1279932022667655</v>
+      </c>
+      <c r="O406" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>10</v>
+      </c>
+      <c r="R406" t="n">
+        <v>0</v>
+      </c>
+      <c r="S406" t="b">
+        <v>0</v>
+      </c>
+      <c r="T406" t="inlineStr"/>
+      <c r="U406" t="inlineStr"/>
+      <c r="V406" t="inlineStr"/>
+      <c r="W406" t="inlineStr"/>
+      <c r="X406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>445</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>20</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>44.80874316939891</v>
+      </c>
+      <c r="F407" t="n">
+        <v>42.83663508469711</v>
+      </c>
+      <c r="G407" t="n">
+        <v>41.47009902735094</v>
+      </c>
+      <c r="H407" t="n">
+        <v>54.09836065573771</v>
+      </c>
+      <c r="I407" t="n">
+        <v>-9.289617486338798</v>
+      </c>
+      <c r="J407" t="n">
+        <v>-0.1106085616689185</v>
+      </c>
+      <c r="K407" t="n">
+        <v>-0.08294966142606895</v>
+      </c>
+      <c r="L407" t="n">
+        <v>-0.03049986783688913</v>
+      </c>
+      <c r="M407" t="n">
+        <v>-9.074064951292627</v>
+      </c>
+      <c r="N407" t="n">
+        <v>-0.04958505437864823</v>
+      </c>
+      <c r="O407" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>0</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0</v>
+      </c>
+      <c r="S407" t="b">
+        <v>1</v>
+      </c>
+      <c r="T407" t="inlineStr"/>
+      <c r="U407" t="inlineStr"/>
+      <c r="V407" t="inlineStr"/>
+      <c r="W407" t="inlineStr"/>
+      <c r="X407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>446</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>20</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>51.28205128205128</v>
+      </c>
+      <c r="F408" t="n">
+        <v>47.68808489485401</v>
+      </c>
+      <c r="G408" t="n">
+        <v>47.53912753912754</v>
+      </c>
+      <c r="H408" t="n">
+        <v>56.41025641025641</v>
+      </c>
+      <c r="I408" t="n">
+        <v>-5.128205128205131</v>
+      </c>
+      <c r="J408" t="n">
+        <v>-1.046131609686755</v>
+      </c>
+      <c r="K408" t="n">
+        <v>-0.6892416277019432</v>
+      </c>
+      <c r="L408" t="n">
+        <v>0.5698682953955108</v>
+      </c>
+      <c r="M408" t="n">
+        <v>384.4328594496709</v>
+      </c>
+      <c r="N408" t="n">
+        <v>1.971450561280364</v>
+      </c>
+      <c r="O408" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>25</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
+      <c r="S408" t="b">
+        <v>0</v>
+      </c>
+      <c r="T408" t="inlineStr"/>
+      <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr"/>
+      <c r="W408" t="inlineStr"/>
+      <c r="X408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>447</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>19.34156378600823</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>51.06382978723404</v>
+      </c>
+      <c r="F409" t="n">
+        <v>47.79954345171735</v>
+      </c>
+      <c r="G409" t="n">
+        <v>45.63277563277563</v>
+      </c>
+      <c r="H409" t="n">
+        <v>55.85106382978723</v>
+      </c>
+      <c r="I409" t="n">
+        <v>-4.787234042553187</v>
+      </c>
+      <c r="J409" t="n">
+        <v>-0.4781799226277778</v>
+      </c>
+      <c r="K409" t="n">
+        <v>-0.3706037675448633</v>
+      </c>
+      <c r="L409" t="n">
+        <v>1.392737271186934</v>
+      </c>
+      <c r="M409" t="n">
+        <v>308.8126622564623</v>
+      </c>
+      <c r="N409" t="n">
+        <v>1.642620543917353</v>
+      </c>
+      <c r="O409" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>25</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0</v>
+      </c>
+      <c r="S409" t="b">
+        <v>0</v>
+      </c>
+      <c r="T409" t="inlineStr"/>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr"/>
+      <c r="W409" t="inlineStr"/>
+      <c r="X409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>448</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>16.01476014760147</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>45</v>
+      </c>
+      <c r="F410" t="n">
+        <v>46.73202614379085</v>
+      </c>
+      <c r="G410" t="n">
+        <v>43.90220299160211</v>
+      </c>
+      <c r="H410" t="n">
+        <v>53</v>
+      </c>
+      <c r="I410" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0.2503217207707257</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0.07968426296014015</v>
+      </c>
+      <c r="L410" t="n">
+        <v>0.1369726949716383</v>
+      </c>
+      <c r="M410" t="n">
+        <v>10.5767666969306</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0.05288383348465302</v>
+      </c>
+      <c r="O410" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>5</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0</v>
+      </c>
+      <c r="S410" t="b">
+        <v>0</v>
+      </c>
+      <c r="T410" t="n">
+        <v>0.05288383348465302</v>
+      </c>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>450</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>19.140625</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>39.89637305699482</v>
+      </c>
+      <c r="F411" t="n">
+        <v>39.49938949938951</v>
+      </c>
+      <c r="G411" t="n">
+        <v>35.88406276716032</v>
+      </c>
+      <c r="H411" t="n">
+        <v>49.74093264248705</v>
+      </c>
+      <c r="I411" t="n">
+        <v>-9.844559585492227</v>
+      </c>
+      <c r="J411" t="n">
+        <v>-0.01099566533208417</v>
+      </c>
+      <c r="K411" t="n">
+        <v>-0.08531661165033455</v>
+      </c>
+      <c r="L411" t="n">
+        <v>-0.0443074378196826</v>
+      </c>
+      <c r="M411" t="n">
+        <v>-10.5418312876149</v>
+      </c>
+      <c r="N411" t="n">
+        <v>-0.05462088750059532</v>
+      </c>
+      <c r="O411" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>0</v>
+      </c>
+      <c r="R411" t="n">
+        <v>0</v>
+      </c>
+      <c r="S411" t="b">
+        <v>1</v>
+      </c>
+      <c r="T411" t="inlineStr"/>
+      <c r="U411" t="inlineStr"/>
+      <c r="V411" t="inlineStr"/>
+      <c r="W411" t="inlineStr"/>
+      <c r="X411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>451</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>26.15384615384615</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="F412" t="n">
+        <v>44.63684463684464</v>
+      </c>
+      <c r="G412" t="n">
+        <v>43.85022496758941</v>
+      </c>
+      <c r="H412" t="n">
+        <v>49.16666666666666</v>
+      </c>
+      <c r="I412" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J412" t="n">
+        <v>29.00612097007354</v>
+      </c>
+      <c r="K412" t="n">
+        <v>7.672454374129018</v>
+      </c>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="n">
+        <v>224.2301685574237</v>
+      </c>
+      <c r="N412" t="n">
+        <v>1.868584737978531</v>
+      </c>
+      <c r="O412" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>30</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="b">
+        <v>0</v>
+      </c>
+      <c r="T412" t="inlineStr"/>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="inlineStr"/>
+      <c r="W412" t="inlineStr"/>
+      <c r="X412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>452</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>18.81481481481482</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>48</v>
+      </c>
+      <c r="F413" t="n">
+        <v>45.80409356725146</v>
+      </c>
+      <c r="G413" t="n">
+        <v>43.21054859977016</v>
+      </c>
+      <c r="H413" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I413" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0.9568583762398351</v>
+      </c>
+      <c r="K413" t="n">
+        <v>0.4572878435635346</v>
+      </c>
+      <c r="L413" t="n">
+        <v>3.550606598246087</v>
+      </c>
+      <c r="M413" t="n">
+        <v>301.7027484879591</v>
+      </c>
+      <c r="N413" t="n">
+        <v>1.508513742439796</v>
+      </c>
+      <c r="O413" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>15</v>
+      </c>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
+      <c r="S413" t="b">
+        <v>0</v>
+      </c>
+      <c r="T413" t="n">
+        <v>1.508513742439796</v>
+      </c>
+      <c r="U413" t="inlineStr"/>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" t="inlineStr"/>
+      <c r="X413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>453</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>18.81856540084388</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>42.4731182795699</v>
+      </c>
+      <c r="F414" t="n">
+        <v>45.78167641325535</v>
+      </c>
+      <c r="G414" t="n">
+        <v>40.98736274874484</v>
+      </c>
+      <c r="H414" t="n">
+        <v>47.8494623655914</v>
+      </c>
+      <c r="I414" t="n">
+        <v>-5.376344086021504</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0.4920501270072811</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0.1183359475976535</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0.1212342697654886</v>
+      </c>
+      <c r="M414" t="n">
+        <v>8.034154645493231</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0.04319437981447974</v>
+      </c>
+      <c r="O414" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>5</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="b">
+        <v>0</v>
+      </c>
+      <c r="T414" t="inlineStr"/>
+      <c r="U414" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" t="inlineStr"/>
+      <c r="X414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>454</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>17.77777777777778</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F415" t="n">
+        <v>42.37228774542207</v>
+      </c>
+      <c r="G415" t="n">
+        <v>40.0685588920883</v>
+      </c>
+      <c r="H415" t="n">
+        <v>44</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0.1090156137757745</v>
+      </c>
+      <c r="K415" t="n">
+        <v>-0.08177055084457394</v>
+      </c>
+      <c r="L415" t="n">
+        <v>0.2629324375621794</v>
+      </c>
+      <c r="M415" t="n">
+        <v>84.64342499472514</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0.4232171249736257</v>
+      </c>
+      <c r="O415" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>10</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0</v>
+      </c>
+      <c r="S415" t="b">
+        <v>1</v>
+      </c>
+      <c r="T415" t="n">
+        <v>0.4232171249736257</v>
+      </c>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" t="inlineStr"/>
+      <c r="X415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>455</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>22.08333333333334</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>51.57894736842105</v>
+      </c>
+      <c r="F416" t="n">
+        <v>49.82702482702483</v>
+      </c>
+      <c r="G416" t="n">
+        <v>49.20496170496171</v>
+      </c>
+      <c r="H416" t="n">
+        <v>50.52631578947368</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1.05263157894737</v>
+      </c>
+      <c r="J416" t="n">
+        <v>-1.406086531867083</v>
+      </c>
+      <c r="K416" t="n">
+        <v>1.790882152567897</v>
+      </c>
+      <c r="L416" t="n">
+        <v>3.704283230473106</v>
+      </c>
+      <c r="M416" t="n">
+        <v>527.6268697343163</v>
+      </c>
+      <c r="N416" t="n">
+        <v>2.776983524917454</v>
+      </c>
+      <c r="O416" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>40</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="b">
+        <v>0</v>
+      </c>
+      <c r="T416" t="inlineStr"/>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" t="inlineStr"/>
+      <c r="X416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>456</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>18.17518248175183</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>49.01960784313725</v>
+      </c>
+      <c r="F417" t="n">
+        <v>49.99345488546049</v>
+      </c>
+      <c r="G417" t="n">
+        <v>47.14084975508404</v>
+      </c>
+      <c r="H417" t="n">
+        <v>47.54901960784314</v>
+      </c>
+      <c r="I417" t="n">
+        <v>1.470588235294116</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0.7859446657665023</v>
+      </c>
+      <c r="K417" t="n">
+        <v>1.502935067910206</v>
+      </c>
+      <c r="L417" t="n">
+        <v>2.089239880143179</v>
+      </c>
+      <c r="M417" t="n">
+        <v>75.54103476556952</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0.3702991900273016</v>
+      </c>
+      <c r="O417" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>20</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" t="b">
+        <v>0</v>
+      </c>
+      <c r="T417" t="n">
+        <v>0.6160367349521734</v>
+      </c>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr"/>
+      <c r="W417" t="inlineStr"/>
+      <c r="X417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>457</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>16.96969696969697</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>39.79591836734694</v>
+      </c>
+      <c r="F418" t="n">
+        <v>40.45751633986929</v>
+      </c>
+      <c r="G418" t="n">
+        <v>36.89753698341813</v>
+      </c>
+      <c r="H418" t="n">
+        <v>45.91836734693878</v>
+      </c>
+      <c r="I418" t="n">
+        <v>-6.122448979591844</v>
+      </c>
+      <c r="J418" t="n">
+        <v>-0.1237228136314238</v>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="n">
+        <v>0.4890708839667041</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0.005041967875945404</v>
+      </c>
+      <c r="O418" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="b">
+        <v>1</v>
+      </c>
+      <c r="T418" t="inlineStr"/>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr"/>
+      <c r="W418" t="inlineStr"/>
+      <c r="X418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>458</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>15.75903614457831</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>40.06211180124223</v>
+      </c>
+      <c r="F419" t="n">
+        <v>40.67667112070443</v>
+      </c>
+      <c r="G419" t="n">
+        <v>32.15031277508483</v>
+      </c>
+      <c r="H419" t="n">
+        <v>51.24223602484472</v>
+      </c>
+      <c r="I419" t="n">
+        <v>-11.18012422360249</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0.0689370916480712</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0.004304900407269372</v>
+      </c>
+      <c r="L419" t="n">
+        <v>-0.02435547611957276</v>
+      </c>
+      <c r="M419" t="n">
+        <v>-2.955411981099317</v>
+      </c>
+      <c r="N419" t="n">
+        <v>-0.009178298077948189</v>
+      </c>
+      <c r="O419" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>0</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0</v>
+      </c>
+      <c r="S419" t="b">
+        <v>1</v>
+      </c>
+      <c r="T419" t="n">
+        <v>0.01150843844714494</v>
+      </c>
+      <c r="U419" t="n">
+        <v>-0.005958776210768122</v>
+      </c>
+      <c r="V419" t="n">
+        <v>-0.006314308993175596</v>
+      </c>
+      <c r="W419" t="inlineStr"/>
+      <c r="X419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>459</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>15.58685446009389</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>38.50931677018634</v>
+      </c>
+      <c r="F420" t="n">
+        <v>39.95347564313082</v>
+      </c>
+      <c r="G420" t="n">
+        <v>37.06797829133148</v>
+      </c>
+      <c r="H420" t="n">
+        <v>52.79503105590062</v>
+      </c>
+      <c r="I420" t="n">
+        <v>-14.28571428571428</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0.03254076981510565</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0.01009922055983296</v>
+      </c>
+      <c r="L420" t="n">
+        <v>-0.03362056922366473</v>
+      </c>
+      <c r="M420" t="n">
+        <v>-7.388705604174079</v>
+      </c>
+      <c r="N420" t="n">
+        <v>-0.04617941002608799</v>
+      </c>
+      <c r="O420" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>0</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0</v>
+      </c>
+      <c r="S420" t="b">
+        <v>1</v>
+      </c>
+      <c r="T420" t="inlineStr"/>
+      <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr"/>
+      <c r="W420" t="inlineStr"/>
+      <c r="X420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>460</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>18.41628959276018</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>45.89235127478754</v>
+      </c>
+      <c r="F421" t="n">
+        <v>45.51042338276381</v>
+      </c>
+      <c r="G421" t="n">
+        <v>42.0272253897619</v>
+      </c>
+      <c r="H421" t="n">
+        <v>49.85835694050991</v>
+      </c>
+      <c r="I421" t="n">
+        <v>-3.966005665722378</v>
+      </c>
+      <c r="J421" t="n">
+        <v>-1.070283162260721</v>
+      </c>
+      <c r="K421" t="n">
+        <v>-0.4577589082694628</v>
+      </c>
+      <c r="L421" t="n">
+        <v>-0.4483277581689288</v>
+      </c>
+      <c r="M421" t="n">
+        <v>350.4912515504215</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0.9928930638822138</v>
+      </c>
+      <c r="O421" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>15</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="b">
+        <v>0</v>
+      </c>
+      <c r="T421" t="n">
+        <v>-0.04002824888362305</v>
+      </c>
+      <c r="U421" t="n">
+        <v>-0.01176945356622599</v>
+      </c>
+      <c r="V421" t="n">
+        <v>1.027897594706094</v>
+      </c>
+      <c r="W421" t="inlineStr"/>
+      <c r="X421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>461</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>17.28937728937729</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>41.95121951219512</v>
+      </c>
+      <c r="F422" t="n">
+        <v>40.14828738512949</v>
+      </c>
+      <c r="G422" t="n">
+        <v>38.63468203197926</v>
+      </c>
+      <c r="H422" t="n">
+        <v>53.65853658536586</v>
+      </c>
+      <c r="I422" t="n">
+        <v>-11.70731707317074</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0.09885363927912551</v>
+      </c>
+      <c r="K422" t="n">
+        <v>-0.03494017313965145</v>
+      </c>
+      <c r="L422" t="n">
+        <v>0.01070358319780998</v>
+      </c>
+      <c r="M422" t="n">
+        <v>-3.505508553495162</v>
+      </c>
+      <c r="N422" t="n">
+        <v>-0.01710004172436664</v>
+      </c>
+      <c r="O422" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>0</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0</v>
+      </c>
+      <c r="S422" t="b">
+        <v>1</v>
+      </c>
+      <c r="T422" t="n">
+        <v>-0.01790653647670908</v>
+      </c>
+      <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr"/>
+      <c r="W422" t="inlineStr"/>
+      <c r="X422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>462</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>14.84444444444444</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>41.07648725212464</v>
+      </c>
+      <c r="F423" t="n">
+        <v>40.10562395151107</v>
+      </c>
+      <c r="G423" t="n">
+        <v>35.34360923717427</v>
+      </c>
+      <c r="H423" t="n">
+        <v>46.45892351274787</v>
+      </c>
+      <c r="I423" t="n">
+        <v>-5.38243626062323</v>
+      </c>
+      <c r="J423" t="n">
+        <v>0.09260957985100361</v>
+      </c>
+      <c r="K423" t="n">
+        <v>-0.1094803871879289</v>
+      </c>
+      <c r="L423" t="n">
+        <v>-0.04665753300589444</v>
+      </c>
+      <c r="M423" t="n">
+        <v>17.09976310402554</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0.048441255252197</v>
+      </c>
+      <c r="O423" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>5</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0</v>
+      </c>
+      <c r="S423" t="b">
+        <v>0</v>
+      </c>
+      <c r="T423" t="n">
+        <v>0.05431425857959475</v>
+      </c>
+      <c r="U423" t="n">
+        <v>0.06852159312868202</v>
+      </c>
+      <c r="V423" t="n">
+        <v>0.04531972676746718</v>
+      </c>
+      <c r="W423" t="inlineStr"/>
+      <c r="X423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>463</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>13.4010152284264</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>48.31804281345565</v>
+      </c>
+      <c r="F424" t="n">
+        <v>49.89658671124712</v>
+      </c>
+      <c r="G424" t="n">
+        <v>41.62859632718228</v>
+      </c>
+      <c r="H424" t="n">
+        <v>54.12844036697248</v>
+      </c>
+      <c r="I424" t="n">
+        <v>-5.810397553516822</v>
+      </c>
+      <c r="J424" t="n">
+        <v>3.741032164611197</v>
+      </c>
+      <c r="K424" t="n">
+        <v>0.859835954245103</v>
+      </c>
+      <c r="L424" t="n">
+        <v>-0.2633360183355876</v>
+      </c>
+      <c r="M424" t="n">
+        <v>294.8999173819738</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0.9018346097308065</v>
+      </c>
+      <c r="O424" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>20</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0</v>
+      </c>
+      <c r="S424" t="b">
+        <v>0</v>
+      </c>
+      <c r="T424" t="n">
+        <v>-0.2041045283877715</v>
+      </c>
+      <c r="U424" t="n">
+        <v>0.242730343133528</v>
+      </c>
+      <c r="V424" t="n">
+        <v>0.4841994021447372</v>
+      </c>
+      <c r="W424" t="inlineStr"/>
+      <c r="X424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>464</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>14.77366255144033</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>45.0261780104712</v>
+      </c>
+      <c r="F425" t="n">
+        <v>43.78427128427128</v>
+      </c>
+      <c r="G425" t="n">
+        <v>39.35253045558144</v>
+      </c>
+      <c r="H425" t="n">
+        <v>52.09424083769634</v>
+      </c>
+      <c r="I425" t="n">
+        <v>-7.068062827225141</v>
+      </c>
+      <c r="J425" t="n">
+        <v>-0.2467197088948728</v>
+      </c>
+      <c r="K425" t="n">
+        <v>0.5359993169898667</v>
+      </c>
+      <c r="L425" t="n">
+        <v>-0.04977390908065871</v>
+      </c>
+      <c r="M425" t="n">
+        <v>33.35244925746088</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0.08731007659021171</v>
+      </c>
+      <c r="O425" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q425" t="n">
+        <v>10</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0</v>
+      </c>
+      <c r="S425" t="b">
+        <v>0</v>
+      </c>
+      <c r="T425" t="n">
+        <v>-0.3437623278276247</v>
+      </c>
+      <c r="U425" t="n">
+        <v>-0.2582075853639929</v>
+      </c>
+      <c r="V425" t="n">
+        <v>-0.2126336546759992</v>
+      </c>
+      <c r="W425" t="inlineStr"/>
+      <c r="X425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>465</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>21.5748031496063</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>49.48453608247423</v>
+      </c>
+      <c r="F426" t="n">
+        <v>47.15927750410509</v>
+      </c>
+      <c r="G426" t="n">
+        <v>45.18792191205985</v>
+      </c>
+      <c r="H426" t="n">
+        <v>49.48453608247423</v>
+      </c>
+      <c r="I426" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" t="n">
+        <v>7.400297730881029</v>
+      </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="n">
+        <v>217.651063598805</v>
+      </c>
+      <c r="N426" t="n">
+        <v>2.243825397925824</v>
+      </c>
+      <c r="O426" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q426" t="n">
+        <v>20</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0</v>
+      </c>
+      <c r="S426" t="b">
+        <v>0</v>
+      </c>
+      <c r="T426" t="inlineStr"/>
+      <c r="U426" t="inlineStr"/>
+      <c r="V426" t="inlineStr"/>
+      <c r="W426" t="inlineStr"/>
+      <c r="X426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>466</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>15.24475524475524</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>42.46987951807229</v>
+      </c>
+      <c r="F427" t="n">
+        <v>42.85921325051761</v>
+      </c>
+      <c r="G427" t="n">
+        <v>34.45841895388978</v>
+      </c>
+      <c r="H427" t="n">
+        <v>50.90361445783132</v>
+      </c>
+      <c r="I427" t="n">
+        <v>-8.433734939759034</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0.05798604112408924</v>
+      </c>
+      <c r="K427" t="n">
+        <v>0.2340338453533029</v>
+      </c>
+      <c r="L427" t="n">
+        <v>-0.03945910386909834</v>
+      </c>
+      <c r="M427" t="n">
+        <v>25.39459235486875</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0.07648973600864081</v>
+      </c>
+      <c r="O427" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>10</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0</v>
+      </c>
+      <c r="S427" t="b">
+        <v>0</v>
+      </c>
+      <c r="T427" t="n">
+        <v>-0.07403450382390339</v>
+      </c>
+      <c r="U427" t="n">
+        <v>-0.1391624144768487</v>
+      </c>
+      <c r="V427" t="n">
+        <v>0.0584140519618371</v>
+      </c>
+      <c r="W427" t="inlineStr"/>
+      <c r="X427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>467</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>49.57264957264957</v>
+      </c>
+      <c r="F428" t="n">
+        <v>46.90022478040911</v>
+      </c>
+      <c r="G428" t="n">
+        <v>45.62004338703368</v>
+      </c>
+      <c r="H428" t="n">
+        <v>47.86324786324786</v>
+      </c>
+      <c r="I428" t="n">
+        <v>1.70940170940171</v>
+      </c>
+      <c r="J428" t="n">
+        <v>11.0360565187736</v>
+      </c>
+      <c r="K428" t="n">
+        <v>2.751732536935217</v>
+      </c>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="n">
+        <v>452.8776770155168</v>
+      </c>
+      <c r="N428" t="n">
+        <v>3.870749376200999</v>
+      </c>
+      <c r="O428" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>20</v>
+      </c>
+      <c r="R428" t="n">
+        <v>0</v>
+      </c>
+      <c r="S428" t="b">
+        <v>1</v>
+      </c>
+      <c r="T428" t="inlineStr"/>
+      <c r="U428" t="inlineStr"/>
+      <c r="V428" t="inlineStr"/>
+      <c r="W428" t="inlineStr"/>
+      <c r="X428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>468</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>17.58928571428571</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>39.37677053824363</v>
+      </c>
+      <c r="F429" t="n">
+        <v>38.38826854942891</v>
+      </c>
+      <c r="G429" t="n">
+        <v>33.78785189130016</v>
+      </c>
+      <c r="H429" t="n">
+        <v>48.44192634560906</v>
+      </c>
+      <c r="I429" t="n">
+        <v>-9.065155807365436</v>
+      </c>
+      <c r="J429" t="n">
+        <v>-0.1364852053293569</v>
+      </c>
+      <c r="K429" t="n">
+        <v>-0.1193199447030226</v>
+      </c>
+      <c r="L429" t="n">
+        <v>-0.0489282314341303</v>
+      </c>
+      <c r="M429" t="n">
+        <v>-6.030276631666439</v>
+      </c>
+      <c r="N429" t="n">
+        <v>-0.01718027530389299</v>
+      </c>
+      <c r="O429" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>0</v>
+      </c>
+      <c r="R429" t="n">
+        <v>0</v>
+      </c>
+      <c r="S429" t="b">
+        <v>1</v>
+      </c>
+      <c r="T429" t="n">
+        <v>-0.01583636921360423</v>
+      </c>
+      <c r="U429" t="n">
+        <v>-0.02594437174601433</v>
+      </c>
+      <c r="V429" t="n">
+        <v>-0.008647643819024324</v>
+      </c>
+      <c r="W429" t="inlineStr"/>
+      <c r="X429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>469</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>12.98969072164948</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>42.60089686098654</v>
+      </c>
+      <c r="F430" t="n">
+        <v>41.415996938385</v>
+      </c>
+      <c r="G430" t="n">
+        <v>38.5488482710705</v>
+      </c>
+      <c r="H430" t="n">
+        <v>52.91479820627802</v>
+      </c>
+      <c r="I430" t="n">
+        <v>-10.31390134529148</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0.1616532851299553</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0.11380579565491</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0.03240417636910441</v>
+      </c>
+      <c r="M430" t="n">
+        <v>-2.737950799619739</v>
+      </c>
+      <c r="N430" t="n">
+        <v>-0.0122778062763217</v>
+      </c>
+      <c r="O430" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>0</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0</v>
+      </c>
+      <c r="S430" t="b">
+        <v>1</v>
+      </c>
+      <c r="T430" t="n">
+        <v>0.003774307076939678</v>
+      </c>
+      <c r="U430" t="inlineStr"/>
+      <c r="V430" t="inlineStr"/>
+      <c r="W430" t="inlineStr"/>
+      <c r="X430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>470</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>18.32599118942731</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>47.02549575070821</v>
+      </c>
+      <c r="F431" t="n">
+        <v>46.30220582151263</v>
+      </c>
+      <c r="G431" t="n">
+        <v>42.75127122803573</v>
+      </c>
+      <c r="H431" t="n">
+        <v>47.87535410764873</v>
+      </c>
+      <c r="I431" t="n">
+        <v>-0.8498583569405156</v>
+      </c>
+      <c r="J431" t="n">
+        <v>2.749570243238407</v>
+      </c>
+      <c r="K431" t="n">
+        <v>2.807704328102019</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0.496292419594028</v>
+      </c>
+      <c r="M431" t="n">
+        <v>2156.90646930323</v>
+      </c>
+      <c r="N431" t="n">
+        <v>6.110216626921332</v>
+      </c>
+      <c r="O431" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>25</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0</v>
+      </c>
+      <c r="S431" t="b">
+        <v>0</v>
+      </c>
+      <c r="T431" t="n">
+        <v>7.273702441133974</v>
+      </c>
+      <c r="U431" t="n">
+        <v>9.752253423651103</v>
+      </c>
+      <c r="V431" t="n">
+        <v>4.419262027082135</v>
+      </c>
+      <c r="W431" t="inlineStr"/>
+      <c r="X431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>471</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>16.86274509803922</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>44.92307692307692</v>
+      </c>
+      <c r="F432" t="n">
+        <v>46.25062125062125</v>
+      </c>
+      <c r="G432" t="n">
+        <v>41.1537130457505</v>
+      </c>
+      <c r="H432" t="n">
+        <v>56.61538461538461</v>
+      </c>
+      <c r="I432" t="n">
+        <v>-11.69230769230769</v>
+      </c>
+      <c r="J432" t="n">
+        <v>-0.1496003961444552</v>
+      </c>
+      <c r="K432" t="n">
+        <v>-0.06232289268219375</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0.01499048526022392</v>
+      </c>
+      <c r="M432" t="n">
+        <v>-4.555245529945353</v>
+      </c>
+      <c r="N432" t="n">
+        <v>-0.01401614009213955</v>
+      </c>
+      <c r="O432" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="b">
+        <v>1</v>
+      </c>
+      <c r="T432" t="n">
+        <v>0.01178176007338337</v>
+      </c>
+      <c r="U432" t="n">
+        <v>-0.02634930891004967</v>
+      </c>
+      <c r="V432" t="n">
+        <v>-0.02897852489302257</v>
+      </c>
+      <c r="W432" t="inlineStr"/>
+      <c r="X432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>472</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>14.86486486486486</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>44.47592067988669</v>
+      </c>
+      <c r="F433" t="n">
+        <v>43.44686133307027</v>
+      </c>
+      <c r="G433" t="n">
+        <v>40.16246349672219</v>
+      </c>
+      <c r="H433" t="n">
+        <v>47.87535410764873</v>
+      </c>
+      <c r="I433" t="n">
+        <v>-3.399433427762034</v>
+      </c>
+      <c r="J433" t="n">
+        <v>-0.8745869039891278</v>
+      </c>
+      <c r="K433" t="n">
+        <v>-0.4717444008743506</v>
+      </c>
+      <c r="L433" t="n">
+        <v>-0.008229232602955581</v>
+      </c>
+      <c r="M433" t="n">
+        <v>368.568730728969</v>
+      </c>
+      <c r="N433" t="n">
+        <v>1.04410405305657</v>
+      </c>
+      <c r="O433" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>10</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="b">
+        <v>1</v>
+      </c>
+      <c r="T433" t="n">
+        <v>-0.08144658528499797</v>
+      </c>
+      <c r="U433" t="n">
+        <v>0.1725950700855096</v>
+      </c>
+      <c r="V433" t="n">
+        <v>0.5880477773442286</v>
+      </c>
+      <c r="W433" t="inlineStr"/>
+      <c r="X433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>473</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>40.625</v>
+      </c>
+      <c r="F434" t="n">
+        <v>41.21212121212122</v>
+      </c>
+      <c r="G434" t="n">
+        <v>38.14814814814815</v>
+      </c>
+      <c r="H434" t="n">
+        <v>39.58333333333333</v>
+      </c>
+      <c r="I434" t="n">
+        <v>1.041666666666671</v>
+      </c>
+      <c r="J434" t="n">
+        <v>-0.2065617317199121</v>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="n">
+        <v>12.43399739731622</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0.1308841831296444</v>
+      </c>
+      <c r="O434" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>10</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="b">
+        <v>1</v>
+      </c>
+      <c r="T434" t="inlineStr"/>
+      <c r="U434" t="inlineStr"/>
+      <c r="V434" t="inlineStr"/>
+      <c r="W434" t="inlineStr"/>
+      <c r="X434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>474</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>15.91240875912409</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>42.99065420560748</v>
+      </c>
+      <c r="F435" t="n">
+        <v>43.89691338692278</v>
+      </c>
+      <c r="G435" t="n">
+        <v>37.81024889267193</v>
+      </c>
+      <c r="H435" t="n">
+        <v>49.53271028037383</v>
+      </c>
+      <c r="I435" t="n">
+        <v>-6.542056074766357</v>
+      </c>
+      <c r="J435" t="n">
+        <v>-0.9492506628148938</v>
+      </c>
+      <c r="K435" t="n">
+        <v>-0.006505632908797878</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0.1133714463493223</v>
+      </c>
+      <c r="M435" t="n">
+        <v>61.18740588758769</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0.1906149716124227</v>
+      </c>
+      <c r="O435" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>15</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0</v>
+      </c>
+      <c r="S435" t="b">
+        <v>0</v>
+      </c>
+      <c r="T435" t="n">
+        <v>0.1906201131589114</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0.5838501722635491</v>
+      </c>
+      <c r="V435" t="n">
+        <v>0.2639639180217128</v>
+      </c>
+      <c r="W435" t="inlineStr"/>
+      <c r="X435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>475</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>17.16312056737589</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>40.74074074074074</v>
+      </c>
+      <c r="F436" t="n">
+        <v>40.71488431953549</v>
+      </c>
+      <c r="G436" t="n">
+        <v>35.59183218414463</v>
+      </c>
+      <c r="H436" t="n">
+        <v>46.2962962962963</v>
+      </c>
+      <c r="I436" t="n">
+        <v>-5.555555555555557</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0.01635337812784172</v>
+      </c>
+      <c r="K436" t="n">
+        <v>-0.04157407361453948</v>
+      </c>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="n">
+        <v>-2.551406640857877</v>
+      </c>
+      <c r="N436" t="n">
+        <v>-0.02362413556349886</v>
+      </c>
+      <c r="O436" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>0</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="b">
+        <v>1</v>
+      </c>
+      <c r="T436" t="inlineStr"/>
+      <c r="U436" t="inlineStr"/>
+      <c r="V436" t="inlineStr"/>
+      <c r="W436" t="inlineStr"/>
+      <c r="X436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>476</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>17.45283018867925</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>42.47787610619469</v>
+      </c>
+      <c r="F437" t="n">
+        <v>41.21720471599112</v>
+      </c>
+      <c r="G437" t="n">
+        <v>34.94875760815129</v>
+      </c>
+      <c r="H437" t="n">
+        <v>45.72271386430678</v>
+      </c>
+      <c r="I437" t="n">
+        <v>-3.244837758112091</v>
+      </c>
+      <c r="J437" t="n">
+        <v>-0.2165041984938386</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0.2254676129018263</v>
+      </c>
+      <c r="L437" t="n">
+        <v>1.035023345907818</v>
+      </c>
+      <c r="M437" t="n">
+        <v>100.6185441004281</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0.2968098646030327</v>
+      </c>
+      <c r="O437" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>10</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="b">
+        <v>1</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0.7201524059337316</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0.514428852129783</v>
+      </c>
+      <c r="V437" t="n">
+        <v>0.3777680067953244</v>
+      </c>
+      <c r="W437" t="inlineStr"/>
+      <c r="X437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>477</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>16.21818181818182</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>42.51207729468599</v>
+      </c>
+      <c r="F438" t="n">
+        <v>40.51721946880163</v>
+      </c>
+      <c r="G438" t="n">
+        <v>37.49259436215959</v>
+      </c>
+      <c r="H438" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="I438" t="n">
+        <v>-5.314009661835755</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0.4759414187144938</v>
+      </c>
+      <c r="K438" t="n">
+        <v>0.3888371190150568</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0.2546832132796574</v>
+      </c>
+      <c r="M438" t="n">
+        <v>16.91753313952258</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0.0821239472792358</v>
+      </c>
+      <c r="O438" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>5</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S438" t="b">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>0.05650076447651628</v>
+      </c>
+      <c r="U438" t="inlineStr"/>
+      <c r="V438" t="inlineStr"/>
+      <c r="W438" t="inlineStr"/>
+      <c r="X438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>478</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>17.60869565217391</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>43.342776203966</v>
+      </c>
+      <c r="F439" t="n">
+        <v>40.83000922172897</v>
+      </c>
+      <c r="G439" t="n">
+        <v>36.04121370317589</v>
+      </c>
+      <c r="H439" t="n">
+        <v>47.30878186968839</v>
+      </c>
+      <c r="I439" t="n">
+        <v>-3.966005665722385</v>
+      </c>
+      <c r="J439" t="n">
+        <v>-0.3996128217662482</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0.1005071355474088</v>
+      </c>
+      <c r="L439" t="n">
+        <v>-0.1448534179474235</v>
+      </c>
+      <c r="M439" t="n">
+        <v>39.7992641598982</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0.1133882169797669</v>
+      </c>
+      <c r="O439" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>10</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="b">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>-0.2058208366477284</v>
+      </c>
+      <c r="U439" t="n">
+        <v>-0.190394238475851</v>
+      </c>
+      <c r="V439" t="n">
+        <v>-0.03264969200822473</v>
+      </c>
+      <c r="W439" t="inlineStr"/>
+      <c r="X439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>479</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>15.31486146095718</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>46.43962848297213</v>
+      </c>
+      <c r="F440" t="n">
+        <v>47.13972219256728</v>
+      </c>
+      <c r="G440" t="n">
+        <v>40.86892943449795</v>
+      </c>
+      <c r="H440" t="n">
+        <v>56.34674922600619</v>
+      </c>
+      <c r="I440" t="n">
+        <v>-9.907120743034056</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0.1089423371547372</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0.05426670707063692</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0.04515513611044952</v>
+      </c>
+      <c r="M440" t="n">
+        <v>2.887310823433907</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0.008939042797009</v>
+      </c>
+      <c r="O440" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>5</v>
+      </c>
+      <c r="R440" t="n">
+        <v>0</v>
+      </c>
+      <c r="S440" t="b">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>-0.1358152433463036</v>
+      </c>
+      <c r="U440" t="n">
+        <v>-0.1051525202363361</v>
+      </c>
+      <c r="V440" t="n">
+        <v>-0.04286113221793523</v>
+      </c>
+      <c r="W440" t="inlineStr"/>
+      <c r="X440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>480</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>47.83950617283951</v>
+      </c>
+      <c r="F441" t="n">
+        <v>45.15538225215645</v>
+      </c>
+      <c r="G441" t="n">
+        <v>42.78846303782005</v>
+      </c>
+      <c r="H441" t="n">
+        <v>56.17283950617284</v>
+      </c>
+      <c r="I441" t="n">
+        <v>-8.333333333333336</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0.1794670697936613</v>
+      </c>
+      <c r="K441" t="n">
+        <v>-0.07512019802028064</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0.01460905818722201</v>
+      </c>
+      <c r="M441" t="n">
+        <v>45.03021078297635</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0.1389821320462233</v>
+      </c>
+      <c r="O441" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>5</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0</v>
+      </c>
+      <c r="S441" t="b">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0.1299010250696757</v>
+      </c>
+      <c r="U441" t="n">
+        <v>0.09178651949410442</v>
+      </c>
+      <c r="V441" t="n">
+        <v>0.1091992868054495</v>
+      </c>
+      <c r="W441" t="inlineStr"/>
+      <c r="X441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>481</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>17.16216216216216</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>42.43697478991596</v>
+      </c>
+      <c r="F442" t="n">
+        <v>43.15703174269498</v>
+      </c>
+      <c r="G442" t="n">
+        <v>37.69964286361741</v>
+      </c>
+      <c r="H442" t="n">
+        <v>47.05882352941176</v>
+      </c>
+      <c r="I442" t="n">
+        <v>-4.621848739495796</v>
+      </c>
+      <c r="J442" t="n">
+        <v>-0.7504977549866989</v>
+      </c>
+      <c r="K442" t="n">
+        <v>-0.2485594476264547</v>
+      </c>
+      <c r="L442" t="n">
+        <v>-0.2760994489776358</v>
+      </c>
+      <c r="M442" t="n">
+        <v>25.16584880195263</v>
+      </c>
+      <c r="N442" t="n">
+        <v>0.105738860512406</v>
+      </c>
+      <c r="O442" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>10</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0</v>
+      </c>
+      <c r="S442" t="b">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0.3075908676159129</v>
+      </c>
+      <c r="U442" t="inlineStr"/>
+      <c r="V442" t="inlineStr"/>
+      <c r="W442" t="inlineStr"/>
+      <c r="X442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>482</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>13.31910352187834</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>42.14186369958276</v>
+      </c>
+      <c r="F443" t="n">
+        <v>41.73523720902752</v>
+      </c>
+      <c r="G443" t="n">
+        <v>40.12550884883897</v>
+      </c>
+      <c r="H443" t="n">
+        <v>51.59944367176634</v>
+      </c>
+      <c r="I443" t="n">
+        <v>-9.457579972183588</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0.008530090649007605</v>
+      </c>
+      <c r="K443" t="n">
+        <v>0.0798539140352139</v>
+      </c>
+      <c r="L443" t="n">
+        <v>0.07677125138821206</v>
+      </c>
+      <c r="M443" t="n">
+        <v>-14.06564337659978</v>
+      </c>
+      <c r="N443" t="n">
+        <v>-0.01956278633741277</v>
+      </c>
+      <c r="O443" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>0</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0</v>
+      </c>
+      <c r="S443" t="b">
+        <v>1</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0.04851936167199156</v>
+      </c>
+      <c r="U443" t="n">
+        <v>0.03770601754457891</v>
+      </c>
+      <c r="V443" t="n">
+        <v>0.004663679217461976</v>
+      </c>
+      <c r="W443" t="n">
+        <v>0.01905053957750582</v>
+      </c>
+      <c r="X443" t="n">
+        <v>-0.01590801786496215</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>483</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>18.18548387096774</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>45.95300261096606</v>
+      </c>
+      <c r="F444" t="n">
+        <v>45.56395114688043</v>
+      </c>
+      <c r="G444" t="n">
+        <v>43.01885486561901</v>
+      </c>
+      <c r="H444" t="n">
+        <v>51.43603133159269</v>
+      </c>
+      <c r="I444" t="n">
+        <v>-5.483028720626628</v>
+      </c>
+      <c r="J444" t="n">
+        <v>-0.04258944487987634</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0.08877034668448161</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0.05741387911624524</v>
+      </c>
+      <c r="M444" t="n">
+        <v>10.27522380509026</v>
+      </c>
+      <c r="N444" t="n">
+        <v>0.02682826058770304</v>
+      </c>
+      <c r="O444" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>5</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0</v>
+      </c>
+      <c r="S444" t="b">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0.08078184388620983</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0.1327201981341998</v>
+      </c>
+      <c r="V444" t="n">
+        <v>0.02833557172064346</v>
+      </c>
+      <c r="W444" t="inlineStr"/>
+      <c r="X444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>484</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>13.65208545269583</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>43.90896921017403</v>
+      </c>
+      <c r="F445" t="n">
+        <v>42.73449971054106</v>
+      </c>
+      <c r="G445" t="n">
+        <v>38.66929822124433</v>
+      </c>
+      <c r="H445" t="n">
+        <v>51.27175368139224</v>
+      </c>
+      <c r="I445" t="n">
+        <v>-7.362784471218212</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0.3065034984590139</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0.1775682660822237</v>
+      </c>
+      <c r="L445" t="n">
+        <v>0.1500186955737228</v>
+      </c>
+      <c r="M445" t="n">
+        <v>14.57175389580175</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0.01953318216595409</v>
+      </c>
+      <c r="O445" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>5</v>
+      </c>
+      <c r="R445" t="n">
+        <v>0</v>
+      </c>
+      <c r="S445" t="b">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0.3622297108625146</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0.3536872893760116</v>
+      </c>
+      <c r="V445" t="n">
+        <v>0.353724311577746</v>
+      </c>
+      <c r="W445" t="n">
+        <v>0.07596789665533343</v>
+      </c>
+      <c r="X445" t="n">
+        <v>0.07107861972312725</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>485</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>13.85542168674699</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>44.38775510204081</v>
+      </c>
+      <c r="F446" t="n">
+        <v>43.79016316320392</v>
+      </c>
+      <c r="G446" t="n">
+        <v>39.4297816878462</v>
+      </c>
+      <c r="H446" t="n">
+        <v>46.68367346938776</v>
+      </c>
+      <c r="I446" t="n">
+        <v>-2.295918367346943</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0.3390891566985704</v>
+      </c>
+      <c r="K446" t="n">
+        <v>-0.125986692761829</v>
+      </c>
+      <c r="L446" t="n">
+        <v>-0.1100080652162003</v>
+      </c>
+      <c r="M446" t="n">
+        <v>37.26931662537481</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0.09531794533343942</v>
+      </c>
+      <c r="O446" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>10</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0</v>
+      </c>
+      <c r="S446" t="b">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0.1807151889871591</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0.06715267199434385</v>
+      </c>
+      <c r="V446" t="n">
+        <v>0.1896715194020507</v>
+      </c>
+      <c r="W446" t="inlineStr"/>
+      <c r="X446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>486</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>13.66737739872068</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>44.50474898236092</v>
+      </c>
+      <c r="F447" t="n">
+        <v>44.7200232359549</v>
+      </c>
+      <c r="G447" t="n">
+        <v>41.07415118110653</v>
+      </c>
+      <c r="H447" t="n">
+        <v>47.76119402985074</v>
+      </c>
+      <c r="I447" t="n">
+        <v>-3.256445047489819</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0.2221135138114784</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0.09663297209337757</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0.3339290143839637</v>
+      </c>
+      <c r="M447" t="n">
+        <v>57.35234632029804</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0.07781865172360657</v>
+      </c>
+      <c r="O447" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>10</v>
+      </c>
+      <c r="R447" t="n">
+        <v>0</v>
+      </c>
+      <c r="S447" t="b">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0.1738129332636379</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0.4718123943437071</v>
+      </c>
+      <c r="V447" t="n">
+        <v>0.3967251298643048</v>
+      </c>
+      <c r="W447" t="n">
+        <v>0.04237088707892912</v>
+      </c>
+      <c r="X447" t="n">
+        <v>0.2471216175238828</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>487</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>14.39739413680782</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>45.88068181818182</v>
+      </c>
+      <c r="F448" t="n">
+        <v>43.93405965493056</v>
+      </c>
+      <c r="G448" t="n">
+        <v>41.71770495299907</v>
+      </c>
+      <c r="H448" t="n">
+        <v>53.40909090909091</v>
+      </c>
+      <c r="I448" t="n">
+        <v>-7.528409090909086</v>
+      </c>
+      <c r="J448" t="n">
+        <v>-0.0870872237764803</v>
+      </c>
+      <c r="K448" t="n">
+        <v>-0.08494984072116026</v>
+      </c>
+      <c r="L448" t="n">
+        <v>-0.0744258811155126</v>
+      </c>
+      <c r="M448" t="n">
+        <v>36.94734762706551</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0.05248202787935442</v>
+      </c>
+      <c r="O448" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>5</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
+      </c>
+      <c r="S448" t="b">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>0.0738703397443561</v>
+      </c>
+      <c r="U448" t="n">
+        <v>0.2263228688889872</v>
+      </c>
+      <c r="V448" t="n">
+        <v>0.168963477870179</v>
+      </c>
+      <c r="W448" t="n">
+        <v>0.1469072354145501</v>
+      </c>
+      <c r="X448" t="n">
+        <v>0.1042580624960637</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>488</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>13.40364333652924</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>42.46231155778894</v>
+      </c>
+      <c r="F449" t="n">
+        <v>40.99444617180799</v>
+      </c>
+      <c r="G449" t="n">
+        <v>36.43754748338082</v>
+      </c>
+      <c r="H449" t="n">
+        <v>48.49246231155779</v>
+      </c>
+      <c r="I449" t="n">
+        <v>-6.030150753768844</v>
+      </c>
+      <c r="J449" t="n">
+        <v>-0.1346688647899026</v>
+      </c>
+      <c r="K449" t="n">
+        <v>-0.06576531802380473</v>
+      </c>
+      <c r="L449" t="n">
+        <v>-0.03647502133884113</v>
+      </c>
+      <c r="M449" t="n">
+        <v>3.35098706276358</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0.004209782742165301</v>
+      </c>
+      <c r="O449" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0</v>
+      </c>
+      <c r="S449" t="b">
+        <v>1</v>
+      </c>
+      <c r="T449" t="n">
+        <v>-0.02879965832839858</v>
+      </c>
+      <c r="U449" t="n">
+        <v>-0.02568843255831956</v>
+      </c>
+      <c r="V449" t="n">
+        <v>-0.02614237268567568</v>
+      </c>
+      <c r="W449" t="n">
+        <v>-0.02858250509361088</v>
+      </c>
+      <c r="X449" t="n">
+        <v>-0.01630311385711545</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>489</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>18.35205992509363</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>42.32558139534884</v>
+      </c>
+      <c r="F450" t="n">
+        <v>40.83500863031779</v>
+      </c>
+      <c r="G450" t="n">
+        <v>39.42240239204186</v>
+      </c>
+      <c r="H450" t="n">
+        <v>54.88372093023256</v>
+      </c>
+      <c r="I450" t="n">
+        <v>-12.55813953488372</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0.20551891658236</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0.1592373241276992</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0.006514349823597077</v>
+      </c>
+      <c r="M450" t="n">
+        <v>-9.95048265014205</v>
+      </c>
+      <c r="N450" t="n">
+        <v>-0.04628131465182349</v>
+      </c>
+      <c r="O450" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>0</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0</v>
+      </c>
+      <c r="S450" t="b">
+        <v>1</v>
+      </c>
+      <c r="T450" t="n">
+        <v>-0.0279379956457263</v>
+      </c>
+      <c r="U450" t="inlineStr"/>
+      <c r="V450" t="inlineStr"/>
+      <c r="W450" t="inlineStr"/>
+      <c r="X450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>490</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>12.15017064846416</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="F451" t="n">
+        <v>44.618309781027</v>
+      </c>
+      <c r="G451" t="n">
+        <v>41.87416330978455</v>
+      </c>
+      <c r="H451" t="n">
+        <v>49.18518518518519</v>
+      </c>
+      <c r="I451" t="n">
+        <v>-4.740740740740748</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0.0907638489167428</v>
+      </c>
+      <c r="K451" t="n">
+        <v>-0.002920104593933388</v>
+      </c>
+      <c r="L451" t="n">
+        <v>-0.01366632392024002</v>
+      </c>
+      <c r="M451" t="n">
+        <v>6.412426021827073</v>
+      </c>
+      <c r="N451" t="n">
+        <v>0.009528121874928786</v>
+      </c>
+      <c r="O451" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>0</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0</v>
+      </c>
+      <c r="S451" t="b">
+        <v>1</v>
+      </c>
+      <c r="T451" t="n">
+        <v>-0.009188973232193334</v>
+      </c>
+      <c r="U451" t="n">
+        <v>-0.02397694026795421</v>
+      </c>
+      <c r="V451" t="n">
+        <v>-0.00186117637051936</v>
+      </c>
+      <c r="W451" t="n">
+        <v>-0.007728609898791916</v>
+      </c>
+      <c r="X451" t="n">
+        <v>0.01805494298000136</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>491</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>20.70631970260223</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>45.04716981132076</v>
+      </c>
+      <c r="F452" t="n">
+        <v>45.19802135325797</v>
+      </c>
+      <c r="G452" t="n">
+        <v>42.58954684932338</v>
+      </c>
+      <c r="H452" t="n">
+        <v>51.88679245283019</v>
+      </c>
+      <c r="I452" t="n">
+        <v>-6.839622641509429</v>
+      </c>
+      <c r="J452" t="n">
+        <v>-0.3321619990521569</v>
+      </c>
+      <c r="K452" t="n">
+        <v>-0.2735867675523714</v>
+      </c>
+      <c r="L452" t="n">
+        <v>-0.1303447285827668</v>
+      </c>
+      <c r="M452" t="n">
+        <v>36.25710122412937</v>
+      </c>
+      <c r="N452" t="n">
+        <v>0.08551203118898437</v>
+      </c>
+      <c r="O452" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>5</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0</v>
+      </c>
+      <c r="S452" t="b">
+        <v>0</v>
+      </c>
+      <c r="T452" t="n">
+        <v>-0.1053448895691015</v>
+      </c>
+      <c r="U452" t="n">
+        <v>-0.07346154195540759</v>
+      </c>
+      <c r="V452" t="n">
+        <v>0.03985773440480225</v>
+      </c>
+      <c r="W452" t="n">
+        <v>0.142334207761921</v>
+      </c>
+      <c r="X452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>492</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>14.08231368186874</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>46.86131386861314</v>
+      </c>
+      <c r="F453" t="n">
+        <v>46.75753156566795</v>
+      </c>
+      <c r="G453" t="n">
+        <v>45.1363874297311</v>
+      </c>
+      <c r="H453" t="n">
+        <v>52.40875912408759</v>
+      </c>
+      <c r="I453" t="n">
+        <v>-5.54744525547445</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0.1805675521208582</v>
+      </c>
+      <c r="K453" t="n">
+        <v>-0.3953422166625799</v>
+      </c>
+      <c r="L453" t="n">
+        <v>-0.107227610179563</v>
+      </c>
+      <c r="M453" t="n">
+        <v>155.3069165012085</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0.2270568954696031</v>
+      </c>
+      <c r="O453" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>10</v>
+      </c>
+      <c r="R453" t="n">
+        <v>0</v>
+      </c>
+      <c r="S453" t="b">
+        <v>0</v>
+      </c>
+      <c r="T453" t="n">
+        <v>-0.1539157362592918</v>
+      </c>
+      <c r="U453" t="n">
+        <v>-0.1363032780851697</v>
+      </c>
+      <c r="V453" t="n">
+        <v>-0.06084037433894044</v>
+      </c>
+      <c r="W453" t="n">
+        <v>0.368505065462133</v>
+      </c>
+      <c r="X453" t="n">
+        <v>0.5070407837172607</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>493</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>16.47446457990115</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>47.16981132075472</v>
+      </c>
+      <c r="F454" t="n">
+        <v>43.89359160713777</v>
+      </c>
+      <c r="G454" t="n">
+        <v>41.87476950634845</v>
+      </c>
+      <c r="H454" t="n">
+        <v>54.71698113207547</v>
+      </c>
+      <c r="I454" t="n">
+        <v>-7.547169811320749</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0.05810390202192593</v>
+      </c>
+      <c r="K454" t="n">
+        <v>0.2089373087971316</v>
+      </c>
+      <c r="L454" t="n">
+        <v>0.09089067444963907</v>
+      </c>
+      <c r="M454" t="n">
+        <v>1.869882942671979</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0.003920090026565993</v>
+      </c>
+      <c r="O454" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>5</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0</v>
+      </c>
+      <c r="S454" t="b">
+        <v>0</v>
+      </c>
+      <c r="T454" t="n">
+        <v>0.002214000093109547</v>
+      </c>
+      <c r="U454" t="n">
+        <v>0.1023330022335853</v>
+      </c>
+      <c r="V454" t="n">
+        <v>0.05278609056694715</v>
+      </c>
+      <c r="W454" t="n">
+        <v>0.07656236140063762</v>
+      </c>
+      <c r="X454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>494</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>13.89623601220753</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>45.47872340425532</v>
+      </c>
+      <c r="F455" t="n">
+        <v>44.99340096004097</v>
+      </c>
+      <c r="G455" t="n">
+        <v>42.97836638612554</v>
+      </c>
+      <c r="H455" t="n">
+        <v>53.8563829787234</v>
+      </c>
+      <c r="I455" t="n">
+        <v>-8.377659574468083</v>
+      </c>
+      <c r="J455" t="n">
+        <v>-0.1191103944062937</v>
+      </c>
+      <c r="K455" t="n">
+        <v>-0.1094361500775439</v>
+      </c>
+      <c r="L455" t="n">
+        <v>-0.087596501920171</v>
+      </c>
+      <c r="M455" t="n">
+        <v>-0.5005840100131849</v>
+      </c>
+      <c r="N455" t="n">
+        <v>-0.0006656702260813629</v>
+      </c>
+      <c r="O455" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>0</v>
+      </c>
+      <c r="R455" t="n">
+        <v>0</v>
+      </c>
+      <c r="S455" t="b">
+        <v>1</v>
+      </c>
+      <c r="T455" t="n">
+        <v>-0.07463720484469284</v>
+      </c>
+      <c r="U455" t="n">
+        <v>-0.02122589835466687</v>
+      </c>
+      <c r="V455" t="n">
+        <v>-0.0166539216654455</v>
+      </c>
+      <c r="W455" t="n">
+        <v>-0.00159566804020443</v>
+      </c>
+      <c r="X455" t="n">
+        <v>-0.001031011964678299</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>495</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>16.26575028636884</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>44.08759124087591</v>
+      </c>
+      <c r="F456" t="n">
+        <v>43.15992241249973</v>
+      </c>
+      <c r="G456" t="n">
+        <v>40.58401578725906</v>
+      </c>
+      <c r="H456" t="n">
+        <v>50.21897810218978</v>
+      </c>
+      <c r="I456" t="n">
+        <v>-6.131386861313871</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0.002175172830356757</v>
+      </c>
+      <c r="K456" t="n">
+        <v>-0.007436127064781743</v>
+      </c>
+      <c r="L456" t="n">
+        <v>0.03211186230433317</v>
+      </c>
+      <c r="M456" t="n">
+        <v>-2.207081337858313</v>
+      </c>
+      <c r="N456" t="n">
+        <v>-0.003222016551617975</v>
+      </c>
+      <c r="O456" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>0</v>
+      </c>
+      <c r="R456" t="n">
+        <v>0</v>
+      </c>
+      <c r="S456" t="b">
+        <v>1</v>
+      </c>
+      <c r="T456" t="n">
+        <v>0.02662109566876517</v>
+      </c>
+      <c r="U456" t="n">
+        <v>0.01253741195229418</v>
+      </c>
+      <c r="V456" t="n">
+        <v>0.01767885101025494</v>
+      </c>
+      <c r="W456" t="n">
+        <v>-0.0140485409715092</v>
+      </c>
+      <c r="X456" t="n">
+        <v>0.003524395929126087</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>496</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>15.21521521521522</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>47.73936170212766</v>
+      </c>
+      <c r="F457" t="n">
+        <v>46.01840237424926</v>
+      </c>
+      <c r="G457" t="n">
+        <v>43.18892259794483</v>
+      </c>
+      <c r="H457" t="n">
+        <v>52.3936170212766</v>
+      </c>
+      <c r="I457" t="n">
+        <v>-4.654255319148938</v>
+      </c>
+      <c r="J457" t="n">
+        <v>0.7516413620676059</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0.9118342168705967</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0.3889650109916522</v>
+      </c>
+      <c r="M457" t="n">
+        <v>78.46218082190296</v>
+      </c>
+      <c r="N457" t="n">
+        <v>0.104338006412105</v>
+      </c>
+      <c r="O457" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>10</v>
+      </c>
+      <c r="R457" t="n">
+        <v>0</v>
+      </c>
+      <c r="S457" t="b">
+        <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>0.5405827470192431</v>
+      </c>
+      <c r="U457" t="n">
+        <v>0.6253296384056743</v>
+      </c>
+      <c r="V457" t="n">
+        <v>0.4250732295710319</v>
+      </c>
+      <c r="W457" t="n">
+        <v>0.05446050507742597</v>
+      </c>
+      <c r="X457" t="n">
+        <v>-0.06290985934959409</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>497</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>18.94736842105264</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>46.96969696969697</v>
+      </c>
+      <c r="F458" t="n">
+        <v>45.19608894608895</v>
+      </c>
+      <c r="G458" t="n">
+        <v>40.00460689822391</v>
+      </c>
+      <c r="H458" t="n">
+        <v>50</v>
+      </c>
+      <c r="I458" t="n">
+        <v>-3.030303030303031</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1.033546208048114</v>
+      </c>
+      <c r="K458" t="n">
+        <v>0.5711420803618372</v>
+      </c>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="n">
+        <v>13.75146119988548</v>
+      </c>
+      <c r="N458" t="n">
+        <v>0.1041777363627688</v>
+      </c>
+      <c r="O458" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>10</v>
+      </c>
+      <c r="R458" t="n">
+        <v>0</v>
+      </c>
+      <c r="S458" t="b">
+        <v>1</v>
+      </c>
+      <c r="T458" t="inlineStr"/>
+      <c r="U458" t="inlineStr"/>
+      <c r="V458" t="inlineStr"/>
+      <c r="W458" t="inlineStr"/>
+      <c r="X458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>498</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>11.65909090909091</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>45.0920245398773</v>
+      </c>
+      <c r="F459" t="n">
+        <v>45.3427249079423</v>
+      </c>
+      <c r="G459" t="n">
+        <v>43.53114451555797</v>
+      </c>
+      <c r="H459" t="n">
+        <v>52.76073619631902</v>
+      </c>
+      <c r="I459" t="n">
+        <v>-7.668711656441715</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0.5660750027690921</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0.4258665692510448</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0.1879347033921501</v>
+      </c>
+      <c r="M459" t="n">
+        <v>4.209170560573796</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0.006455783068364717</v>
+      </c>
+      <c r="O459" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>5</v>
+      </c>
+      <c r="R459" t="n">
+        <v>0</v>
+      </c>
+      <c r="S459" t="b">
+        <v>0</v>
+      </c>
+      <c r="T459" t="n">
+        <v>-0.02503065008277559</v>
+      </c>
+      <c r="U459" t="n">
+        <v>0.05311955234158279</v>
+      </c>
+      <c r="V459" t="n">
+        <v>0.01869685845384377</v>
+      </c>
+      <c r="W459" t="n">
+        <v>0.03513321210462237</v>
+      </c>
+      <c r="X459" t="n">
+        <v>0.1079158599712803</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>499</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>23.9426523297491</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>44.87179487179488</v>
+      </c>
+      <c r="F460" t="n">
+        <v>45.60700321767875</v>
+      </c>
+      <c r="G460" t="n">
+        <v>43.67752466113122</v>
+      </c>
+      <c r="H460" t="n">
+        <v>51.70940170940172</v>
+      </c>
+      <c r="I460" t="n">
+        <v>-6.837606837606842</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0.1102659761084698</v>
+      </c>
+      <c r="K460" t="n">
+        <v>-0.02898621600822537</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0.01333437266332718</v>
+      </c>
+      <c r="M460" t="n">
+        <v>1.608186965022171</v>
+      </c>
+      <c r="N460" t="n">
+        <v>0.006872593867616113</v>
+      </c>
+      <c r="O460" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0</v>
+      </c>
+      <c r="S460" t="b">
+        <v>1</v>
+      </c>
+      <c r="T460" t="n">
+        <v>0.003578931430567778</v>
+      </c>
+      <c r="U460" t="inlineStr"/>
+      <c r="V460" t="inlineStr"/>
+      <c r="W460" t="inlineStr"/>
+      <c r="X460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>500</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>15.16533637400228</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>45.77039274924471</v>
+      </c>
+      <c r="F461" t="n">
+        <v>44.51829879214525</v>
+      </c>
+      <c r="G461" t="n">
+        <v>42.61187412878409</v>
+      </c>
+      <c r="H461" t="n">
+        <v>56.19335347432024</v>
+      </c>
+      <c r="I461" t="n">
+        <v>-10.42296072507553</v>
+      </c>
+      <c r="J461" t="n">
+        <v>-0.1126431017456338</v>
+      </c>
+      <c r="K461" t="n">
+        <v>-0.05027873556639392</v>
+      </c>
+      <c r="L461" t="n">
+        <v>-0.02031865444484254</v>
+      </c>
+      <c r="M461" t="n">
+        <v>-2.560867511619136</v>
+      </c>
+      <c r="N461" t="n">
+        <v>-0.003868379926917125</v>
+      </c>
+      <c r="O461" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>0</v>
+      </c>
+      <c r="R461" t="n">
+        <v>0</v>
+      </c>
+      <c r="S461" t="b">
+        <v>1</v>
+      </c>
+      <c r="T461" t="n">
+        <v>-0.03464494133224157</v>
+      </c>
+      <c r="U461" t="n">
+        <v>-0.02476176959119687</v>
+      </c>
+      <c r="V461" t="n">
+        <v>-0.02976986370156889</v>
+      </c>
+      <c r="W461" t="n">
+        <v>-0.02404557612501574</v>
+      </c>
+      <c r="X461" t="n">
+        <v>-0.01082565609726586</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>501</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>18.91472868217054</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>43.08681672025724</v>
+      </c>
+      <c r="F462" t="n">
+        <v>45.4006192034361</v>
+      </c>
+      <c r="G462" t="n">
+        <v>40.46641364703998</v>
+      </c>
+      <c r="H462" t="n">
+        <v>56.91318327974276</v>
+      </c>
+      <c r="I462" t="n">
+        <v>-13.82636655948552</v>
+      </c>
+      <c r="J462" t="n">
+        <v>-0.002142877099861664</v>
+      </c>
+      <c r="K462" t="n">
+        <v>-0.08595353415458148</v>
+      </c>
+      <c r="L462" t="n">
+        <v>-0.06738335906144499</v>
+      </c>
+      <c r="M462" t="n">
+        <v>-6.761230662246547</v>
+      </c>
+      <c r="N462" t="n">
+        <v>-0.02174029151847764</v>
+      </c>
+      <c r="O462" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>0</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0</v>
+      </c>
+      <c r="S462" t="b">
+        <v>1</v>
+      </c>
+      <c r="T462" t="n">
+        <v>-0.02986758237761116</v>
+      </c>
+      <c r="U462" t="n">
+        <v>-0.02058781240436849</v>
+      </c>
+      <c r="V462" t="n">
+        <v>-0.02430276197369551</v>
+      </c>
+      <c r="W462" t="inlineStr"/>
+      <c r="X462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>502</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>12.6813880126183</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>46.62998624484182</v>
+      </c>
+      <c r="F463" t="n">
+        <v>46.36130848499958</v>
+      </c>
+      <c r="G463" t="n">
+        <v>44.66886563557059</v>
+      </c>
+      <c r="H463" t="n">
+        <v>53.50756533700137</v>
+      </c>
+      <c r="I463" t="n">
+        <v>-6.877579092159557</v>
+      </c>
+      <c r="J463" t="n">
+        <v>-0.02564015501352657</v>
+      </c>
+      <c r="K463" t="n">
+        <v>-0.02845689194559313</v>
+      </c>
+      <c r="L463" t="n">
+        <v>-0.03737091234689217</v>
+      </c>
+      <c r="M463" t="n">
+        <v>20.37641172803671</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0.02802807665479603</v>
+      </c>
+      <c r="O463" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>5</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0</v>
+      </c>
+      <c r="S463" t="b">
+        <v>0</v>
+      </c>
+      <c r="T463" t="n">
+        <v>0.03509738897210354</v>
+      </c>
+      <c r="U463" t="n">
+        <v>-0.03596212141557385</v>
+      </c>
+      <c r="V463" t="n">
+        <v>-0.04929651482546376</v>
+      </c>
+      <c r="W463" t="n">
+        <v>-0.04095714200906677</v>
+      </c>
+      <c r="X463" t="n">
+        <v>-0.04770143149862585</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>503</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>15.8411214953271</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>41.55455904334828</v>
+      </c>
+      <c r="F464" t="n">
+        <v>40.62255677375952</v>
+      </c>
+      <c r="G464" t="n">
+        <v>37.28780338708593</v>
+      </c>
+      <c r="H464" t="n">
+        <v>51.12107623318386</v>
+      </c>
+      <c r="I464" t="n">
+        <v>-9.566517189835572</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0.04260989038955245</v>
+      </c>
+      <c r="K464" t="n">
+        <v>-0.06876468400329572</v>
+      </c>
+      <c r="L464" t="n">
+        <v>-0.008766993996024819</v>
+      </c>
+      <c r="M464" t="n">
+        <v>-6.64023107660158</v>
+      </c>
+      <c r="N464" t="n">
+        <v>-0.0099404656835353</v>
+      </c>
+      <c r="O464" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>0</v>
+      </c>
+      <c r="R464" t="n">
+        <v>0</v>
+      </c>
+      <c r="S464" t="b">
+        <v>1</v>
+      </c>
+      <c r="T464" t="n">
+        <v>0.03426049282911947</v>
+      </c>
+      <c r="U464" t="n">
+        <v>0.01641875095183104</v>
+      </c>
+      <c r="V464" t="n">
+        <v>-0.0131884042979649</v>
+      </c>
+      <c r="W464" t="n">
+        <v>-0.03219017243676081</v>
+      </c>
+      <c r="X464" t="n">
+        <v>-0.04099621006415475</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>504</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>13.04531085353003</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>40.02751031636863</v>
+      </c>
+      <c r="F465" t="n">
+        <v>41.65381375373102</v>
+      </c>
+      <c r="G465" t="n">
+        <v>37.18843222717942</v>
+      </c>
+      <c r="H465" t="n">
+        <v>50.48143053645116</v>
+      </c>
+      <c r="I465" t="n">
+        <v>-10.45392022008253</v>
+      </c>
+      <c r="J465" t="n">
+        <v>-0.1442658989850196</v>
+      </c>
+      <c r="K465" t="n">
+        <v>-0.1143591273397286</v>
+      </c>
+      <c r="L465" t="n">
+        <v>-0.09489156892666036</v>
+      </c>
+      <c r="M465" t="n">
+        <v>-30.41054316013452</v>
+      </c>
+      <c r="N465" t="n">
+        <v>-0.04183018316387142</v>
+      </c>
+      <c r="O465" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>0</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0</v>
+      </c>
+      <c r="S465" t="b">
+        <v>1</v>
+      </c>
+      <c r="T465" t="n">
+        <v>-0.08962910712513569</v>
+      </c>
+      <c r="U465" t="n">
+        <v>-0.06877208273079526</v>
+      </c>
+      <c r="V465" t="n">
+        <v>-0.06006505630955383</v>
+      </c>
+      <c r="W465" t="n">
+        <v>-0.05623316233775977</v>
+      </c>
+      <c r="X465" t="n">
+        <v>-0.04715605924049203</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>506</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>17.48987854251012</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>42.7807486631016</v>
+      </c>
+      <c r="F466" t="n">
+        <v>43.52429180015387</v>
+      </c>
+      <c r="G466" t="n">
+        <v>37.13939598828037</v>
+      </c>
+      <c r="H466" t="n">
+        <v>50.80213903743316</v>
+      </c>
+      <c r="I466" t="n">
+        <v>-8.021390374331553</v>
+      </c>
+      <c r="J466" t="n">
+        <v>-0.05678130881505553</v>
+      </c>
+      <c r="K466" t="n">
+        <v>0.2670824433564188</v>
+      </c>
+      <c r="L466" t="n">
+        <v>0.3177793348883222</v>
+      </c>
+      <c r="M466" t="n">
+        <v>29.09770642534616</v>
+      </c>
+      <c r="N466" t="n">
+        <v>0.1556027081569313</v>
+      </c>
+      <c r="O466" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>10</v>
+      </c>
+      <c r="R466" t="n">
+        <v>0</v>
+      </c>
+      <c r="S466" t="b">
+        <v>0</v>
+      </c>
+      <c r="T466" t="inlineStr"/>
+      <c r="U466" t="inlineStr"/>
+      <c r="V466" t="inlineStr"/>
+      <c r="W466" t="inlineStr"/>
+      <c r="X466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>507</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>17.79141104294479</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>50</v>
+      </c>
+      <c r="F467" t="n">
+        <v>47.83140898635877</v>
+      </c>
+      <c r="G467" t="n">
+        <v>49.15616485682205</v>
+      </c>
+      <c r="H467" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="I467" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="J467" t="n">
+        <v>4.529898794624416</v>
+      </c>
+      <c r="K467" t="n">
+        <v>1.332335130235436</v>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="n">
+        <v>143.6147308631276</v>
+      </c>
+      <c r="N467" t="n">
+        <v>1.196789423859397</v>
+      </c>
+      <c r="O467" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>20</v>
+      </c>
+      <c r="R467" t="n">
+        <v>0</v>
+      </c>
+      <c r="S467" t="b">
+        <v>0</v>
+      </c>
+      <c r="T467" t="inlineStr"/>
+      <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr"/>
+      <c r="W467" t="inlineStr"/>
+      <c r="X467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>508</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>18.125</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>43.58974358974359</v>
+      </c>
+      <c r="F468" t="n">
+        <v>40.77678757556806</v>
+      </c>
+      <c r="G468" t="n">
+        <v>37.84766889015786</v>
+      </c>
+      <c r="H468" t="n">
+        <v>45.64102564102564</v>
+      </c>
+      <c r="I468" t="n">
+        <v>-2.051282051282051</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0.2636610225179979</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0.8869117151080675</v>
+      </c>
+      <c r="L468" t="n">
+        <v>3.118768659373993</v>
+      </c>
+      <c r="M468" t="n">
+        <v>378.1787706230607</v>
+      </c>
+      <c r="N468" t="n">
+        <v>1.939378310887491</v>
+      </c>
+      <c r="O468" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>25</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="b">
+        <v>0</v>
+      </c>
+      <c r="T468" t="inlineStr"/>
+      <c r="U468" t="inlineStr"/>
+      <c r="V468" t="inlineStr"/>
+      <c r="W468" t="inlineStr"/>
+      <c r="X468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>509</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>22.33333333333334</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>43.18181818181818</v>
+      </c>
+      <c r="F469" t="n">
+        <v>41.22655122655123</v>
+      </c>
+      <c r="G469" t="n">
+        <v>41.33823828845276</v>
+      </c>
+      <c r="H469" t="n">
+        <v>47.72727272727273</v>
+      </c>
+      <c r="I469" t="n">
+        <v>-4.545454545454547</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0.08892597904736163</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0.02191654033145412</v>
+      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="n">
+        <v>3.292597191834901</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0.02494391811996137</v>
+      </c>
+      <c r="O469" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>0</v>
+      </c>
+      <c r="R469" t="n">
+        <v>0</v>
+      </c>
+      <c r="S469" t="b">
+        <v>1</v>
+      </c>
+      <c r="T469" t="inlineStr"/>
+      <c r="U469" t="inlineStr"/>
+      <c r="V469" t="inlineStr"/>
+      <c r="W469" t="inlineStr"/>
+      <c r="X469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>510</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>21.05263157894737</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>51.28205128205128</v>
+      </c>
+      <c r="F470" t="n">
+        <v>47.10546041630629</v>
+      </c>
+      <c r="G470" t="n">
+        <v>45.39317396624692</v>
+      </c>
+      <c r="H470" t="n">
+        <v>48.2051282051282</v>
+      </c>
+      <c r="I470" t="n">
+        <v>3.076923076923073</v>
+      </c>
+      <c r="J470" t="n">
+        <v>131.1153734741628</v>
+      </c>
+      <c r="K470" t="n">
+        <v>16.30504720772274</v>
+      </c>
+      <c r="L470" t="n">
+        <v>22.24928198457943</v>
+      </c>
+      <c r="M470" t="n">
+        <v>10122.38684270714</v>
+      </c>
+      <c r="N470" t="n">
+        <v>51.90967611644686</v>
+      </c>
+      <c r="O470" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>30</v>
+      </c>
+      <c r="R470" t="n">
+        <v>0</v>
+      </c>
+      <c r="S470" t="b">
+        <v>0</v>
+      </c>
+      <c r="T470" t="inlineStr"/>
+      <c r="U470" t="inlineStr"/>
+      <c r="V470" t="inlineStr"/>
+      <c r="W470" t="inlineStr"/>
+      <c r="X470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>511</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>17.09844559585492</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>44.13793103448276</v>
+      </c>
+      <c r="F471" t="n">
+        <v>43.76711199076364</v>
+      </c>
+      <c r="G471" t="n">
+        <v>38.94473944539821</v>
+      </c>
+      <c r="H471" t="n">
+        <v>42.06896551724138</v>
+      </c>
+      <c r="I471" t="n">
+        <v>2.068965517241381</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0.1604505156530027</v>
+      </c>
+      <c r="K471" t="n">
+        <v>-0.1140823108789758</v>
+      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="n">
+        <v>17.46842787610919</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0.1204719163869599</v>
+      </c>
+      <c r="O471" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q471" t="n">
+        <v>10</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0</v>
+      </c>
+      <c r="S471" t="b">
+        <v>1</v>
+      </c>
+      <c r="T471" t="inlineStr"/>
+      <c r="U471" t="inlineStr"/>
+      <c r="V471" t="inlineStr"/>
+      <c r="W471" t="inlineStr"/>
+      <c r="X471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>512</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>19.46666666666667</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>44.24778761061947</v>
+      </c>
+      <c r="F472" t="n">
+        <v>42.50574952051168</v>
+      </c>
+      <c r="G472" t="n">
+        <v>39.03860205455738</v>
+      </c>
+      <c r="H472" t="n">
+        <v>50.88495575221239</v>
+      </c>
+      <c r="I472" t="n">
+        <v>-6.637168141592923</v>
+      </c>
+      <c r="J472" t="n">
+        <v>-0.2605358961934593</v>
+      </c>
+      <c r="K472" t="n">
+        <v>0.1465829367209597</v>
+      </c>
+      <c r="L472" t="n">
+        <v>0.2700188347544463</v>
+      </c>
+      <c r="M472" t="n">
+        <v>61.78718885463832</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0.273394640949727</v>
+      </c>
+      <c r="O472" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q472" t="n">
+        <v>10</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0</v>
+      </c>
+      <c r="S472" t="b">
+        <v>0</v>
+      </c>
+      <c r="T472" t="n">
+        <v>0.1115544934383358</v>
+      </c>
+      <c r="U472" t="inlineStr"/>
+      <c r="V472" t="inlineStr"/>
+      <c r="W472" t="inlineStr"/>
+      <c r="X472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>514</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>16.18320610687023</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>42.56410256410256</v>
+      </c>
+      <c r="F473" t="n">
+        <v>43.82570255438127</v>
+      </c>
+      <c r="G473" t="n">
+        <v>36.52615855661541</v>
+      </c>
+      <c r="H473" t="n">
+        <v>52.30769230769231</v>
+      </c>
+      <c r="I473" t="n">
+        <v>-9.743589743589752</v>
+      </c>
+      <c r="J473" t="n">
+        <v>-0.3491015400893761</v>
+      </c>
+      <c r="K473" t="n">
+        <v>0.5577698761751972</v>
+      </c>
+      <c r="L473" t="n">
+        <v>0.4586306633490763</v>
+      </c>
+      <c r="M473" t="n">
+        <v>13.77543609180678</v>
+      </c>
+      <c r="N473" t="n">
+        <v>0.07064326200926554</v>
+      </c>
+      <c r="O473" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q473" t="n">
+        <v>10</v>
+      </c>
+      <c r="R473" t="n">
+        <v>0</v>
+      </c>
+      <c r="S473" t="b">
+        <v>0</v>
+      </c>
+      <c r="T473" t="inlineStr"/>
+      <c r="U473" t="inlineStr"/>
+      <c r="V473" t="inlineStr"/>
+      <c r="W473" t="inlineStr"/>
+      <c r="X473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>516</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>16.23529411764706</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="F474" t="n">
+        <v>47.5505111976631</v>
+      </c>
+      <c r="G474" t="n">
+        <v>41.10344827586207</v>
+      </c>
+      <c r="H474" t="n">
+        <v>52.82051282051282</v>
+      </c>
+      <c r="I474" t="n">
+        <v>-6.666666666666671</v>
+      </c>
+      <c r="J474" t="n">
+        <v>0.7950395625971567</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0.3837939386084404</v>
+      </c>
+      <c r="L474" t="n">
+        <v>0.2706979402191363</v>
+      </c>
+      <c r="M474" t="n">
+        <v>33.83362577112388</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0.1735057731852507</v>
+      </c>
+      <c r="O474" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>15</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0</v>
+      </c>
+      <c r="S474" t="b">
+        <v>0</v>
+      </c>
+      <c r="T474" t="inlineStr"/>
+      <c r="U474" t="inlineStr"/>
+      <c r="V474" t="inlineStr"/>
+      <c r="W474" t="inlineStr"/>
+      <c r="X474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>517</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>17.41573033707865</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>46.92307692307692</v>
+      </c>
+      <c r="F475" t="n">
+        <v>43.30038933812519</v>
+      </c>
+      <c r="G475" t="n">
+        <v>38.33305673111499</v>
+      </c>
+      <c r="H475" t="n">
+        <v>42.30769230769231</v>
+      </c>
+      <c r="I475" t="n">
+        <v>4.615384615384613</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1.738560716609468</v>
+      </c>
+      <c r="K475" t="n">
+        <v>-0.02708725989653857</v>
+      </c>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="n">
+        <v>35.74968553186577</v>
+      </c>
+      <c r="N475" t="n">
+        <v>0.2749975810143521</v>
+      </c>
+      <c r="O475" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>15</v>
+      </c>
+      <c r="R475" t="n">
+        <v>0</v>
+      </c>
+      <c r="S475" t="b">
+        <v>0</v>
+      </c>
+      <c r="T475" t="inlineStr"/>
+      <c r="U475" t="inlineStr"/>
+      <c r="V475" t="inlineStr"/>
+      <c r="W475" t="inlineStr"/>
+      <c r="X475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>518</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>18.61003861003861</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>45.12820512820513</v>
+      </c>
+      <c r="F476" t="n">
+        <v>43.04036067642216</v>
+      </c>
+      <c r="G476" t="n">
+        <v>39.94875859694634</v>
+      </c>
+      <c r="H476" t="n">
+        <v>48.2051282051282</v>
+      </c>
+      <c r="I476" t="n">
+        <v>-3.076923076923073</v>
+      </c>
+      <c r="J476" t="n">
+        <v>1.608976499877086</v>
+      </c>
+      <c r="K476" t="n">
+        <v>1.963139681472968</v>
+      </c>
+      <c r="L476" t="n">
+        <v>1.320031549203969</v>
+      </c>
+      <c r="M476" t="n">
+        <v>50.25705318826928</v>
+      </c>
+      <c r="N476" t="n">
+        <v>0.2577284778885604</v>
+      </c>
+      <c r="O476" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q476" t="n">
+        <v>15</v>
+      </c>
+      <c r="R476" t="n">
+        <v>0</v>
+      </c>
+      <c r="S476" t="b">
+        <v>0</v>
+      </c>
+      <c r="T476" t="inlineStr"/>
+      <c r="U476" t="inlineStr"/>
+      <c r="V476" t="inlineStr"/>
+      <c r="W476" t="inlineStr"/>
+      <c r="X476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>519</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>16.31840796019901</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>43.24324324324324</v>
+      </c>
+      <c r="F477" t="n">
+        <v>42.1685606060606</v>
+      </c>
+      <c r="G477" t="n">
+        <v>37.2923364589562</v>
+      </c>
+      <c r="H477" t="n">
+        <v>52.02702702702703</v>
+      </c>
+      <c r="I477" t="n">
+        <v>-8.78378378378379</v>
+      </c>
+      <c r="J477" t="n">
+        <v>-0.005511032983497444</v>
+      </c>
+      <c r="K477" t="n">
+        <v>-0.01305668711656622</v>
+      </c>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="n">
+        <v>-2.625189897426935</v>
+      </c>
+      <c r="N477" t="n">
+        <v>-0.01773776957720902</v>
+      </c>
+      <c r="O477" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q477" t="n">
+        <v>0</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0</v>
+      </c>
+      <c r="S477" t="b">
+        <v>1</v>
+      </c>
+      <c r="T477" t="inlineStr"/>
+      <c r="U477" t="inlineStr"/>
+      <c r="V477" t="inlineStr"/>
+      <c r="W477" t="inlineStr"/>
+      <c r="X477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>520</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>22.421875</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F478" t="n">
+        <v>45.15667710789661</v>
+      </c>
+      <c r="G478" t="n">
+        <v>41.38872823083349</v>
+      </c>
+      <c r="H478" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I478" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J478" t="n">
+        <v>-0.02678942613495962</v>
+      </c>
+      <c r="K478" t="n">
+        <v>-0.08017395449219464</v>
+      </c>
+      <c r="L478" t="n">
+        <v>0.04458424586430131</v>
+      </c>
+      <c r="M478" t="n">
+        <v>23.52514835671212</v>
+      </c>
+      <c r="N478" t="n">
+        <v>0.1176257417835606</v>
+      </c>
+      <c r="O478" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q478" t="n">
+        <v>10</v>
+      </c>
+      <c r="R478" t="n">
+        <v>0</v>
+      </c>
+      <c r="S478" t="b">
+        <v>0</v>
+      </c>
+      <c r="T478" t="n">
+        <v>0.1176257417835606</v>
+      </c>
+      <c r="U478" t="inlineStr"/>
+      <c r="V478" t="inlineStr"/>
+      <c r="W478" t="inlineStr"/>
+      <c r="X478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>522</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>16.69291338582677</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>38.46153846153847</v>
+      </c>
+      <c r="F479" t="n">
+        <v>38.71794871794872</v>
+      </c>
+      <c r="G479" t="n">
+        <v>33.07412093185586</v>
+      </c>
+      <c r="H479" t="n">
+        <v>50.25641025641026</v>
+      </c>
+      <c r="I479" t="n">
+        <v>-11.79487179487179</v>
+      </c>
+      <c r="J479" t="n">
+        <v>-0.1820401537340709</v>
+      </c>
+      <c r="K479" t="n">
+        <v>-0.131529838796009</v>
+      </c>
+      <c r="L479" t="n">
+        <v>-0.08485779956040063</v>
+      </c>
+      <c r="M479" t="n">
+        <v>-14.69898772834354</v>
+      </c>
+      <c r="N479" t="n">
+        <v>-0.07537942424791558</v>
+      </c>
+      <c r="O479" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q479" t="n">
+        <v>0</v>
+      </c>
+      <c r="R479" t="n">
+        <v>0</v>
+      </c>
+      <c r="S479" t="b">
+        <v>1</v>
+      </c>
+      <c r="T479" t="inlineStr"/>
+      <c r="U479" t="inlineStr"/>
+      <c r="V479" t="inlineStr"/>
+      <c r="W479" t="inlineStr"/>
+      <c r="X479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>524</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>17.14285714285715</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>42.05128205128205</v>
+      </c>
+      <c r="F480" t="n">
+        <v>41.33123398474885</v>
+      </c>
+      <c r="G480" t="n">
+        <v>37.37335148279367</v>
+      </c>
+      <c r="H480" t="n">
+        <v>48.2051282051282</v>
+      </c>
+      <c r="I480" t="n">
+        <v>-6.153846153846153</v>
+      </c>
+      <c r="J480" t="n">
+        <v>-0.5670813745005779</v>
+      </c>
+      <c r="K480" t="n">
+        <v>-0.00043909773971194</v>
+      </c>
+      <c r="L480" t="n">
+        <v>0.0775396695634015</v>
+      </c>
+      <c r="M480" t="n">
+        <v>12.59788494309186</v>
+      </c>
+      <c r="N480" t="n">
+        <v>0.06460453816970183</v>
+      </c>
+      <c r="O480" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q480" t="n">
+        <v>10</v>
+      </c>
+      <c r="R480" t="n">
+        <v>0</v>
+      </c>
+      <c r="S480" t="b">
+        <v>0</v>
+      </c>
+      <c r="T480" t="inlineStr"/>
+      <c r="U480" t="inlineStr"/>
+      <c r="V480" t="inlineStr"/>
+      <c r="W480" t="inlineStr"/>
+      <c r="X480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>525</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>18.83040935672514</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>44.53125</v>
+      </c>
+      <c r="F481" t="n">
+        <v>44.82179740716326</v>
+      </c>
+      <c r="G481" t="n">
+        <v>40.58883911907428</v>
+      </c>
+      <c r="H481" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="I481" t="n">
+        <v>-2.34375</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0.03946121594698781</v>
+      </c>
+      <c r="K481" t="n">
+        <v>0.377787976127114</v>
+      </c>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="n">
+        <v>18.56774308165643</v>
+      </c>
+      <c r="N481" t="n">
+        <v>0.1450604928254409</v>
+      </c>
+      <c r="O481" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q481" t="n">
+        <v>10</v>
+      </c>
+      <c r="R481" t="n">
+        <v>0</v>
+      </c>
+      <c r="S481" t="b">
+        <v>0</v>
+      </c>
+      <c r="T481" t="inlineStr"/>
+      <c r="U481" t="inlineStr"/>
+      <c r="V481" t="inlineStr"/>
+      <c r="W481" t="inlineStr"/>
+      <c r="X481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>526</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>18.046875</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="F482" t="n">
+        <v>44.71230158730158</v>
+      </c>
+      <c r="G482" t="n">
+        <v>40.66528919911512</v>
+      </c>
+      <c r="H482" t="n">
+        <v>45.12820512820513</v>
+      </c>
+      <c r="I482" t="n">
+        <v>1.538461538461533</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0.00254136987485964</v>
+      </c>
+      <c r="K482" t="n">
+        <v>-0.1745239533125441</v>
+      </c>
+      <c r="L482" t="n">
+        <v>3.030546302074272</v>
+      </c>
+      <c r="M482" t="n">
+        <v>463.272832340946</v>
+      </c>
+      <c r="N482" t="n">
+        <v>2.375758114568954</v>
+      </c>
+      <c r="O482" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q482" t="n">
+        <v>15</v>
+      </c>
+      <c r="R482" t="n">
+        <v>0</v>
+      </c>
+      <c r="S482" t="b">
+        <v>0</v>
+      </c>
+      <c r="T482" t="inlineStr"/>
+      <c r="U482" t="inlineStr"/>
+      <c r="V482" t="inlineStr"/>
+      <c r="W482" t="inlineStr"/>
+      <c r="X482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>527</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>20.50420168067227</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>41.39784946236559</v>
+      </c>
+      <c r="F483" t="n">
+        <v>41.52452025586354</v>
+      </c>
+      <c r="G483" t="n">
+        <v>38.83245583027913</v>
+      </c>
+      <c r="H483" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="I483" t="n">
+        <v>-4.838709677419352</v>
+      </c>
+      <c r="J483" t="n">
+        <v>-0.1358145638348319</v>
+      </c>
+      <c r="K483" t="n">
+        <v>-0.04957509606052994</v>
+      </c>
+      <c r="L483" t="n">
+        <v>-0.02415191335881531</v>
+      </c>
+      <c r="M483" t="n">
+        <v>2.265393623416443</v>
+      </c>
+      <c r="N483" t="n">
+        <v>0.01217953560976582</v>
+      </c>
+      <c r="O483" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q483" t="n">
+        <v>0</v>
+      </c>
+      <c r="R483" t="n">
+        <v>0</v>
+      </c>
+      <c r="S483" t="b">
+        <v>1</v>
+      </c>
+      <c r="T483" t="inlineStr"/>
+      <c r="U483" t="inlineStr"/>
+      <c r="V483" t="inlineStr"/>
+      <c r="W483" t="inlineStr"/>
+      <c r="X483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>528</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>19.23371647509579</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>44</v>
+      </c>
+      <c r="F484" t="n">
+        <v>41.98332347586079</v>
+      </c>
+      <c r="G484" t="n">
+        <v>40.23946481692961</v>
+      </c>
+      <c r="H484" t="n">
+        <v>44</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0.4406440983351544</v>
+      </c>
+      <c r="K484" t="n">
+        <v>-0.3697810138429379</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0.1072898771916315</v>
+      </c>
+      <c r="M484" t="n">
+        <v>37.68905763603547</v>
+      </c>
+      <c r="N484" t="n">
+        <v>0.1884452881801774</v>
+      </c>
+      <c r="O484" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q484" t="n">
+        <v>10</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0</v>
+      </c>
+      <c r="S484" t="b">
+        <v>1</v>
+      </c>
+      <c r="T484" t="n">
+        <v>0.1884452881801774</v>
+      </c>
+      <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr"/>
+      <c r="W484" t="inlineStr"/>
+      <c r="X484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>529</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>12.54901960784314</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>38.59649122807017</v>
+      </c>
+      <c r="F485" t="n">
+        <v>39.67227579252537</v>
+      </c>
+      <c r="G485" t="n">
+        <v>35.61344041162565</v>
+      </c>
+      <c r="H485" t="n">
+        <v>46.49122807017544</v>
+      </c>
+      <c r="I485" t="n">
+        <v>-7.894736842105267</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0.07281136005565514</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0.01109115343157797</v>
+      </c>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="n">
+        <v>-1.582573765451073</v>
+      </c>
+      <c r="N485" t="n">
+        <v>-0.01388222601272871</v>
+      </c>
+      <c r="O485" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>0</v>
+      </c>
+      <c r="S485" t="b">
+        <v>1</v>
+      </c>
+      <c r="T485" t="inlineStr"/>
+      <c r="U485" t="inlineStr"/>
+      <c r="V485" t="inlineStr"/>
+      <c r="W485" t="inlineStr"/>
+      <c r="X485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>530</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>18.42857142857143</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>39.1566265060241</v>
+      </c>
+      <c r="F486" t="n">
+        <v>39.45650183773741</v>
+      </c>
+      <c r="G486" t="n">
+        <v>33.90741041903833</v>
+      </c>
+      <c r="H486" t="n">
+        <v>46.08433734939759</v>
+      </c>
+      <c r="I486" t="n">
+        <v>-6.927710843373497</v>
+      </c>
+      <c r="J486" t="n">
+        <v>-0.08495577152132938</v>
+      </c>
+      <c r="K486" t="n">
+        <v>-0.03181648851878961</v>
+      </c>
+      <c r="L486" t="n">
+        <v>-0.1064327055406649</v>
+      </c>
+      <c r="M486" t="n">
+        <v>-14.67534494635078</v>
+      </c>
+      <c r="N486" t="n">
+        <v>-0.04447074226166902</v>
+      </c>
+      <c r="O486" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q486" t="n">
+        <v>0</v>
+      </c>
+      <c r="R486" t="n">
+        <v>0</v>
+      </c>
+      <c r="S486" t="b">
+        <v>1</v>
+      </c>
+      <c r="T486" t="n">
+        <v>-0.1012958899980124</v>
+      </c>
+      <c r="U486" t="n">
+        <v>-0.09290803700417018</v>
+      </c>
+      <c r="V486" t="n">
+        <v>-0.06125590990989215</v>
+      </c>
+      <c r="W486" t="inlineStr"/>
+      <c r="X486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>531</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>15.55555555555555</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>45.61403508771929</v>
+      </c>
+      <c r="F487" t="n">
+        <v>42.53594771241831</v>
+      </c>
+      <c r="G487" t="n">
+        <v>41.36254182693811</v>
+      </c>
+      <c r="H487" t="n">
+        <v>48.24561403508772</v>
+      </c>
+      <c r="I487" t="n">
+        <v>-2.631578947368425</v>
+      </c>
+      <c r="J487" t="n">
+        <v>-0.2362849162805003</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0.5592931107871609</v>
+      </c>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="n">
+        <v>29.65470728727706</v>
+      </c>
+      <c r="N487" t="n">
+        <v>0.260129011291904</v>
+      </c>
+      <c r="O487" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q487" t="n">
+        <v>10</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="b">
+        <v>1</v>
+      </c>
+      <c r="T487" t="inlineStr"/>
+      <c r="U487" t="inlineStr"/>
+      <c r="V487" t="inlineStr"/>
+      <c r="W487" t="inlineStr"/>
+      <c r="X487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>532</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>18.74709976798144</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>39.82300884955752</v>
+      </c>
+      <c r="F488" t="n">
+        <v>39.95427138284281</v>
+      </c>
+      <c r="G488" t="n">
+        <v>35.9020581118952</v>
+      </c>
+      <c r="H488" t="n">
+        <v>45.72271386430678</v>
+      </c>
+      <c r="I488" t="n">
+        <v>-5.899705014749259</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0.01385921242720315</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0.02876053494350842</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0.008827911382326097</v>
+      </c>
+      <c r="M488" t="n">
+        <v>-8.13984160512733</v>
+      </c>
+      <c r="N488" t="n">
+        <v>-0.02415383265616419</v>
+      </c>
+      <c r="O488" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>0</v>
+      </c>
+      <c r="S488" t="b">
+        <v>1</v>
+      </c>
+      <c r="T488" t="n">
+        <v>-0.02536725478146536</v>
+      </c>
+      <c r="U488" t="n">
+        <v>-0.03611482979626402</v>
+      </c>
+      <c r="V488" t="n">
+        <v>-0.02190271493669082</v>
+      </c>
+      <c r="W488" t="inlineStr"/>
+      <c r="X488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>533</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>17.55102040816326</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>42.98245614035088</v>
+      </c>
+      <c r="F489" t="n">
+        <v>40.7396331738437</v>
+      </c>
+      <c r="G489" t="n">
+        <v>40.01663395944304</v>
+      </c>
+      <c r="H489" t="n">
+        <v>50</v>
+      </c>
+      <c r="I489" t="n">
+        <v>-7.017543859649123</v>
+      </c>
+      <c r="J489" t="n">
+        <v>0.4649153104862881</v>
+      </c>
+      <c r="K489" t="n">
+        <v>0.1500912286786782</v>
+      </c>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="n">
+        <v>7.797026825288852</v>
+      </c>
+      <c r="N489" t="n">
+        <v>0.0683949721516566</v>
+      </c>
+      <c r="O489" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q489" t="n">
+        <v>10</v>
+      </c>
+      <c r="R489" t="n">
+        <v>0</v>
+      </c>
+      <c r="S489" t="b">
+        <v>0</v>
+      </c>
+      <c r="T489" t="inlineStr"/>
+      <c r="U489" t="inlineStr"/>
+      <c r="V489" t="inlineStr"/>
+      <c r="W489" t="inlineStr"/>
+      <c r="X489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>534</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>18.52193995381062</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>42.18289085545723</v>
+      </c>
+      <c r="F490" t="n">
+        <v>42.62738072008467</v>
+      </c>
+      <c r="G490" t="n">
+        <v>36.53212647587158</v>
+      </c>
+      <c r="H490" t="n">
+        <v>48.08259587020649</v>
+      </c>
+      <c r="I490" t="n">
+        <v>-5.899705014749259</v>
+      </c>
+      <c r="J490" t="n">
+        <v>-0.1538489688000183</v>
+      </c>
+      <c r="K490" t="n">
+        <v>-0.01628927055792616</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0.01197415312599588</v>
+      </c>
+      <c r="M490" t="n">
+        <v>-1.49040756078243</v>
+      </c>
+      <c r="N490" t="n">
+        <v>-0.004396482480184158</v>
+      </c>
+      <c r="O490" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q490" t="n">
+        <v>0</v>
+      </c>
+      <c r="R490" t="n">
+        <v>0</v>
+      </c>
+      <c r="S490" t="b">
+        <v>1</v>
+      </c>
+      <c r="T490" t="n">
+        <v>-0.0003913079599299607</v>
+      </c>
+      <c r="U490" t="n">
+        <v>-0.00563467117576738</v>
+      </c>
+      <c r="V490" t="n">
+        <v>-0.002143455794186716</v>
+      </c>
+      <c r="W490" t="inlineStr"/>
+      <c r="X490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>535</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>14.25287356321839</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="F491" t="n">
+        <v>44.51298701298701</v>
+      </c>
+      <c r="G491" t="n">
+        <v>44.26767676767676</v>
+      </c>
+      <c r="H491" t="n">
+        <v>44.92753623188405</v>
+      </c>
+      <c r="I491" t="n">
+        <v>2.898550724637687</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2.457858543893086</v>
+      </c>
+      <c r="K491" t="n">
+        <v>2.024205951101806</v>
+      </c>
+      <c r="L491" t="n">
+        <v>18.22582361314023</v>
+      </c>
+      <c r="M491" t="n">
+        <v>1135.772283457306</v>
+      </c>
+      <c r="N491" t="n">
+        <v>5.486822625397616</v>
+      </c>
+      <c r="O491" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q491" t="n">
+        <v>20</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="b">
+        <v>1</v>
+      </c>
+      <c r="T491" t="n">
+        <v>6.853917998298312</v>
+      </c>
+      <c r="U491" t="inlineStr"/>
+      <c r="V491" t="inlineStr"/>
+      <c r="W491" t="inlineStr"/>
+      <c r="X491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>536</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>15.85215605749487</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>45.0261780104712</v>
+      </c>
+      <c r="F492" t="n">
+        <v>44.21534465012726</v>
+      </c>
+      <c r="G492" t="n">
+        <v>38.90730765565819</v>
+      </c>
+      <c r="H492" t="n">
+        <v>49.73821989528796</v>
+      </c>
+      <c r="I492" t="n">
+        <v>-4.712041884816763</v>
+      </c>
+      <c r="J492" t="n">
+        <v>2.99270542905585</v>
+      </c>
+      <c r="K492" t="n">
+        <v>3.796393878564098</v>
+      </c>
+      <c r="L492" t="n">
+        <v>4.422812157501014</v>
+      </c>
+      <c r="M492" t="n">
+        <v>328.9196417997227</v>
+      </c>
+      <c r="N492" t="n">
+        <v>0.8610461827217872</v>
+      </c>
+      <c r="O492" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q492" t="n">
+        <v>10</v>
+      </c>
+      <c r="R492" t="n">
+        <v>0</v>
+      </c>
+      <c r="S492" t="b">
+        <v>1</v>
+      </c>
+      <c r="T492" t="n">
+        <v>4.074136267855891</v>
+      </c>
+      <c r="U492" t="n">
+        <v>2.965241928521995</v>
+      </c>
+      <c r="V492" t="n">
+        <v>1.092903179251775</v>
+      </c>
+      <c r="W492" t="inlineStr"/>
+      <c r="X492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>538</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>13.47517730496454</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>42.90030211480362</v>
+      </c>
+      <c r="F493" t="n">
+        <v>43.57960588051299</v>
+      </c>
+      <c r="G493" t="n">
+        <v>34.71935056371787</v>
+      </c>
+      <c r="H493" t="n">
+        <v>50.45317220543807</v>
+      </c>
+      <c r="I493" t="n">
+        <v>-7.552870090634443</v>
+      </c>
+      <c r="J493" t="n">
+        <v>0.3571835464634455</v>
+      </c>
+      <c r="K493" t="n">
+        <v>1.82136142414691</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0.8418062978642644</v>
+      </c>
+      <c r="M493" t="n">
+        <v>56.52382759416298</v>
+      </c>
+      <c r="N493" t="n">
+        <v>0.1712843260429181</v>
+      </c>
+      <c r="O493" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q493" t="n">
+        <v>10</v>
+      </c>
+      <c r="R493" t="n">
+        <v>0</v>
+      </c>
+      <c r="S493" t="b">
+        <v>0</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0.499553410528478</v>
+      </c>
+      <c r="U493" t="n">
+        <v>0.01610748089134961</v>
+      </c>
+      <c r="V493" t="n">
+        <v>0.1422488401779804</v>
+      </c>
+      <c r="W493" t="inlineStr"/>
+      <c r="X493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>539</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>9.640287769784173</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>38.23529411764706</v>
+      </c>
+      <c r="F494" t="n">
+        <v>41.48627980206928</v>
+      </c>
+      <c r="G494" t="n">
+        <v>32.5609756097561</v>
+      </c>
+      <c r="H494" t="n">
+        <v>45.09803921568628</v>
+      </c>
+      <c r="I494" t="n">
+        <v>-6.86274509803922</v>
+      </c>
+      <c r="J494" t="n">
+        <v>0.2386538524068789</v>
+      </c>
+      <c r="K494" t="n">
+        <v>0.03187449919487392</v>
+      </c>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="n">
+        <v>7.196200168809269</v>
+      </c>
+      <c r="N494" t="n">
+        <v>0.0705509820471497</v>
+      </c>
+      <c r="O494" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q494" t="n">
+        <v>10</v>
+      </c>
+      <c r="R494" t="n">
+        <v>0</v>
+      </c>
+      <c r="S494" t="b">
+        <v>0</v>
+      </c>
+      <c r="T494" t="inlineStr"/>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="inlineStr"/>
+      <c r="W494" t="inlineStr"/>
+      <c r="X494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>540</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>19.95327102803738</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>38.85542168674699</v>
+      </c>
+      <c r="F495" t="n">
+        <v>39.61093873388756</v>
+      </c>
+      <c r="G495" t="n">
+        <v>33.03337544783111</v>
+      </c>
+      <c r="H495" t="n">
+        <v>49.09638554216868</v>
+      </c>
+      <c r="I495" t="n">
+        <v>-10.24096385542169</v>
+      </c>
+      <c r="J495" t="n">
+        <v>0.1771650229955802</v>
+      </c>
+      <c r="K495" t="n">
+        <v>0.05324109724822478</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0.009477882446386067</v>
+      </c>
+      <c r="M495" t="n">
+        <v>-8.529612138602701</v>
+      </c>
+      <c r="N495" t="n">
+        <v>-0.02569160282711657</v>
+      </c>
+      <c r="O495" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q495" t="n">
+        <v>0</v>
+      </c>
+      <c r="R495" t="n">
+        <v>0</v>
+      </c>
+      <c r="S495" t="b">
+        <v>1</v>
+      </c>
+      <c r="T495" t="n">
+        <v>0.002429528293785736</v>
+      </c>
+      <c r="U495" t="n">
+        <v>-0.01299367803632902</v>
+      </c>
+      <c r="V495" t="n">
+        <v>-0.02062674839806926</v>
+      </c>
+      <c r="W495" t="inlineStr"/>
+      <c r="X495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>541</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>13.58490566037736</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>45.64102564102564</v>
+      </c>
+      <c r="F496" t="n">
+        <v>43.77777777777779</v>
+      </c>
+      <c r="G496" t="n">
+        <v>37.87606417129979</v>
+      </c>
+      <c r="H496" t="n">
+        <v>50.76923076923077</v>
+      </c>
+      <c r="I496" t="n">
+        <v>-5.128205128205124</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1.022756264339482</v>
+      </c>
+      <c r="K496" t="n">
+        <v>1.081517898933302</v>
+      </c>
+      <c r="L496" t="n">
+        <v>3.653359214995353</v>
+      </c>
+      <c r="M496" t="n">
+        <v>229.0279805574811</v>
+      </c>
+      <c r="N496" t="n">
+        <v>1.174502464397339</v>
+      </c>
+      <c r="O496" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q496" t="n">
+        <v>20</v>
+      </c>
+      <c r="R496" t="n">
+        <v>0</v>
+      </c>
+      <c r="S496" t="b">
+        <v>1</v>
+      </c>
+      <c r="T496" t="inlineStr"/>
+      <c r="U496" t="inlineStr"/>
+      <c r="V496" t="inlineStr"/>
+      <c r="W496" t="inlineStr"/>
+      <c r="X496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>542</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>12.71221532091097</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>42.67015706806283</v>
+      </c>
+      <c r="F497" t="n">
+        <v>42.18174696435566</v>
+      </c>
+      <c r="G497" t="n">
+        <v>34.47749888183101</v>
+      </c>
+      <c r="H497" t="n">
+        <v>44.50261780104712</v>
+      </c>
+      <c r="I497" t="n">
+        <v>-1.832460732984295</v>
+      </c>
+      <c r="J497" t="n">
+        <v>-0.9017655909408314</v>
+      </c>
+      <c r="K497" t="n">
+        <v>-0.4032607762631916</v>
+      </c>
+      <c r="L497" t="n">
+        <v>-0.2030315680836543</v>
+      </c>
+      <c r="M497" t="n">
+        <v>27.02578292816941</v>
+      </c>
+      <c r="N497" t="n">
+        <v>0.07093381345976223</v>
+      </c>
+      <c r="O497" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>10</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="b">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>-0.2637904856471022</v>
+      </c>
+      <c r="U497" t="n">
+        <v>-0.1123612956156095</v>
+      </c>
+      <c r="V497" t="n">
+        <v>0.02911339749679641</v>
+      </c>
+      <c r="W497" t="inlineStr"/>
+      <c r="X497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>543</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>14.5985401459854</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>42.46153846153846</v>
+      </c>
+      <c r="F498" t="n">
+        <v>44.4985011548479</v>
+      </c>
+      <c r="G498" t="n">
+        <v>38.69391344749768</v>
+      </c>
+      <c r="H498" t="n">
+        <v>51.07692307692307</v>
+      </c>
+      <c r="I498" t="n">
+        <v>-8.615384615384613</v>
+      </c>
+      <c r="J498" t="n">
+        <v>0.0199755923268944</v>
+      </c>
+      <c r="K498" t="n">
+        <v>0.003835263451517648</v>
+      </c>
+      <c r="L498" t="n">
+        <v>-0.05562153567533111</v>
+      </c>
+      <c r="M498" t="n">
+        <v>0.5746498395065061</v>
+      </c>
+      <c r="N498" t="n">
+        <v>0.001768153352327711</v>
+      </c>
+      <c r="O498" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q498" t="n">
+        <v>0</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="b">
+        <v>1</v>
+      </c>
+      <c r="T498" t="n">
+        <v>-0.05050327706200015</v>
+      </c>
+      <c r="U498" t="n">
+        <v>-0.02003757412713071</v>
+      </c>
+      <c r="V498" t="n">
+        <v>-0.002373750129508067</v>
+      </c>
+      <c r="W498" t="inlineStr"/>
+      <c r="X498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>544</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>14.68468468468469</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>47.59206798866856</v>
+      </c>
+      <c r="F499" t="n">
+        <v>46.55848212817731</v>
+      </c>
+      <c r="G499" t="n">
+        <v>43.23008938384047</v>
+      </c>
+      <c r="H499" t="n">
+        <v>47.87535410764873</v>
+      </c>
+      <c r="I499" t="n">
+        <v>-0.2832861189801648</v>
+      </c>
+      <c r="J499" t="n">
+        <v>-1.364677210038186</v>
+      </c>
+      <c r="K499" t="n">
+        <v>-0.9286659635176265</v>
+      </c>
+      <c r="L499" t="n">
+        <v>-0.3318058509009633</v>
+      </c>
+      <c r="M499" t="n">
+        <v>7931.819737999404</v>
+      </c>
+      <c r="N499" t="n">
+        <v>22.4697443002816</v>
+      </c>
+      <c r="O499" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q499" t="n">
+        <v>40</v>
+      </c>
+      <c r="R499" t="n">
+        <v>0</v>
+      </c>
+      <c r="S499" t="b">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>-0.227348044894324</v>
+      </c>
+      <c r="U499" t="n">
+        <v>2.111404500425162</v>
+      </c>
+      <c r="V499" t="n">
+        <v>18.89689413649383</v>
+      </c>
+      <c r="W499" t="inlineStr"/>
+      <c r="X499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>546</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>18.77450980392157</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>43.92523364485982</v>
+      </c>
+      <c r="F500" t="n">
+        <v>42.79295166127123</v>
+      </c>
+      <c r="G500" t="n">
+        <v>38.38600980722929</v>
+      </c>
+      <c r="H500" t="n">
+        <v>46.72897196261682</v>
+      </c>
+      <c r="I500" t="n">
+        <v>-2.803738317757009</v>
+      </c>
+      <c r="J500" t="n">
+        <v>-0.7010524329936303</v>
+      </c>
+      <c r="K500" t="n">
+        <v>0.5405240787879154</v>
+      </c>
+      <c r="L500" t="n">
+        <v>-0.1629702525993122</v>
+      </c>
+      <c r="M500" t="n">
+        <v>200.195921572641</v>
+      </c>
+      <c r="N500" t="n">
+        <v>0.6236633070798786</v>
+      </c>
+      <c r="O500" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q500" t="n">
+        <v>15</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="b">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0.06425193416418097</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0.2865403058625238</v>
+      </c>
+      <c r="V500" t="n">
+        <v>0.7297226081712614</v>
+      </c>
+      <c r="W500" t="inlineStr"/>
+      <c r="X500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>548</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>17.49419953596288</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>42.72997032640949</v>
+      </c>
+      <c r="F501" t="n">
+        <v>42.39338237777733</v>
+      </c>
+      <c r="G501" t="n">
+        <v>37.99474274314813</v>
+      </c>
+      <c r="H501" t="n">
+        <v>49.55489614243324</v>
+      </c>
+      <c r="I501" t="n">
+        <v>-6.824925816023743</v>
+      </c>
+      <c r="J501" t="n">
+        <v>-0.1479492590115666</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0.1524478753570581</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0.07633720742486143</v>
+      </c>
+      <c r="M501" t="n">
+        <v>6.541492171767501</v>
+      </c>
+      <c r="N501" t="n">
+        <v>0.01941095599931009</v>
+      </c>
+      <c r="O501" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q501" t="n">
+        <v>5</v>
+      </c>
+      <c r="R501" t="n">
+        <v>0</v>
+      </c>
+      <c r="S501" t="b">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>-0.08430246821987375</v>
+      </c>
+      <c r="U501" t="n">
+        <v>0.04211013012594481</v>
+      </c>
+      <c r="V501" t="n">
+        <v>0.03165241103551731</v>
+      </c>
+      <c r="W501" t="inlineStr"/>
+      <c r="X501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>549</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>16.14285714285715</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>41.34615384615385</v>
+      </c>
+      <c r="F502" t="n">
+        <v>44.25850340136055</v>
+      </c>
+      <c r="G502" t="n">
+        <v>36.71986543840091</v>
+      </c>
+      <c r="H502" t="n">
+        <v>49.03846153846153</v>
+      </c>
+      <c r="I502" t="n">
+        <v>-7.692307692307686</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0.2107201572779422</v>
+      </c>
+      <c r="K502" t="n">
+        <v>-0.008139203133697209</v>
+      </c>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="n">
+        <v>-0.1556412976846531</v>
+      </c>
+      <c r="N502" t="n">
+        <v>-0.00149655093927551</v>
+      </c>
+      <c r="O502" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q502" t="n">
+        <v>5</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="b">
+        <v>0</v>
+      </c>
+      <c r="T502" t="inlineStr"/>
+      <c r="U502" t="inlineStr"/>
+      <c r="V502" t="inlineStr"/>
+      <c r="W502" t="inlineStr"/>
+      <c r="X502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>550</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>19.03448275862069</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>41.29793510324484</v>
+      </c>
+      <c r="F503" t="n">
+        <v>39.72321943004034</v>
+      </c>
+      <c r="G503" t="n">
+        <v>36.25000146891022</v>
+      </c>
+      <c r="H503" t="n">
+        <v>45.72271386430678</v>
+      </c>
+      <c r="I503" t="n">
+        <v>-4.424778761061944</v>
+      </c>
+      <c r="J503" t="n">
+        <v>-0.3646911077102555</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0.3839124120237676</v>
+      </c>
+      <c r="L503" t="n">
+        <v>0.3562237569863301</v>
+      </c>
+      <c r="M503" t="n">
+        <v>58.46618623735378</v>
+      </c>
+      <c r="N503" t="n">
+        <v>0.1729768823590349</v>
+      </c>
+      <c r="O503" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q503" t="n">
+        <v>5</v>
+      </c>
+      <c r="R503" t="n">
+        <v>0</v>
+      </c>
+      <c r="S503" t="b">
+        <v>0</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0.2599319378833171</v>
+      </c>
+      <c r="U503" t="n">
+        <v>0.1412196947313273</v>
+      </c>
+      <c r="V503" t="n">
+        <v>0.1753134637612971</v>
+      </c>
+      <c r="W503" t="inlineStr"/>
+      <c r="X503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>551</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>13.98457583547558</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>42.10526315789473</v>
+      </c>
+      <c r="F504" t="n">
+        <v>40.95309215621197</v>
+      </c>
+      <c r="G504" t="n">
+        <v>35.20366479925303</v>
+      </c>
+      <c r="H504" t="n">
+        <v>52.0123839009288</v>
+      </c>
+      <c r="I504" t="n">
+        <v>-9.907120743034064</v>
+      </c>
+      <c r="J504" t="n">
+        <v>-0.1769375011060066</v>
+      </c>
+      <c r="K504" t="n">
+        <v>-0.2125172337780127</v>
+      </c>
+      <c r="L504" t="n">
+        <v>0.1418420523885737</v>
+      </c>
+      <c r="M504" t="n">
+        <v>176.2986976767854</v>
+      </c>
+      <c r="N504" t="n">
+        <v>0.5458164014761157</v>
+      </c>
+      <c r="O504" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q504" t="n">
+        <v>15</v>
+      </c>
+      <c r="R504" t="n">
+        <v>0</v>
+      </c>
+      <c r="S504" t="b">
+        <v>0</v>
+      </c>
+      <c r="T504" t="n">
+        <v>-0.0816590217042733</v>
+      </c>
+      <c r="U504" t="n">
+        <v>0.5292470373020453</v>
+      </c>
+      <c r="V504" t="n">
+        <v>0.7442886970909589</v>
+      </c>
+      <c r="W504" t="inlineStr"/>
+      <c r="X504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>552</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>43.342776203966</v>
+      </c>
+      <c r="F505" t="n">
+        <v>43.06203135650988</v>
+      </c>
+      <c r="G505" t="n">
+        <v>40.66836694743672</v>
+      </c>
+      <c r="H505" t="n">
+        <v>55.52407932011332</v>
+      </c>
+      <c r="I505" t="n">
+        <v>-12.18130311614731</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0.08036230679918815</v>
+      </c>
+      <c r="K505" t="n">
+        <v>-0.01903297760196637</v>
+      </c>
+      <c r="L505" t="n">
+        <v>-0.01954840728025848</v>
+      </c>
+      <c r="M505" t="n">
+        <v>-10.46539304120398</v>
+      </c>
+      <c r="N505" t="n">
+        <v>-0.02964700578244754</v>
+      </c>
+      <c r="O505" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="b">
+        <v>1</v>
+      </c>
+      <c r="T505" t="n">
+        <v>-0.02350976750567995</v>
+      </c>
+      <c r="U505" t="n">
+        <v>-0.03325034828654253</v>
+      </c>
+      <c r="V505" t="n">
+        <v>-0.05948231645810485</v>
+      </c>
+      <c r="W505" t="inlineStr"/>
+      <c r="X505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>553</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>15.13157894736842</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>41.59663865546219</v>
+      </c>
+      <c r="F506" t="n">
+        <v>41.86499215070644</v>
+      </c>
+      <c r="G506" t="n">
+        <v>38.17235396182765</v>
+      </c>
+      <c r="H506" t="n">
+        <v>51.68067226890757</v>
+      </c>
+      <c r="I506" t="n">
+        <v>-10.08403361344538</v>
+      </c>
+      <c r="J506" t="n">
+        <v>-0.06229395271754555</v>
+      </c>
+      <c r="K506" t="n">
+        <v>-0.1319007408058855</v>
+      </c>
+      <c r="L506" t="n">
+        <v>-0.07969621548581965</v>
+      </c>
+      <c r="M506" t="n">
+        <v>-5.364731694105402</v>
+      </c>
+      <c r="N506" t="n">
+        <v>-0.02263599870930549</v>
+      </c>
+      <c r="O506" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>0</v>
+      </c>
+      <c r="S506" t="b">
+        <v>1</v>
+      </c>
+      <c r="T506" t="n">
+        <v>-0.03881143432889061</v>
+      </c>
+      <c r="U506" t="inlineStr"/>
+      <c r="V506" t="inlineStr"/>
+      <c r="W506" t="inlineStr"/>
+      <c r="X506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>554</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>40.52863436123348</v>
+      </c>
+      <c r="F507" t="n">
+        <v>40.89051762319089</v>
+      </c>
+      <c r="G507" t="n">
+        <v>36.30658396159062</v>
+      </c>
+      <c r="H507" t="n">
+        <v>52.27606461086637</v>
+      </c>
+      <c r="I507" t="n">
+        <v>-11.74743024963289</v>
+      </c>
+      <c r="J507" t="n">
+        <v>-0.007627357767823355</v>
+      </c>
+      <c r="K507" t="n">
+        <v>-0.04854939087874002</v>
+      </c>
+      <c r="L507" t="n">
+        <v>-0.03332318813831648</v>
+      </c>
+      <c r="M507" t="n">
+        <v>-22.29822555669298</v>
+      </c>
+      <c r="N507" t="n">
+        <v>-0.03279150817160733</v>
+      </c>
+      <c r="O507" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>0</v>
+      </c>
+      <c r="S507" t="b">
+        <v>1</v>
+      </c>
+      <c r="T507" t="n">
+        <v>-0.01628767546331495</v>
+      </c>
+      <c r="U507" t="n">
+        <v>-0.04374114427367209</v>
+      </c>
+      <c r="V507" t="n">
+        <v>-0.04001651392549727</v>
+      </c>
+      <c r="W507" t="n">
+        <v>-0.02720757525011834</v>
+      </c>
+      <c r="X507" t="n">
+        <v>-0.02085354327622818</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>555</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>13.79084967320262</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>39.07563025210084</v>
+      </c>
+      <c r="F508" t="n">
+        <v>38.52644087938206</v>
+      </c>
+      <c r="G508" t="n">
+        <v>33.20091223423822</v>
+      </c>
+      <c r="H508" t="n">
+        <v>54.6218487394958</v>
+      </c>
+      <c r="I508" t="n">
+        <v>-15.54621848739495</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0.04900258851968374</v>
+      </c>
+      <c r="K508" t="n">
+        <v>-0.04641741854967676</v>
+      </c>
+      <c r="L508" t="n">
+        <v>-0.04824628699103565</v>
+      </c>
+      <c r="M508" t="n">
+        <v>-11.65404721727189</v>
+      </c>
+      <c r="N508" t="n">
+        <v>-0.04896658494652056</v>
+      </c>
+      <c r="O508" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="b">
+        <v>1</v>
+      </c>
+      <c r="T508" t="n">
+        <v>-0.07004340059573011</v>
+      </c>
+      <c r="U508" t="inlineStr"/>
+      <c r="V508" t="inlineStr"/>
+      <c r="W508" t="inlineStr"/>
+      <c r="X508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>556</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>13.08970099667774</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>42.19653179190752</v>
+      </c>
+      <c r="F509" t="n">
+        <v>40.85500617653611</v>
+      </c>
+      <c r="G509" t="n">
+        <v>39.86146367809884</v>
+      </c>
+      <c r="H509" t="n">
+        <v>50</v>
+      </c>
+      <c r="I509" t="n">
+        <v>-7.803468208092482</v>
+      </c>
+      <c r="J509" t="n">
+        <v>-0.02655454972729785</v>
+      </c>
+      <c r="K509" t="n">
+        <v>-0.08686035473058254</v>
+      </c>
+      <c r="L509" t="n">
+        <v>-0.03952666375840645</v>
+      </c>
+      <c r="M509" t="n">
+        <v>-5.298597608846791</v>
+      </c>
+      <c r="N509" t="n">
+        <v>-0.007656932960761259</v>
+      </c>
+      <c r="O509" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q509" t="n">
+        <v>0</v>
+      </c>
+      <c r="R509" t="n">
+        <v>0</v>
+      </c>
+      <c r="S509" t="b">
+        <v>1</v>
+      </c>
+      <c r="T509" t="n">
+        <v>-0.03140714200244084</v>
+      </c>
+      <c r="U509" t="n">
+        <v>-0.02254215246883228</v>
+      </c>
+      <c r="V509" t="n">
+        <v>-0.01149517057306284</v>
+      </c>
+      <c r="W509" t="n">
+        <v>0.008119591405266569</v>
+      </c>
+      <c r="X509" t="n">
+        <v>0.01622199173543871</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>557</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>14.73867595818815</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 5, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="F510" t="n">
+        <v>44.01641713724739</v>
+      </c>
+      <c r="G510" t="n">
+        <v>41.31045744402182</v>
+      </c>
+      <c r="H510" t="n">
+        <v>48.47826086956522</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-2.826086956521742</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0.8934944268935788</v>
+      </c>
+      <c r="K510" t="n">
+        <v>-0.4178020499723742</v>
+      </c>
+      <c r="L510" t="n">
+        <v>0.1863433916588051</v>
+      </c>
+      <c r="M510" t="n">
+        <v>188.3844108793375</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0.4095313279985598</v>
+      </c>
+      <c r="O510" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q510" t="n">
+        <v>10</v>
+      </c>
+      <c r="R510" t="n">
+        <v>0</v>
+      </c>
+      <c r="S510" t="b">
+        <v>1</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0.1001756384716498</v>
+      </c>
+      <c r="U510" t="n">
+        <v>0.0458761704972045</v>
+      </c>
+      <c r="V510" t="n">
+        <v>-0.03640392325369888</v>
+      </c>
+      <c r="W510" t="n">
+        <v>0.5270276023112264</v>
+      </c>
+      <c r="X510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>558</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>43.79084967320262</v>
+      </c>
+      <c r="F511" t="n">
+        <v>43.41411543704348</v>
+      </c>
+      <c r="G511" t="n">
+        <v>37.99955136272271</v>
+      </c>
+      <c r="H511" t="n">
+        <v>52.15686274509805</v>
+      </c>
+      <c r="I511" t="n">
+        <v>-8.366013071895431</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0.4288726787209134</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0.3560127923103258</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0.5024890940330922</v>
+      </c>
+      <c r="M511" t="n">
+        <v>49.94846646424591</v>
+      </c>
+      <c r="N511" t="n">
+        <v>0.06529211302515806</v>
+      </c>
+      <c r="O511" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q511" t="n">
+        <v>5</v>
+      </c>
+      <c r="R511" t="n">
+        <v>0</v>
+      </c>
+      <c r="S511" t="b">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0.4017088836414742</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0.3465658562249155</v>
+      </c>
+      <c r="V511" t="n">
+        <v>0.5020074840522804</v>
+      </c>
+      <c r="W511" t="n">
+        <v>0.2961386001904548</v>
+      </c>
+      <c r="X511" t="n">
+        <v>0.3096154224278813</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>559</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>16.34517766497462</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>44.56521739130434</v>
+      </c>
+      <c r="F512" t="n">
+        <v>44.66699895897236</v>
+      </c>
+      <c r="G512" t="n">
+        <v>40.73251936252831</v>
+      </c>
+      <c r="H512" t="n">
+        <v>51.73913043478261</v>
+      </c>
+      <c r="I512" t="n">
+        <v>-7.173913043478265</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0.01124753070128975</v>
+      </c>
+      <c r="K512" t="n">
+        <v>0.1753367035580833</v>
+      </c>
+      <c r="L512" t="n">
+        <v>-0.04944526303338648</v>
+      </c>
+      <c r="M512" t="n">
+        <v>45.33618873404146</v>
+      </c>
+      <c r="N512" t="n">
+        <v>0.0985569320305249</v>
+      </c>
+      <c r="O512" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q512" t="n">
+        <v>10</v>
+      </c>
+      <c r="R512" t="n">
+        <v>0</v>
+      </c>
+      <c r="S512" t="b">
+        <v>0</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0.2464008285017069</v>
+      </c>
+      <c r="U512" t="n">
+        <v>0.3932357505336574</v>
+      </c>
+      <c r="V512" t="n">
+        <v>0.3019092236943257</v>
+      </c>
+      <c r="W512" t="n">
+        <v>0.04224663776048874</v>
+      </c>
+      <c r="X512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>560</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>12.72183449651047</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>46.27450980392157</v>
+      </c>
+      <c r="F513" t="n">
+        <v>45.4721974159614</v>
+      </c>
+      <c r="G513" t="n">
+        <v>42.99766820743174</v>
+      </c>
+      <c r="H513" t="n">
+        <v>52.81045751633987</v>
+      </c>
+      <c r="I513" t="n">
+        <v>-6.535947712418306</v>
+      </c>
+      <c r="J513" t="n">
+        <v>-0.1640977765575101</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0.2358462862095489</v>
+      </c>
+      <c r="L513" t="n">
+        <v>-0.03195185701474126</v>
+      </c>
+      <c r="M513" t="n">
+        <v>62.66042603894397</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0.0819090536456784</v>
+      </c>
+      <c r="O513" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q513" t="n">
+        <v>10</v>
+      </c>
+      <c r="R513" t="n">
+        <v>0</v>
+      </c>
+      <c r="S513" t="b">
+        <v>0</v>
+      </c>
+      <c r="T513" t="n">
+        <v>-0.1913476957728736</v>
+      </c>
+      <c r="U513" t="n">
+        <v>-0.1066496622812743</v>
+      </c>
+      <c r="V513" t="n">
+        <v>0.05597385614392086</v>
+      </c>
+      <c r="W513" t="n">
+        <v>0.0313497786109971</v>
+      </c>
+      <c r="X513" t="n">
+        <v>0.04621304487749484</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>561</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>14.62686567164179</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>40</v>
+      </c>
+      <c r="F514" t="n">
+        <v>40.45844248630628</v>
+      </c>
+      <c r="G514" t="n">
+        <v>33.75472822437171</v>
+      </c>
+      <c r="H514" t="n">
+        <v>47.44186046511628</v>
+      </c>
+      <c r="I514" t="n">
+        <v>-7.441860465116278</v>
+      </c>
+      <c r="J514" t="n">
+        <v>-0.1425600619297001</v>
+      </c>
+      <c r="K514" t="n">
+        <v>-0.1169770112664007</v>
+      </c>
+      <c r="L514" t="n">
+        <v>-0.08238083783204066</v>
+      </c>
+      <c r="M514" t="n">
+        <v>-9.692076709275838</v>
+      </c>
+      <c r="N514" t="n">
+        <v>-0.04507942655477134</v>
+      </c>
+      <c r="O514" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>0</v>
+      </c>
+      <c r="S514" t="b">
+        <v>1</v>
+      </c>
+      <c r="T514" t="n">
+        <v>-0.0639248983965011</v>
+      </c>
+      <c r="U514" t="inlineStr"/>
+      <c r="V514" t="inlineStr"/>
+      <c r="W514" t="inlineStr"/>
+      <c r="X514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>562</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>15.49228944246738</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>43.80804953560371</v>
+      </c>
+      <c r="F515" t="n">
+        <v>43.13591854951113</v>
+      </c>
+      <c r="G515" t="n">
+        <v>39.82014804533889</v>
+      </c>
+      <c r="H515" t="n">
+        <v>50.77399380804953</v>
+      </c>
+      <c r="I515" t="n">
+        <v>-6.965944272445817</v>
+      </c>
+      <c r="J515" t="n">
+        <v>-0.002352113442406392</v>
+      </c>
+      <c r="K515" t="n">
+        <v>-0.02056863634556151</v>
+      </c>
+      <c r="L515" t="n">
+        <v>-0.02045780658657672</v>
+      </c>
+      <c r="M515" t="n">
+        <v>-15.62305156858706</v>
+      </c>
+      <c r="N515" t="n">
+        <v>-0.02425939684563208</v>
+      </c>
+      <c r="O515" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q515" t="n">
+        <v>0</v>
+      </c>
+      <c r="R515" t="n">
+        <v>0</v>
+      </c>
+      <c r="S515" t="b">
+        <v>1</v>
+      </c>
+      <c r="T515" t="n">
+        <v>-0.01111244322901122</v>
+      </c>
+      <c r="U515" t="n">
+        <v>-0.03254977116079351</v>
+      </c>
+      <c r="V515" t="n">
+        <v>-0.01056975488081733</v>
+      </c>
+      <c r="W515" t="n">
+        <v>-0.002659512782580364</v>
+      </c>
+      <c r="X515" t="n">
+        <v>-0.009466937657064562</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>563</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>19.5045045045045</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>44.85714285714285</v>
+      </c>
+      <c r="F516" t="n">
+        <v>46.1333314192271</v>
+      </c>
+      <c r="G516" t="n">
+        <v>42.42829541085218</v>
+      </c>
+      <c r="H516" t="n">
+        <v>50.28571428571429</v>
+      </c>
+      <c r="I516" t="n">
+        <v>-5.428571428571438</v>
+      </c>
+      <c r="J516" t="n">
+        <v>0.9700451371448247</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0.215060748706223</v>
+      </c>
+      <c r="L516" t="n">
+        <v>0.2099276504225073</v>
+      </c>
+      <c r="M516" t="n">
+        <v>10.91027557747204</v>
+      </c>
+      <c r="N516" t="n">
+        <v>0.03117221593563439</v>
+      </c>
+      <c r="O516" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q516" t="n">
+        <v>5</v>
+      </c>
+      <c r="R516" t="n">
+        <v>0</v>
+      </c>
+      <c r="S516" t="b">
+        <v>0</v>
+      </c>
+      <c r="T516" t="n">
+        <v>0.1495402706282832</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0.08518260741316221</v>
+      </c>
+      <c r="V516" t="n">
+        <v>0.003768889393484471</v>
+      </c>
+      <c r="W516" t="inlineStr"/>
+      <c r="X516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>564</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>11.97396963123644</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>44.74053295932679</v>
+      </c>
+      <c r="F517" t="n">
+        <v>45.29420970266041</v>
+      </c>
+      <c r="G517" t="n">
+        <v>43.68259152604714</v>
+      </c>
+      <c r="H517" t="n">
+        <v>50.91164095371668</v>
+      </c>
+      <c r="I517" t="n">
+        <v>-6.171107994389892</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0.2886194653272295</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0.1341925117032038</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0.6456521014818253</v>
+      </c>
+      <c r="M517" t="n">
+        <v>60.32829682592794</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0.08484992521227559</v>
+      </c>
+      <c r="O517" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q517" t="n">
+        <v>10</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="b">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>0.7161990760773803</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0.4241399775928861</v>
+      </c>
+      <c r="V517" t="n">
+        <v>0.203165864522231</v>
+      </c>
+      <c r="W517" t="n">
+        <v>1.038944772051698</v>
+      </c>
+      <c r="X517" t="n">
+        <v>0.37083807855234</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>565</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>16.47495361781076</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>44.10377358490566</v>
+      </c>
+      <c r="F518" t="n">
+        <v>43.31923787304365</v>
+      </c>
+      <c r="G518" t="n">
+        <v>38.54540795518287</v>
+      </c>
+      <c r="H518" t="n">
+        <v>56.13207547169812</v>
+      </c>
+      <c r="I518" t="n">
+        <v>-12.02830188679246</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0.1005257958510578</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0.09668407726045473</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0.0985748232741336</v>
+      </c>
+      <c r="M518" t="n">
+        <v>-2.555306427380984</v>
+      </c>
+      <c r="N518" t="n">
+        <v>-0.006026666102313641</v>
+      </c>
+      <c r="O518" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>0</v>
+      </c>
+      <c r="S518" t="b">
+        <v>1</v>
+      </c>
+      <c r="T518" t="n">
+        <v>0.04583507656547767</v>
+      </c>
+      <c r="U518" t="n">
+        <v>0.04831805365741337</v>
+      </c>
+      <c r="V518" t="n">
+        <v>0.01453443556655216</v>
+      </c>
+      <c r="W518" t="n">
+        <v>-0.00904170869972667</v>
+      </c>
+      <c r="X518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>566</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>13.03797468354431</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>46.01648351648351</v>
+      </c>
+      <c r="F519" t="n">
+        <v>45.14860383281436</v>
+      </c>
+      <c r="G519" t="n">
+        <v>44.17931828025748</v>
+      </c>
+      <c r="H519" t="n">
+        <v>50.96153846153846</v>
+      </c>
+      <c r="I519" t="n">
+        <v>-4.945054945054949</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0.08529466947705089</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0.1014217190806379</v>
+      </c>
+      <c r="L519" t="n">
+        <v>0.438455371361315</v>
+      </c>
+      <c r="M519" t="n">
+        <v>38.62015214163259</v>
+      </c>
+      <c r="N519" t="n">
+        <v>0.0531226301810627</v>
+      </c>
+      <c r="O519" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q519" t="n">
+        <v>10</v>
+      </c>
+      <c r="R519" t="n">
+        <v>0</v>
+      </c>
+      <c r="S519" t="b">
+        <v>0</v>
+      </c>
+      <c r="T519" t="n">
+        <v>0.2062331073926775</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0.2497880996167648</v>
+      </c>
+      <c r="V519" t="n">
+        <v>0.09908187588598558</v>
+      </c>
+      <c r="W519" t="n">
+        <v>0.2115175842331457</v>
+      </c>
+      <c r="X519" t="n">
+        <v>0.08753419736641348</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>567</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>18.369384359401</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 10, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>43.18658280922432</v>
+      </c>
+      <c r="F520" t="n">
+        <v>42.58361509811385</v>
+      </c>
+      <c r="G520" t="n">
+        <v>39.33720486063056</v>
+      </c>
+      <c r="H520" t="n">
+        <v>48.84696016771489</v>
+      </c>
+      <c r="I520" t="n">
+        <v>-5.660377358490571</v>
+      </c>
+      <c r="J520" t="n">
+        <v>-0.08721981352998683</v>
+      </c>
+      <c r="K520" t="n">
+        <v>-0.3042895888885283</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0.06344714423783056</v>
+      </c>
+      <c r="M520" t="n">
+        <v>37.70723841851458</v>
+      </c>
+      <c r="N520" t="n">
+        <v>0.07905081429457983</v>
+      </c>
+      <c r="O520" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q520" t="n">
+        <v>10</v>
+      </c>
+      <c r="R520" t="n">
+        <v>0</v>
+      </c>
+      <c r="S520" t="b">
+        <v>1</v>
+      </c>
+      <c r="T520" t="n">
+        <v>-0.04473225581817054</v>
+      </c>
+      <c r="U520" t="n">
+        <v>-0.06265514631788495</v>
+      </c>
+      <c r="V520" t="n">
+        <v>0.003482186218071775</v>
+      </c>
+      <c r="W520" t="n">
+        <v>-0.08631394077986154</v>
+      </c>
+      <c r="X520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>568</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>14.46592065106816</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>44.68085106382978</v>
+      </c>
+      <c r="F521" t="n">
+        <v>45.41213577659236</v>
+      </c>
+      <c r="G521" t="n">
+        <v>42.44429405719728</v>
+      </c>
+      <c r="H521" t="n">
+        <v>53.8563829787234</v>
+      </c>
+      <c r="I521" t="n">
+        <v>-9.175531914893618</v>
+      </c>
+      <c r="J521" t="n">
+        <v>-0.3535401563453675</v>
+      </c>
+      <c r="K521" t="n">
+        <v>-0.2877768194915504</v>
+      </c>
+      <c r="L521" t="n">
+        <v>-0.2375130921243269</v>
+      </c>
+      <c r="M521" t="n">
+        <v>14.80022130210646</v>
+      </c>
+      <c r="N521" t="n">
+        <v>0.01968114534854583</v>
+      </c>
+      <c r="O521" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q521" t="n">
+        <v>5</v>
+      </c>
+      <c r="R521" t="n">
+        <v>0</v>
+      </c>
+      <c r="S521" t="b">
+        <v>0</v>
+      </c>
+      <c r="T521" t="n">
+        <v>-0.2095274722630717</v>
+      </c>
+      <c r="U521" t="n">
+        <v>-0.08545738279849019</v>
+      </c>
+      <c r="V521" t="n">
+        <v>-0.0604904493492145</v>
+      </c>
+      <c r="W521" t="n">
+        <v>0.001906731493732501</v>
+      </c>
+      <c r="X521" t="n">
+        <v>-0.00667043764553938</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>570</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>13.02380952380953</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.1, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>46.54895666131621</v>
+      </c>
+      <c r="F522" t="n">
+        <v>46.22263121853822</v>
+      </c>
+      <c r="G522" t="n">
+        <v>44.56505732235654</v>
+      </c>
+      <c r="H522" t="n">
+        <v>52.64847512038523</v>
+      </c>
+      <c r="I522" t="n">
+        <v>-6.099518459069017</v>
+      </c>
+      <c r="J522" t="n">
+        <v>-0.367400554769003</v>
+      </c>
+      <c r="K522" t="n">
+        <v>-0.0955873315215517</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0.03725684228531511</v>
+      </c>
+      <c r="M522" t="n">
+        <v>11.71856084446091</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0.01880988899592441</v>
+      </c>
+      <c r="O522" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q522" t="n">
+        <v>5</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="b">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>0.008798324308114971</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0.03384875013981696</v>
+      </c>
+      <c r="V522" t="n">
+        <v>0.1578154180941345</v>
+      </c>
+      <c r="W522" t="n">
+        <v>0.1976306218201842</v>
+      </c>
+      <c r="X522" t="n">
+        <v>0.07311727902207758</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>571</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 1.0, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="F523" t="n">
+        <v>41.65811439518336</v>
+      </c>
+      <c r="G523" t="n">
+        <v>39.37619380386676</v>
+      </c>
+      <c r="H523" t="n">
+        <v>59.84848484848485</v>
+      </c>
+      <c r="I523" t="n">
+        <v>-18.93939393939394</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.02179847044533716</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0.0110965891866698</v>
+      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="n">
+        <v>-3.695119765887682</v>
+      </c>
+      <c r="N523" t="n">
+        <v>-0.02799333155975517</v>
+      </c>
+      <c r="O523" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="b">
+        <v>1</v>
+      </c>
+      <c r="T523" t="inlineStr"/>
+      <c r="U523" t="inlineStr"/>
+      <c r="V523" t="inlineStr"/>
+      <c r="W523" t="inlineStr"/>
+      <c r="X523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>572</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>12.49462365591398</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>45.02923976608187</v>
+      </c>
+      <c r="F524" t="n">
+        <v>45.67834114301734</v>
+      </c>
+      <c r="G524" t="n">
+        <v>43.10225082554211</v>
+      </c>
+      <c r="H524" t="n">
+        <v>52.77777777777778</v>
+      </c>
+      <c r="I524" t="n">
+        <v>-7.748538011695906</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0.1381487345210553</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0.06074658719224644</v>
+      </c>
+      <c r="L524" t="n">
+        <v>0.04049236591198631</v>
+      </c>
+      <c r="M524" t="n">
+        <v>2.178066751843659</v>
+      </c>
+      <c r="N524" t="n">
+        <v>0.003184308116730495</v>
+      </c>
+      <c r="O524" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q524" t="n">
+        <v>0</v>
+      </c>
+      <c r="R524" t="n">
+        <v>0</v>
+      </c>
+      <c r="S524" t="b">
+        <v>1</v>
+      </c>
+      <c r="T524" t="n">
+        <v>0.03946139357144716</v>
+      </c>
+      <c r="U524" t="n">
+        <v>0.05865338919616476</v>
+      </c>
+      <c r="V524" t="n">
+        <v>0.03846975362386748</v>
+      </c>
+      <c r="W524" t="n">
+        <v>0.01871593788934707</v>
+      </c>
+      <c r="X524" t="n">
+        <v>0.03391113605594364</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>573</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>20.07194244604316</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 5, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>41.88034188034188</v>
+      </c>
+      <c r="F525" t="n">
+        <v>40.36710692907153</v>
+      </c>
+      <c r="G525" t="n">
+        <v>38.50486196110431</v>
+      </c>
+      <c r="H525" t="n">
+        <v>55.98290598290598</v>
+      </c>
+      <c r="I525" t="n">
+        <v>-14.1025641025641</v>
+      </c>
+      <c r="J525" t="n">
+        <v>-0.00353434692015611</v>
+      </c>
+      <c r="K525" t="n">
+        <v>-0.01458820929317696</v>
+      </c>
+      <c r="L525" t="n">
+        <v>-0.003992212140688783</v>
+      </c>
+      <c r="M525" t="n">
+        <v>-8.499073707623964</v>
+      </c>
+      <c r="N525" t="n">
+        <v>-0.03632082781035882</v>
+      </c>
+      <c r="O525" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>0</v>
+      </c>
+      <c r="S525" t="b">
+        <v>1</v>
+      </c>
+      <c r="T525" t="n">
+        <v>-0.05847215525000721</v>
+      </c>
+      <c r="U525" t="inlineStr"/>
+      <c r="V525" t="inlineStr"/>
+      <c r="W525" t="inlineStr"/>
+      <c r="X525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>574</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>11.72852598091198</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.01, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 6, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>48.62637362637363</v>
+      </c>
+      <c r="F526" t="n">
+        <v>47.09745206199106</v>
+      </c>
+      <c r="G526" t="n">
+        <v>46.25163071667401</v>
+      </c>
+      <c r="H526" t="n">
+        <v>54.67032967032966</v>
+      </c>
+      <c r="I526" t="n">
+        <v>-6.043956043956037</v>
+      </c>
+      <c r="J526" t="n">
+        <v>-0.08673381469998588</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0.7488063936889415</v>
+      </c>
+      <c r="L526" t="n">
+        <v>-0.05220536963793175</v>
+      </c>
+      <c r="M526" t="n">
+        <v>94.67638357675173</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0.130049977440593</v>
+      </c>
+      <c r="O526" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="Q526" t="n">
+        <v>10</v>
+      </c>
+      <c r="R526" t="n">
+        <v>0</v>
+      </c>
+      <c r="S526" t="b">
+        <v>0</v>
+      </c>
+      <c r="T526" t="n">
+        <v>0.3802001143725288</v>
+      </c>
+      <c r="U526" t="n">
+        <v>0.6351061154906613</v>
+      </c>
+      <c r="V526" t="n">
+        <v>0.3071784568366404</v>
+      </c>
+      <c r="W526" t="n">
+        <v>0.4337841598294352</v>
+      </c>
+      <c r="X526" t="n">
+        <v>0.1785783181762164</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>575</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>16.47058823529412</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 0.8, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 4, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>39.08523908523909</v>
+      </c>
+      <c r="F527" t="n">
+        <v>40.41804829161873</v>
+      </c>
+      <c r="G527" t="n">
+        <v>34.77427592571522</v>
+      </c>
+      <c r="H527" t="n">
+        <v>52.80665280665281</v>
+      </c>
+      <c r="I527" t="n">
+        <v>-13.72141372141372</v>
+      </c>
+      <c r="J527" t="n">
+        <v>-0.1118649476797395</v>
+      </c>
+      <c r="K527" t="n">
+        <v>-0.06987243376807854</v>
+      </c>
+      <c r="L527" t="n">
+        <v>-0.03575537352646468</v>
+      </c>
+      <c r="M527" t="n">
+        <v>-19.2810580489745</v>
+      </c>
+      <c r="N527" t="n">
+        <v>-0.04008535976917776</v>
+      </c>
+      <c r="O527" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q527" t="n">
+        <v>0</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="b">
+        <v>1</v>
+      </c>
+      <c r="T527" t="n">
+        <v>-0.00669091803503683</v>
+      </c>
+      <c r="U527" t="n">
+        <v>-0.02365973938602997</v>
+      </c>
+      <c r="V527" t="n">
+        <v>-0.04314836969507647</v>
+      </c>
+      <c r="W527" t="n">
+        <v>-0.04506422818264852</v>
+      </c>
+      <c r="X527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>576</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>15.09554140127389</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>{'objective': 'multi:softprob', 'base_score': None, 'booster': None, 'callbacks': None, 'colsample_bylevel': None, 'colsample_bynode': None, 'colsample_bytree': 1.0, 'device': None, 'early_stopping_rounds': None, 'enable_categorical': False, 'eval_metric': None, 'feature_types': None, 'gamma': 0.5, 'grow_policy': None, 'importance_type': None, 'interaction_constraints': None, 'learning_rate': 0.001, 'max_bin': None, 'max_cat_threshold': None, 'max_cat_to_onehot': None, 'max_delta_step': None, 'max_depth': 3, 'max_leaves': None, 'min_child_weight': 1, 'missing': nan, 'monotone_constraints': None, 'multi_strategy': None, 'n_estimators': 100, 'n_jobs': None, 'num_parallel_tree': None, 'random_state': None, 'reg_alpha': None, 'reg_lambda': None, 'sampling_method': None, 'scale_pos_weight': None, 'subsample': 0.8, 'tree_method': None, 'validate_parameters': None, 'verbosity': None}</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>42.65536723163842</v>
+      </c>
+      <c r="F528" t="n">
+        <v>40.95959595959596</v>
+      </c>
+      <c r="G528" t="n">
+        <v>39.29114637674023</v>
+      </c>
+      <c r="H528" t="n">
+        <v>52.54237288135594</v>
+      </c>
+      <c r="I528" t="n">
+        <v>-9.887005649717516</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0.04966874173284253</v>
+      </c>
+      <c r="K528" t="n">
+        <v>-0.03236999693802574</v>
+      </c>
+      <c r="L528" t="n">
+        <v>-0.04293081035490729</v>
+      </c>
+      <c r="M528" t="n">
+        <v>-23.67434278478909</v>
+      </c>
+      <c r="N528" t="n">
+        <v>-0.03343833726665126</v>
+      </c>
+      <c r="O528" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="Q528" t="n">
+        <v>0</v>
+      </c>
+      <c r="R528" t="n">
+        <v>0</v>
+      </c>
+      <c r="S528" t="b">
+        <v>1</v>
+      </c>
+      <c r="T528" t="n">
+        <v>-0.05250688323723196</v>
+      </c>
+      <c r="U528" t="n">
+        <v>-0.0458685000562686</v>
+      </c>
+      <c r="V528" t="n">
+        <v>-0.058828340683461</v>
+      </c>
+      <c r="W528" t="n">
+        <v>-0.03871729985984736</v>
+      </c>
+      <c r="X528" t="n">
+        <v>-0.04173994367622029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
